--- a/MECÂNICAS/PAUTA M/JHONSON/Campanha Johnson - Top Contas Q4 FY26.xlsx
+++ b/MECÂNICAS/PAUTA M/JHONSON/Campanha Johnson - Top Contas Q4 FY26.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\Nicolas\Acompanhamentos\JOHNSON\2025.26\Q4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B360582-4F05-4C6F-AFFE-6687AB678A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20EFE581-66D0-4101-9E8E-8C9C765DF180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="705" firstSheet="1" activeTab="3" xr2:uid="{1E3193F5-9832-4B59-8D54-14EFCF6055F0}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="705" firstSheet="1" activeTab="3" xr2:uid="{1E3193F5-9832-4B59-8D54-14EFCF6055F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Mecânica" sheetId="32" state="hidden" r:id="rId1"/>
@@ -3427,7 +3427,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="213">
+  <cellXfs count="210">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3942,37 +3942,10 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3993,6 +3966,33 @@
     <xf numFmtId="3" fontId="4" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4008,11 +4008,6 @@
     <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -5782,9 +5777,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>957277</xdr:colOff>
+      <xdr:colOff>960452</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>12757</xdr:rowOff>
+      <xdr:rowOff>9582</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5862,9 +5857,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>600517</xdr:colOff>
+      <xdr:colOff>597342</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>125895</xdr:rowOff>
+      <xdr:rowOff>122720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6464,20 +6459,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B34:E43"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="0.5703125" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" customWidth="1"/>
-    <col min="5" max="11" width="9.28515625" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="9.28515625" customWidth="1"/>
-    <col min="14" max="15" width="8.7109375" customWidth="1"/>
+    <col min="1" max="1" width="0.54296875" customWidth="1"/>
+    <col min="2" max="2" width="26.26953125" customWidth="1"/>
+    <col min="3" max="3" width="12.54296875" customWidth="1"/>
+    <col min="4" max="4" width="11.7265625" customWidth="1"/>
+    <col min="5" max="11" width="9.26953125" customWidth="1"/>
+    <col min="12" max="12" width="10.7265625" customWidth="1"/>
+    <col min="13" max="13" width="9.26953125" customWidth="1"/>
+    <col min="14" max="15" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="34" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="C35" s="153" t="s">
         <v>183</v>
       </c>
@@ -6488,7 +6483,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B36" s="154" t="s">
         <v>186</v>
       </c>
@@ -6503,7 +6498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B37" s="154" t="s">
         <v>187</v>
       </c>
@@ -6518,7 +6513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B38" s="154" t="s">
         <v>188</v>
       </c>
@@ -6534,7 +6529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B39" s="154" t="s">
         <v>189</v>
       </c>
@@ -6550,7 +6545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B40" s="157" t="s">
         <v>190</v>
       </c>
@@ -6565,7 +6560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B41" s="154" t="s">
         <v>191</v>
       </c>
@@ -6580,7 +6575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:5" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:5" ht="15" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B42" s="158" t="s">
         <v>45</v>
       </c>
@@ -6597,7 +6592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:5" collapsed="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="2:5" collapsed="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
@@ -6609,32 +6604,32 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08E16C2E-5CEA-4148-9F7B-CE9B93585081}">
   <dimension ref="A1:X762"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="2" max="2" width="7.5703125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="34.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="4" width="10.42578125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="11.42578125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="6" width="1.5703125" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" customWidth="1"/>
-    <col min="9" max="9" width="27.28515625" customWidth="1"/>
-    <col min="10" max="11" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="2.7109375" customWidth="1"/>
-    <col min="13" max="13" width="13.28515625" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" customWidth="1"/>
-    <col min="16" max="16" width="11.28515625" customWidth="1"/>
-    <col min="17" max="17" width="10.28515625" customWidth="1"/>
-    <col min="18" max="18" width="2.5703125" customWidth="1"/>
-    <col min="19" max="19" width="1.7109375" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" customWidth="1"/>
-    <col min="21" max="21" width="9.140625" customWidth="1"/>
-    <col min="22" max="22" width="24.85546875" customWidth="1"/>
-    <col min="23" max="23" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="2" max="2" width="7.54296875" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="3" width="34.26953125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="10.453125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="11.453125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="1.54296875" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="15.7265625" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" customWidth="1"/>
+    <col min="9" max="9" width="27.26953125" customWidth="1"/>
+    <col min="10" max="11" width="11.453125" customWidth="1"/>
+    <col min="12" max="12" width="2.7265625" customWidth="1"/>
+    <col min="13" max="13" width="13.26953125" customWidth="1"/>
+    <col min="15" max="15" width="14.7265625" customWidth="1"/>
+    <col min="16" max="16" width="11.26953125" customWidth="1"/>
+    <col min="17" max="17" width="10.26953125" customWidth="1"/>
+    <col min="18" max="18" width="2.54296875" customWidth="1"/>
+    <col min="19" max="19" width="1.7265625" customWidth="1"/>
+    <col min="20" max="20" width="14.453125" customWidth="1"/>
+    <col min="21" max="21" width="9.1796875" customWidth="1"/>
+    <col min="22" max="22" width="24.81640625" customWidth="1"/>
+    <col min="23" max="23" width="20.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="138" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="138" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="136"/>
       <c r="B1" s="137" t="s">
         <v>510</v>
@@ -6663,7 +6658,7 @@
       <c r="V1" s="140"/>
       <c r="W1" s="140"/>
     </row>
-    <row r="2" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="30"/>
       <c r="B2" t="s">
         <v>13</v>
@@ -6720,7 +6715,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="30"/>
       <c r="C3" t="s">
         <v>45</v>
@@ -6760,7 +6755,7 @@
       </c>
       <c r="X3" s="6"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="30" t="s">
         <v>513</v>
       </c>
@@ -6819,7 +6814,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" s="30" t="s">
         <v>514</v>
       </c>
@@ -6878,7 +6873,7 @@
         <v>0.33300000000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="30" t="s">
         <v>515</v>
       </c>
@@ -6937,7 +6932,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="30" t="s">
         <v>516</v>
       </c>
@@ -6996,7 +6991,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A8" s="30" t="s">
         <v>517</v>
       </c>
@@ -7055,7 +7050,7 @@
         <v>0.16700000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" s="30" t="s">
         <v>518</v>
       </c>
@@ -7114,7 +7109,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="30" t="s">
         <v>519</v>
       </c>
@@ -7173,7 +7168,7 @@
         <v>1.3959999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="30" t="s">
         <v>520</v>
       </c>
@@ -7232,7 +7227,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A12" s="30" t="s">
         <v>521</v>
       </c>
@@ -7291,7 +7286,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="30" t="s">
         <v>522</v>
       </c>
@@ -7350,7 +7345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="30" t="s">
         <v>523</v>
       </c>
@@ -7409,7 +7404,7 @@
         <v>1.583</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" s="30" t="s">
         <v>524</v>
       </c>
@@ -7468,7 +7463,7 @@
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" s="30" t="s">
         <v>525</v>
       </c>
@@ -7527,7 +7522,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A17" s="30" t="s">
         <v>526</v>
       </c>
@@ -7586,7 +7581,7 @@
         <v>0.41699999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A18" s="30" t="s">
         <v>527</v>
       </c>
@@ -7645,7 +7640,7 @@
         <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A19" s="30" t="s">
         <v>528</v>
       </c>
@@ -7704,7 +7699,7 @@
         <v>0.20799999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A20" s="30" t="s">
         <v>529</v>
       </c>
@@ -7763,7 +7758,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A21" s="30" t="s">
         <v>530</v>
       </c>
@@ -7822,7 +7817,7 @@
         <v>0.33300000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A22" s="30" t="s">
         <v>531</v>
       </c>
@@ -7881,7 +7876,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A23" s="30" t="s">
         <v>532</v>
       </c>
@@ -7940,7 +7935,7 @@
         <v>1.333</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A24" s="30" t="s">
         <v>533</v>
       </c>
@@ -7999,7 +7994,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A25" s="30" t="s">
         <v>534</v>
       </c>
@@ -8058,7 +8053,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A26" s="30" t="s">
         <v>535</v>
       </c>
@@ -8117,7 +8112,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A27" s="30" t="s">
         <v>536</v>
       </c>
@@ -8176,7 +8171,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A28" s="30" t="s">
         <v>537</v>
       </c>
@@ -8235,7 +8230,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A29" s="30" t="s">
         <v>538</v>
       </c>
@@ -8294,7 +8289,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A30" s="30" t="s">
         <v>539</v>
       </c>
@@ -8353,7 +8348,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A31" s="30" t="s">
         <v>540</v>
       </c>
@@ -8412,7 +8407,7 @@
         <v>1.083</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A32" s="30" t="s">
         <v>541</v>
       </c>
@@ -8471,7 +8466,7 @@
         <v>0.33300000000000002</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A33" s="30" t="s">
         <v>542</v>
       </c>
@@ -8530,7 +8525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A34" s="30" t="s">
         <v>543</v>
       </c>
@@ -8589,7 +8584,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A35" s="30" t="s">
         <v>544</v>
       </c>
@@ -8648,7 +8643,7 @@
         <v>3.5419999999999998</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A36" s="30" t="s">
         <v>545</v>
       </c>
@@ -8707,7 +8702,7 @@
         <v>0.41699999999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A37" s="30" t="s">
         <v>546</v>
       </c>
@@ -8766,7 +8761,7 @@
         <v>0.45800000000000002</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A38" s="30" t="s">
         <v>547</v>
       </c>
@@ -8825,7 +8820,7 @@
         <v>3.5830000000000002</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A39" s="30" t="s">
         <v>548</v>
       </c>
@@ -8884,7 +8879,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A40" s="30" t="s">
         <v>549</v>
       </c>
@@ -8943,7 +8938,7 @@
         <v>9.375</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A41" s="30" t="s">
         <v>550</v>
       </c>
@@ -9002,7 +8997,7 @@
         <v>0.33300000000000002</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A42" s="30" t="s">
         <v>551</v>
       </c>
@@ -9061,7 +9056,7 @@
         <v>0.111</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A43" s="30" t="s">
         <v>552</v>
       </c>
@@ -9120,7 +9115,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A44" s="30" t="s">
         <v>553</v>
       </c>
@@ -9179,7 +9174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A45" s="30" t="s">
         <v>554</v>
       </c>
@@ -9238,7 +9233,7 @@
         <v>1.375</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A46" s="30" t="s">
         <v>555</v>
       </c>
@@ -9297,7 +9292,7 @@
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A47" s="30" t="s">
         <v>556</v>
       </c>
@@ -9356,7 +9351,7 @@
         <v>1.3129999999999999</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A48" s="30" t="s">
         <v>557</v>
       </c>
@@ -9415,7 +9410,7 @@
         <v>0.54200000000000004</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A49" s="30" t="s">
         <v>558</v>
       </c>
@@ -9474,7 +9469,7 @@
         <v>5.5209999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A50" s="30" t="s">
         <v>559</v>
       </c>
@@ -9533,7 +9528,7 @@
         <v>3.4169999999999998</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A51" s="30" t="s">
         <v>560</v>
       </c>
@@ -9592,7 +9587,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A52" s="30" t="s">
         <v>561</v>
       </c>
@@ -9651,7 +9646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A53" s="30" t="s">
         <v>562</v>
       </c>
@@ -9710,7 +9705,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A54" s="30" t="s">
         <v>563</v>
       </c>
@@ -9769,7 +9764,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A55" s="30" t="s">
         <v>564</v>
       </c>
@@ -9828,7 +9823,7 @@
         <v>0.16700000000000001</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A56" s="30" t="s">
         <v>565</v>
       </c>
@@ -9887,7 +9882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A57" s="30" t="s">
         <v>566</v>
       </c>
@@ -9946,7 +9941,7 @@
         <v>0.33300000000000002</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A58" s="30" t="s">
         <v>567</v>
       </c>
@@ -10005,7 +10000,7 @@
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A59" s="30" t="s">
         <v>568</v>
       </c>
@@ -10064,7 +10059,7 @@
         <v>0.95799999999999996</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A60" s="30" t="s">
         <v>569</v>
       </c>
@@ -10123,7 +10118,7 @@
         <v>0.29199999999999998</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A61" s="30" t="s">
         <v>570</v>
       </c>
@@ -10182,7 +10177,7 @@
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A62" s="30" t="s">
         <v>571</v>
       </c>
@@ -10241,7 +10236,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A63" s="30" t="s">
         <v>572</v>
       </c>
@@ -10300,7 +10295,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A64" s="30" t="s">
         <v>573</v>
       </c>
@@ -10359,7 +10354,7 @@
         <v>0.20799999999999999</v>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A65" s="30" t="s">
         <v>574</v>
       </c>
@@ -10418,7 +10413,7 @@
         <v>0.29199999999999998</v>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A66" s="30" t="s">
         <v>575</v>
       </c>
@@ -10477,7 +10472,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A67" s="30" t="s">
         <v>576</v>
       </c>
@@ -10536,7 +10531,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A68" s="30" t="s">
         <v>577</v>
       </c>
@@ -10595,7 +10590,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A69" s="30" t="s">
         <v>578</v>
       </c>
@@ -10654,7 +10649,7 @@
         <v>1.625</v>
       </c>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A70" s="30" t="s">
         <v>579</v>
       </c>
@@ -10713,7 +10708,7 @@
         <v>1.417</v>
       </c>
     </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A71" s="30" t="s">
         <v>580</v>
       </c>
@@ -10772,7 +10767,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A72" s="30" t="s">
         <v>581</v>
       </c>
@@ -10831,7 +10826,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A73" s="30" t="s">
         <v>582</v>
       </c>
@@ -10890,7 +10885,7 @@
         <v>0.16700000000000001</v>
       </c>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A74" s="30" t="s">
         <v>583</v>
       </c>
@@ -10949,7 +10944,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A75" s="30" t="s">
         <v>584</v>
       </c>
@@ -11008,7 +11003,7 @@
         <v>1.167</v>
       </c>
     </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A76" s="30" t="s">
         <v>585</v>
       </c>
@@ -11067,7 +11062,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A77" s="30" t="s">
         <v>586</v>
       </c>
@@ -11126,7 +11121,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A78" s="30" t="s">
         <v>587</v>
       </c>
@@ -11185,7 +11180,7 @@
         <v>0.33300000000000002</v>
       </c>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A79" s="30" t="s">
         <v>588</v>
       </c>
@@ -11244,7 +11239,7 @@
         <v>0.33300000000000002</v>
       </c>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A80" s="30" t="s">
         <v>589</v>
       </c>
@@ -11303,7 +11298,7 @@
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A81" s="30" t="s">
         <v>590</v>
       </c>
@@ -11362,7 +11357,7 @@
         <v>0.33300000000000002</v>
       </c>
     </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A82" s="30" t="s">
         <v>591</v>
       </c>
@@ -11421,7 +11416,7 @@
         <v>0.16700000000000001</v>
       </c>
     </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A83" s="30" t="s">
         <v>592</v>
       </c>
@@ -11480,7 +11475,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A84" s="30" t="s">
         <v>593</v>
       </c>
@@ -11539,7 +11534,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A85" s="30" t="s">
         <v>594</v>
       </c>
@@ -11598,7 +11593,7 @@
         <v>0.58299999999999996</v>
       </c>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A86" s="30" t="s">
         <v>595</v>
       </c>
@@ -11657,7 +11652,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A87" s="30" t="s">
         <v>596</v>
       </c>
@@ -11716,7 +11711,7 @@
         <v>0.33300000000000002</v>
       </c>
     </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A88" s="30" t="s">
         <v>597</v>
       </c>
@@ -11775,7 +11770,7 @@
         <v>1.167</v>
       </c>
     </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A89" s="30" t="s">
         <v>598</v>
       </c>
@@ -11834,7 +11829,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A90" s="30" t="s">
         <v>599</v>
       </c>
@@ -11893,7 +11888,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A91" s="30" t="s">
         <v>600</v>
       </c>
@@ -11952,7 +11947,7 @@
         <v>4.6669999999999998</v>
       </c>
     </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A92" s="30" t="s">
         <v>601</v>
       </c>
@@ -12011,7 +12006,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A93" s="30" t="s">
         <v>602</v>
       </c>
@@ -12070,7 +12065,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A94" s="30" t="s">
         <v>603</v>
       </c>
@@ -12129,7 +12124,7 @@
         <v>18.167000000000002</v>
       </c>
     </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A95" s="30" t="s">
         <v>604</v>
       </c>
@@ -12188,7 +12183,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A96" s="30" t="s">
         <v>605</v>
       </c>
@@ -12247,7 +12242,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A97" s="30" t="s">
         <v>606</v>
       </c>
@@ -12306,7 +12301,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A98" s="30" t="s">
         <v>607</v>
       </c>
@@ -12365,7 +12360,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A99" s="30" t="s">
         <v>608</v>
       </c>
@@ -12424,7 +12419,7 @@
         <v>0.188</v>
       </c>
     </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A100" s="30" t="s">
         <v>609</v>
       </c>
@@ -12483,7 +12478,7 @@
         <v>0.81299999999999994</v>
       </c>
     </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A101" s="30" t="s">
         <v>610</v>
       </c>
@@ -12542,7 +12537,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A102" s="30" t="s">
         <v>611</v>
       </c>
@@ -12601,7 +12596,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A103" s="30" t="s">
         <v>612</v>
       </c>
@@ -12660,7 +12655,7 @@
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A104" s="30" t="s">
         <v>613</v>
       </c>
@@ -12719,7 +12714,7 @@
         <v>1.125</v>
       </c>
     </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A105" s="30" t="s">
         <v>614</v>
       </c>
@@ -12778,7 +12773,7 @@
         <v>1.117</v>
       </c>
     </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A106" s="30" t="s">
         <v>615</v>
       </c>
@@ -12837,7 +12832,7 @@
         <v>1.125</v>
       </c>
     </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A107" s="30" t="s">
         <v>616</v>
       </c>
@@ -12885,12 +12880,9 @@
       <c r="Q107">
         <v>2</v>
       </c>
-      <c r="T107" s="210"/>
-      <c r="U107" s="211"/>
-      <c r="V107" s="211"/>
-      <c r="W107" s="211"/>
-    </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T107" s="187"/>
+    </row>
+    <row r="108" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A108" s="30" t="s">
         <v>617</v>
       </c>
@@ -12922,12 +12914,9 @@
       <c r="K108" s="134">
         <v>3</v>
       </c>
-      <c r="T108" s="210"/>
-      <c r="U108" s="211"/>
-      <c r="V108" s="211"/>
-      <c r="W108" s="211"/>
-    </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T108" s="187"/>
+    </row>
+    <row r="109" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A109" s="30" t="s">
         <v>618</v>
       </c>
@@ -12959,12 +12948,9 @@
       <c r="K109" s="134">
         <v>3</v>
       </c>
-      <c r="T109" s="210"/>
-      <c r="U109" s="211"/>
-      <c r="V109" s="211"/>
-      <c r="W109" s="211"/>
-    </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T109" s="187"/>
+    </row>
+    <row r="110" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A110" s="30" t="s">
         <v>619</v>
       </c>
@@ -12996,12 +12982,10 @@
       <c r="K110" s="134">
         <v>3</v>
       </c>
-      <c r="T110" s="210"/>
-      <c r="U110" s="211"/>
-      <c r="V110" s="211"/>
-      <c r="W110" s="212"/>
-    </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T110" s="187"/>
+      <c r="W110" s="6"/>
+    </row>
+    <row r="111" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A111" s="30" t="s">
         <v>620</v>
       </c>
@@ -13033,12 +13017,9 @@
       <c r="K111" s="134">
         <v>3</v>
       </c>
-      <c r="T111" s="210"/>
-      <c r="U111" s="211"/>
-      <c r="V111" s="211"/>
-      <c r="W111" s="211"/>
-    </row>
-    <row r="112" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T111" s="187"/>
+    </row>
+    <row r="112" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A112" s="30" t="s">
         <v>621</v>
       </c>
@@ -13070,12 +13051,9 @@
       <c r="K112" s="133">
         <v>3</v>
       </c>
-      <c r="T112" s="210"/>
-      <c r="U112" s="211"/>
-      <c r="V112" s="211"/>
-      <c r="W112" s="211"/>
-    </row>
-    <row r="113" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T112" s="187"/>
+    </row>
+    <row r="113" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A113" s="30" t="s">
         <v>622</v>
       </c>
@@ -13107,12 +13085,9 @@
       <c r="K113" s="133">
         <v>5.875</v>
       </c>
-      <c r="T113" s="210"/>
-      <c r="U113" s="211"/>
-      <c r="V113" s="211"/>
-      <c r="W113" s="211"/>
-    </row>
-    <row r="114" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T113" s="187"/>
+    </row>
+    <row r="114" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A114" s="30" t="s">
         <v>623</v>
       </c>
@@ -13144,12 +13119,9 @@
       <c r="K114" s="134">
         <v>3</v>
       </c>
-      <c r="T114" s="210"/>
-      <c r="U114" s="211"/>
-      <c r="V114" s="211"/>
-      <c r="W114" s="211"/>
-    </row>
-    <row r="115" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T114" s="187"/>
+    </row>
+    <row r="115" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A115" s="30" t="s">
         <v>624</v>
       </c>
@@ -13181,12 +13153,9 @@
       <c r="K115" s="134">
         <v>3</v>
       </c>
-      <c r="T115" s="210"/>
-      <c r="U115" s="211"/>
-      <c r="V115" s="211"/>
-      <c r="W115" s="211"/>
-    </row>
-    <row r="116" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T115" s="187"/>
+    </row>
+    <row r="116" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A116" s="30" t="s">
         <v>625</v>
       </c>
@@ -13218,12 +13187,9 @@
       <c r="K116" s="134">
         <v>3</v>
       </c>
-      <c r="T116" s="210"/>
-      <c r="U116" s="211"/>
-      <c r="V116" s="211"/>
-      <c r="W116" s="211"/>
-    </row>
-    <row r="117" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T116" s="187"/>
+    </row>
+    <row r="117" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A117" s="30" t="s">
         <v>626</v>
       </c>
@@ -13255,12 +13221,9 @@
       <c r="K117" s="134">
         <v>173</v>
       </c>
-      <c r="T117" s="210"/>
-      <c r="U117" s="211"/>
-      <c r="V117" s="211"/>
-      <c r="W117" s="211"/>
-    </row>
-    <row r="118" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T117" s="187"/>
+    </row>
+    <row r="118" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A118" s="30" t="s">
         <v>627</v>
       </c>
@@ -13292,12 +13255,9 @@
       <c r="K118" s="134">
         <v>788.33299999999997</v>
       </c>
-      <c r="T118" s="210"/>
-      <c r="U118" s="211"/>
-      <c r="V118" s="211"/>
-      <c r="W118" s="211"/>
-    </row>
-    <row r="119" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T118" s="187"/>
+    </row>
+    <row r="119" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A119" s="30" t="s">
         <v>628</v>
       </c>
@@ -13329,12 +13289,9 @@
       <c r="K119" s="134">
         <v>773.58299999999997</v>
       </c>
-      <c r="T119" s="210"/>
-      <c r="U119" s="211"/>
-      <c r="V119" s="211"/>
-      <c r="W119" s="211"/>
-    </row>
-    <row r="120" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T119" s="187"/>
+    </row>
+    <row r="120" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A120" s="30" t="s">
         <v>629</v>
       </c>
@@ -13366,12 +13323,9 @@
       <c r="K120" s="134">
         <v>222.25</v>
       </c>
-      <c r="T120" s="210"/>
-      <c r="U120" s="211"/>
-      <c r="V120" s="211"/>
-      <c r="W120" s="211"/>
-    </row>
-    <row r="121" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T120" s="187"/>
+    </row>
+    <row r="121" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A121" s="30" t="s">
         <v>630</v>
       </c>
@@ -13403,12 +13357,9 @@
       <c r="K121" s="134">
         <v>194.18799999999999</v>
       </c>
-      <c r="T121" s="210"/>
-      <c r="U121" s="211"/>
-      <c r="V121" s="211"/>
-      <c r="W121" s="211"/>
-    </row>
-    <row r="122" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T121" s="187"/>
+    </row>
+    <row r="122" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A122" s="30" t="s">
         <v>631</v>
       </c>
@@ -13440,12 +13391,9 @@
       <c r="K122" s="134">
         <v>86</v>
       </c>
-      <c r="T122" s="210"/>
-      <c r="U122" s="211"/>
-      <c r="V122" s="211"/>
-      <c r="W122" s="211"/>
-    </row>
-    <row r="123" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T122" s="187"/>
+    </row>
+    <row r="123" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A123" s="30" t="s">
         <v>632</v>
       </c>
@@ -13477,12 +13425,9 @@
       <c r="K123" s="134">
         <v>355</v>
       </c>
-      <c r="T123" s="210"/>
-      <c r="U123" s="211"/>
-      <c r="V123" s="211"/>
-      <c r="W123" s="211"/>
-    </row>
-    <row r="124" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T123" s="187"/>
+    </row>
+    <row r="124" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A124" s="30" t="s">
         <v>633</v>
       </c>
@@ -13514,12 +13459,9 @@
       <c r="K124" s="133">
         <v>287</v>
       </c>
-      <c r="T124" s="210"/>
-      <c r="U124" s="211"/>
-      <c r="V124" s="211"/>
-      <c r="W124" s="211"/>
-    </row>
-    <row r="125" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T124" s="187"/>
+    </row>
+    <row r="125" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A125" s="30" t="s">
         <v>634</v>
       </c>
@@ -13551,12 +13493,9 @@
       <c r="K125" s="134">
         <v>266</v>
       </c>
-      <c r="T125" s="210"/>
-      <c r="U125" s="211"/>
-      <c r="V125" s="211"/>
-      <c r="W125" s="211"/>
-    </row>
-    <row r="126" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T125" s="187"/>
+    </row>
+    <row r="126" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A126" s="30" t="s">
         <v>635</v>
       </c>
@@ -13588,12 +13527,9 @@
       <c r="K126" s="134">
         <v>140</v>
       </c>
-      <c r="T126" s="210"/>
-      <c r="U126" s="211"/>
-      <c r="V126" s="211"/>
-      <c r="W126" s="211"/>
-    </row>
-    <row r="127" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T126" s="187"/>
+    </row>
+    <row r="127" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A127" s="30" t="s">
         <v>636</v>
       </c>
@@ -13625,12 +13561,9 @@
       <c r="K127" s="134">
         <v>41</v>
       </c>
-      <c r="T127" s="210"/>
-      <c r="U127" s="211"/>
-      <c r="V127" s="211"/>
-      <c r="W127" s="211"/>
-    </row>
-    <row r="128" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T127" s="187"/>
+    </row>
+    <row r="128" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A128" s="30" t="s">
         <v>637</v>
       </c>
@@ -13662,12 +13595,9 @@
       <c r="K128" s="133">
         <v>3</v>
       </c>
-      <c r="T128" s="210"/>
-      <c r="U128" s="211"/>
-      <c r="V128" s="211"/>
-      <c r="W128" s="211"/>
-    </row>
-    <row r="129" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T128" s="187"/>
+    </row>
+    <row r="129" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A129" s="30" t="s">
         <v>638</v>
       </c>
@@ -13699,12 +13629,9 @@
       <c r="K129" s="134">
         <v>5.875</v>
       </c>
-      <c r="T129" s="210"/>
-      <c r="U129" s="211"/>
-      <c r="V129" s="211"/>
-      <c r="W129" s="211"/>
-    </row>
-    <row r="130" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T129" s="187"/>
+    </row>
+    <row r="130" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A130" s="30" t="s">
         <v>639</v>
       </c>
@@ -13736,12 +13663,9 @@
       <c r="K130" s="133">
         <v>2</v>
       </c>
-      <c r="T130" s="210"/>
-      <c r="U130" s="211"/>
-      <c r="V130" s="211"/>
-      <c r="W130" s="211"/>
-    </row>
-    <row r="131" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T130" s="187"/>
+    </row>
+    <row r="131" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A131" s="30" t="s">
         <v>640</v>
       </c>
@@ -13773,12 +13697,9 @@
       <c r="K131" s="133">
         <v>4</v>
       </c>
-      <c r="T131" s="210"/>
-      <c r="U131" s="211"/>
-      <c r="V131" s="211"/>
-      <c r="W131" s="211"/>
-    </row>
-    <row r="132" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T131" s="187"/>
+    </row>
+    <row r="132" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A132" s="30" t="s">
         <v>641</v>
       </c>
@@ -13810,12 +13731,9 @@
       <c r="K132" s="134">
         <v>5.875</v>
       </c>
-      <c r="T132" s="210"/>
-      <c r="U132" s="211"/>
-      <c r="V132" s="211"/>
-      <c r="W132" s="211"/>
-    </row>
-    <row r="133" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T132" s="187"/>
+    </row>
+    <row r="133" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A133" s="30" t="s">
         <v>642</v>
       </c>
@@ -13847,12 +13765,9 @@
       <c r="K133" s="134">
         <v>3</v>
       </c>
-      <c r="T133" s="210"/>
-      <c r="U133" s="211"/>
-      <c r="V133" s="211"/>
-      <c r="W133" s="211"/>
-    </row>
-    <row r="134" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T133" s="187"/>
+    </row>
+    <row r="134" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A134" s="30" t="s">
         <v>643</v>
       </c>
@@ -13884,12 +13799,9 @@
       <c r="K134" s="134">
         <v>6.5</v>
       </c>
-      <c r="T134" s="210"/>
-      <c r="U134" s="211"/>
-      <c r="V134" s="211"/>
-      <c r="W134" s="211"/>
-    </row>
-    <row r="135" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T134" s="187"/>
+    </row>
+    <row r="135" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A135" s="30" t="s">
         <v>644</v>
       </c>
@@ -13921,12 +13833,9 @@
       <c r="K135" s="134">
         <v>6.5</v>
       </c>
-      <c r="T135" s="210"/>
-      <c r="U135" s="211"/>
-      <c r="V135" s="211"/>
-      <c r="W135" s="211"/>
-    </row>
-    <row r="136" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T135" s="187"/>
+    </row>
+    <row r="136" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A136" s="30" t="s">
         <v>645</v>
       </c>
@@ -13958,12 +13867,9 @@
       <c r="K136" s="134">
         <v>6.5</v>
       </c>
-      <c r="T136" s="210"/>
-      <c r="U136" s="211"/>
-      <c r="V136" s="211"/>
-      <c r="W136" s="211"/>
-    </row>
-    <row r="137" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T136" s="187"/>
+    </row>
+    <row r="137" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A137" s="30" t="s">
         <v>646</v>
       </c>
@@ -13995,12 +13901,9 @@
       <c r="K137" s="133">
         <v>6.5</v>
       </c>
-      <c r="T137" s="210"/>
-      <c r="U137" s="211"/>
-      <c r="V137" s="211"/>
-      <c r="W137" s="211"/>
-    </row>
-    <row r="138" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T137" s="187"/>
+    </row>
+    <row r="138" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A138" s="30" t="s">
         <v>647</v>
       </c>
@@ -14032,12 +13935,9 @@
       <c r="K138" s="134">
         <v>6.5</v>
       </c>
-      <c r="T138" s="210"/>
-      <c r="U138" s="211"/>
-      <c r="V138" s="211"/>
-      <c r="W138" s="211"/>
-    </row>
-    <row r="139" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T138" s="187"/>
+    </row>
+    <row r="139" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A139" s="30" t="s">
         <v>648</v>
       </c>
@@ -14069,12 +13969,9 @@
       <c r="K139" s="133">
         <v>6.5</v>
       </c>
-      <c r="T139" s="210"/>
-      <c r="U139" s="211"/>
-      <c r="V139" s="211"/>
-      <c r="W139" s="211"/>
-    </row>
-    <row r="140" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T139" s="187"/>
+    </row>
+    <row r="140" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A140" s="30" t="s">
         <v>649</v>
       </c>
@@ -14106,12 +14003,9 @@
       <c r="K140" s="133">
         <v>6.5</v>
       </c>
-      <c r="T140" s="210"/>
-      <c r="U140" s="211"/>
-      <c r="V140" s="211"/>
-      <c r="W140" s="211"/>
-    </row>
-    <row r="141" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T140" s="187"/>
+    </row>
+    <row r="141" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A141" s="30" t="s">
         <v>650</v>
       </c>
@@ -14143,12 +14037,9 @@
       <c r="K141" s="133">
         <v>6.5</v>
       </c>
-      <c r="T141" s="210"/>
-      <c r="U141" s="211"/>
-      <c r="V141" s="211"/>
-      <c r="W141" s="211"/>
-    </row>
-    <row r="142" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T141" s="187"/>
+    </row>
+    <row r="142" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A142" s="30" t="s">
         <v>651</v>
       </c>
@@ -14180,12 +14071,9 @@
       <c r="K142" s="133">
         <v>6.875</v>
       </c>
-      <c r="T142" s="210"/>
-      <c r="U142" s="211"/>
-      <c r="V142" s="211"/>
-      <c r="W142" s="211"/>
-    </row>
-    <row r="143" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T142" s="187"/>
+    </row>
+    <row r="143" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A143" s="30" t="s">
         <v>652</v>
       </c>
@@ -14217,12 +14105,9 @@
       <c r="K143" s="134">
         <v>281</v>
       </c>
-      <c r="T143" s="210"/>
-      <c r="U143" s="211"/>
-      <c r="V143" s="211"/>
-      <c r="W143" s="211"/>
-    </row>
-    <row r="144" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T143" s="187"/>
+    </row>
+    <row r="144" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A144" s="30" t="s">
         <v>653</v>
       </c>
@@ -14254,12 +14139,9 @@
       <c r="K144" s="134">
         <v>26.332999999999998</v>
       </c>
-      <c r="T144" s="210"/>
-      <c r="U144" s="211"/>
-      <c r="V144" s="211"/>
-      <c r="W144" s="211"/>
-    </row>
-    <row r="145" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T144" s="187"/>
+    </row>
+    <row r="145" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A145" s="30" t="s">
         <v>654</v>
       </c>
@@ -14291,12 +14173,9 @@
       <c r="K145" s="133">
         <v>4.625</v>
       </c>
-      <c r="T145" s="210"/>
-      <c r="U145" s="211"/>
-      <c r="V145" s="211"/>
-      <c r="W145" s="211"/>
-    </row>
-    <row r="146" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T145" s="187"/>
+    </row>
+    <row r="146" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A146" s="30" t="s">
         <v>655</v>
       </c>
@@ -14328,12 +14207,9 @@
       <c r="K146" s="133">
         <v>26</v>
       </c>
-      <c r="T146" s="210"/>
-      <c r="U146" s="211"/>
-      <c r="V146" s="211"/>
-      <c r="W146" s="211"/>
-    </row>
-    <row r="147" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T146" s="187"/>
+    </row>
+    <row r="147" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A147" s="30" t="s">
         <v>656</v>
       </c>
@@ -14365,12 +14241,9 @@
       <c r="K147" s="134">
         <v>50.542000000000002</v>
       </c>
-      <c r="T147" s="210"/>
-      <c r="U147" s="211"/>
-      <c r="V147" s="211"/>
-      <c r="W147" s="211"/>
-    </row>
-    <row r="148" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T147" s="187"/>
+    </row>
+    <row r="148" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A148" s="30" t="s">
         <v>657</v>
       </c>
@@ -14402,12 +14275,9 @@
       <c r="K148" s="134">
         <v>42.082999999999998</v>
       </c>
-      <c r="T148" s="210"/>
-      <c r="U148" s="211"/>
-      <c r="V148" s="211"/>
-      <c r="W148" s="211"/>
-    </row>
-    <row r="149" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T148" s="187"/>
+    </row>
+    <row r="149" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A149" s="30" t="s">
         <v>658</v>
       </c>
@@ -14439,12 +14309,9 @@
       <c r="K149" s="134">
         <v>13.167</v>
       </c>
-      <c r="T149" s="210"/>
-      <c r="U149" s="211"/>
-      <c r="V149" s="211"/>
-      <c r="W149" s="211"/>
-    </row>
-    <row r="150" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T149" s="187"/>
+    </row>
+    <row r="150" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A150" s="30" t="s">
         <v>659</v>
       </c>
@@ -14476,12 +14343,9 @@
       <c r="K150" s="134">
         <v>133.25</v>
       </c>
-      <c r="T150" s="210"/>
-      <c r="U150" s="211"/>
-      <c r="V150" s="211"/>
-      <c r="W150" s="211"/>
-    </row>
-    <row r="151" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T150" s="187"/>
+    </row>
+    <row r="151" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A151" s="30" t="s">
         <v>660</v>
       </c>
@@ -14513,12 +14377,9 @@
       <c r="K151" s="133">
         <v>28.582999999999998</v>
       </c>
-      <c r="T151" s="210"/>
-      <c r="U151" s="211"/>
-      <c r="V151" s="211"/>
-      <c r="W151" s="211"/>
-    </row>
-    <row r="152" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T151" s="187"/>
+    </row>
+    <row r="152" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A152" s="30" t="s">
         <v>661</v>
       </c>
@@ -14550,12 +14411,9 @@
       <c r="K152" s="134">
         <v>9.25</v>
       </c>
-      <c r="T152" s="210"/>
-      <c r="U152" s="211"/>
-      <c r="V152" s="211"/>
-      <c r="W152" s="211"/>
-    </row>
-    <row r="153" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T152" s="187"/>
+    </row>
+    <row r="153" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A153" s="30" t="s">
         <v>662</v>
       </c>
@@ -14587,12 +14445,9 @@
       <c r="K153" s="133">
         <v>13.375</v>
       </c>
-      <c r="T153" s="210"/>
-      <c r="U153" s="211"/>
-      <c r="V153" s="211"/>
-      <c r="W153" s="211"/>
-    </row>
-    <row r="154" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T153" s="187"/>
+    </row>
+    <row r="154" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A154" s="30" t="s">
         <v>663</v>
       </c>
@@ -14624,12 +14479,9 @@
       <c r="K154" s="134">
         <v>4</v>
       </c>
-      <c r="T154" s="210"/>
-      <c r="U154" s="211"/>
-      <c r="V154" s="211"/>
-      <c r="W154" s="211"/>
-    </row>
-    <row r="155" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T154" s="187"/>
+    </row>
+    <row r="155" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A155" s="30" t="s">
         <v>664</v>
       </c>
@@ -14661,12 +14513,9 @@
       <c r="K155" s="134">
         <v>18.5</v>
       </c>
-      <c r="T155" s="210"/>
-      <c r="U155" s="211"/>
-      <c r="V155" s="211"/>
-      <c r="W155" s="211"/>
-    </row>
-    <row r="156" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T155" s="187"/>
+    </row>
+    <row r="156" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A156" s="30" t="s">
         <v>665</v>
       </c>
@@ -14698,12 +14547,9 @@
       <c r="K156" s="134">
         <v>5</v>
       </c>
-      <c r="T156" s="210"/>
-      <c r="U156" s="211"/>
-      <c r="V156" s="211"/>
-      <c r="W156" s="211"/>
-    </row>
-    <row r="157" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T156" s="187"/>
+    </row>
+    <row r="157" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A157" s="30" t="s">
         <v>666</v>
       </c>
@@ -14735,12 +14581,9 @@
       <c r="K157" s="134">
         <v>22.542000000000002</v>
       </c>
-      <c r="T157" s="210"/>
-      <c r="U157" s="211"/>
-      <c r="V157" s="211"/>
-      <c r="W157" s="211"/>
-    </row>
-    <row r="158" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T157" s="187"/>
+    </row>
+    <row r="158" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A158" s="30" t="s">
         <v>667</v>
       </c>
@@ -14772,12 +14615,9 @@
       <c r="K158" s="133">
         <v>23.792000000000002</v>
       </c>
-      <c r="T158" s="210"/>
-      <c r="U158" s="211"/>
-      <c r="V158" s="211"/>
-      <c r="W158" s="211"/>
-    </row>
-    <row r="159" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T158" s="187"/>
+    </row>
+    <row r="159" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A159" s="30" t="s">
         <v>668</v>
       </c>
@@ -14809,12 +14649,9 @@
       <c r="K159" s="134">
         <v>41.457999999999998</v>
       </c>
-      <c r="T159" s="210"/>
-      <c r="U159" s="211"/>
-      <c r="V159" s="211"/>
-      <c r="W159" s="211"/>
-    </row>
-    <row r="160" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T159" s="187"/>
+    </row>
+    <row r="160" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A160" s="30" t="s">
         <v>669</v>
       </c>
@@ -14846,12 +14683,9 @@
       <c r="K160" s="133">
         <v>26.332999999999998</v>
       </c>
-      <c r="T160" s="210"/>
-      <c r="U160" s="211"/>
-      <c r="V160" s="211"/>
-      <c r="W160" s="211"/>
-    </row>
-    <row r="161" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T160" s="187"/>
+    </row>
+    <row r="161" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A161" s="30" t="s">
         <v>670</v>
       </c>
@@ -14883,12 +14717,9 @@
       <c r="K161" s="134">
         <v>76.207999999999998</v>
       </c>
-      <c r="T161" s="210"/>
-      <c r="U161" s="211"/>
-      <c r="V161" s="211"/>
-      <c r="W161" s="211"/>
-    </row>
-    <row r="162" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T161" s="187"/>
+    </row>
+    <row r="162" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A162" s="30" t="s">
         <v>671</v>
       </c>
@@ -14920,12 +14751,9 @@
       <c r="K162" s="134">
         <v>26.332999999999998</v>
       </c>
-      <c r="T162" s="210"/>
-      <c r="U162" s="211"/>
-      <c r="V162" s="211"/>
-      <c r="W162" s="211"/>
-    </row>
-    <row r="163" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T162" s="187"/>
+    </row>
+    <row r="163" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A163" s="30" t="s">
         <v>672</v>
       </c>
@@ -14957,12 +14785,9 @@
       <c r="K163" s="133">
         <v>13.667</v>
       </c>
-      <c r="T163" s="210"/>
-      <c r="U163" s="211"/>
-      <c r="V163" s="211"/>
-      <c r="W163" s="211"/>
-    </row>
-    <row r="164" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T163" s="187"/>
+    </row>
+    <row r="164" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A164" s="30" t="s">
         <v>673</v>
       </c>
@@ -14994,12 +14819,9 @@
       <c r="K164" s="133">
         <v>6.5</v>
       </c>
-      <c r="T164" s="210"/>
-      <c r="U164" s="211"/>
-      <c r="V164" s="211"/>
-      <c r="W164" s="211"/>
-    </row>
-    <row r="165" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T164" s="187"/>
+    </row>
+    <row r="165" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A165" s="30" t="s">
         <v>674</v>
       </c>
@@ -15031,12 +14853,9 @@
       <c r="K165" s="133">
         <v>-6.5</v>
       </c>
-      <c r="T165" s="210"/>
-      <c r="U165" s="211"/>
-      <c r="V165" s="211"/>
-      <c r="W165" s="211"/>
-    </row>
-    <row r="166" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T165" s="187"/>
+    </row>
+    <row r="166" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A166" s="30" t="s">
         <v>675</v>
       </c>
@@ -15068,12 +14887,9 @@
       <c r="K166" s="134">
         <v>6.5</v>
       </c>
-      <c r="T166" s="210"/>
-      <c r="U166" s="211"/>
-      <c r="V166" s="211"/>
-      <c r="W166" s="211"/>
-    </row>
-    <row r="167" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T166" s="187"/>
+    </row>
+    <row r="167" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A167" s="30" t="s">
         <v>676</v>
       </c>
@@ -15105,12 +14921,9 @@
       <c r="K167" s="134">
         <v>6.5</v>
       </c>
-      <c r="T167" s="210"/>
-      <c r="U167" s="211"/>
-      <c r="V167" s="211"/>
-      <c r="W167" s="211"/>
-    </row>
-    <row r="168" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T167" s="187"/>
+    </row>
+    <row r="168" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A168" s="30" t="s">
         <v>677</v>
       </c>
@@ -15142,12 +14955,9 @@
       <c r="K168" s="133">
         <v>6.5</v>
       </c>
-      <c r="T168" s="210"/>
-      <c r="U168" s="211"/>
-      <c r="V168" s="211"/>
-      <c r="W168" s="211"/>
-    </row>
-    <row r="169" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T168" s="187"/>
+    </row>
+    <row r="169" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A169" s="30" t="s">
         <v>678</v>
       </c>
@@ -15179,12 +14989,9 @@
       <c r="K169" s="133">
         <v>6.5</v>
       </c>
-      <c r="T169" s="210"/>
-      <c r="U169" s="211"/>
-      <c r="V169" s="211"/>
-      <c r="W169" s="211"/>
-    </row>
-    <row r="170" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T169" s="187"/>
+    </row>
+    <row r="170" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A170" s="30" t="s">
         <v>679</v>
       </c>
@@ -15216,12 +15023,9 @@
       <c r="K170" s="133">
         <v>145.375</v>
       </c>
-      <c r="T170" s="210"/>
-      <c r="U170" s="211"/>
-      <c r="V170" s="211"/>
-      <c r="W170" s="211"/>
-    </row>
-    <row r="171" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T170" s="187"/>
+    </row>
+    <row r="171" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A171" s="30" t="s">
         <v>680</v>
       </c>
@@ -15253,12 +15057,9 @@
       <c r="K171" s="133">
         <v>259.58300000000003</v>
       </c>
-      <c r="T171" s="210"/>
-      <c r="U171" s="211"/>
-      <c r="V171" s="211"/>
-      <c r="W171" s="211"/>
-    </row>
-    <row r="172" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T171" s="187"/>
+    </row>
+    <row r="172" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A172" s="30" t="s">
         <v>681</v>
       </c>
@@ -15290,12 +15091,9 @@
       <c r="K172" s="133">
         <v>-8.5</v>
       </c>
-      <c r="T172" s="210"/>
-      <c r="U172" s="211"/>
-      <c r="V172" s="211"/>
-      <c r="W172" s="211"/>
-    </row>
-    <row r="173" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T172" s="187"/>
+    </row>
+    <row r="173" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A173" s="30" t="s">
         <v>682</v>
       </c>
@@ -15327,12 +15125,9 @@
       <c r="K173" s="133">
         <v>25.082999999999998</v>
       </c>
-      <c r="T173" s="210"/>
-      <c r="U173" s="211"/>
-      <c r="V173" s="211"/>
-      <c r="W173" s="211"/>
-    </row>
-    <row r="174" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T173" s="187"/>
+    </row>
+    <row r="174" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A174" s="30" t="s">
         <v>683</v>
       </c>
@@ -15364,12 +15159,9 @@
       <c r="K174" s="134">
         <v>65</v>
       </c>
-      <c r="T174" s="210"/>
-      <c r="U174" s="211"/>
-      <c r="V174" s="211"/>
-      <c r="W174" s="211"/>
-    </row>
-    <row r="175" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T174" s="187"/>
+    </row>
+    <row r="175" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A175" s="30" t="s">
         <v>684</v>
       </c>
@@ -15401,12 +15193,9 @@
       <c r="K175" s="133">
         <v>23.832999999999998</v>
       </c>
-      <c r="T175" s="210"/>
-      <c r="U175" s="211"/>
-      <c r="V175" s="211"/>
-      <c r="W175" s="211"/>
-    </row>
-    <row r="176" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T175" s="187"/>
+    </row>
+    <row r="176" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A176" s="30" t="s">
         <v>685</v>
       </c>
@@ -15438,12 +15227,9 @@
       <c r="K176" s="134">
         <v>65.167000000000002</v>
       </c>
-      <c r="T176" s="210"/>
-      <c r="U176" s="211"/>
-      <c r="V176" s="211"/>
-      <c r="W176" s="211"/>
-    </row>
-    <row r="177" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T176" s="187"/>
+    </row>
+    <row r="177" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A177" s="30" t="s">
         <v>686</v>
       </c>
@@ -15475,12 +15261,9 @@
       <c r="K177" s="134">
         <v>113.417</v>
       </c>
-      <c r="T177" s="210"/>
-      <c r="U177" s="211"/>
-      <c r="V177" s="211"/>
-      <c r="W177" s="211"/>
-    </row>
-    <row r="178" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T177" s="187"/>
+    </row>
+    <row r="178" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A178" s="30" t="s">
         <v>687</v>
       </c>
@@ -15512,12 +15295,9 @@
       <c r="K178" s="134">
         <v>195.333</v>
       </c>
-      <c r="T178" s="210"/>
-      <c r="U178" s="211"/>
-      <c r="V178" s="211"/>
-      <c r="W178" s="211"/>
-    </row>
-    <row r="179" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T178" s="187"/>
+    </row>
+    <row r="179" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A179" s="30" t="s">
         <v>688</v>
       </c>
@@ -15549,12 +15329,9 @@
       <c r="K179" s="134">
         <v>26.667000000000002</v>
       </c>
-      <c r="T179" s="210"/>
-      <c r="U179" s="211"/>
-      <c r="V179" s="211"/>
-      <c r="W179" s="211"/>
-    </row>
-    <row r="180" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T179" s="187"/>
+    </row>
+    <row r="180" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A180" s="30" t="s">
         <v>689</v>
       </c>
@@ -15586,12 +15363,10 @@
       <c r="K180" s="133">
         <v>30.667000000000002</v>
       </c>
-      <c r="T180" s="210"/>
-      <c r="U180" s="211"/>
-      <c r="V180" s="211"/>
-      <c r="W180" s="212"/>
-    </row>
-    <row r="181" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T180" s="187"/>
+      <c r="W180" s="6"/>
+    </row>
+    <row r="181" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A181" s="30" t="s">
         <v>690</v>
       </c>
@@ -15623,12 +15398,9 @@
       <c r="K181" s="134">
         <v>5.875</v>
       </c>
-      <c r="T181" s="210"/>
-      <c r="U181" s="211"/>
-      <c r="V181" s="211"/>
-      <c r="W181" s="211"/>
-    </row>
-    <row r="182" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T181" s="187"/>
+    </row>
+    <row r="182" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A182" s="30" t="s">
         <v>691</v>
       </c>
@@ -15660,12 +15432,9 @@
       <c r="K182" s="134">
         <v>5</v>
       </c>
-      <c r="T182" s="210"/>
-      <c r="U182" s="211"/>
-      <c r="V182" s="211"/>
-      <c r="W182" s="211"/>
-    </row>
-    <row r="183" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T182" s="187"/>
+    </row>
+    <row r="183" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A183" s="30" t="s">
         <v>692</v>
       </c>
@@ -15697,12 +15466,9 @@
       <c r="K183" s="6">
         <v>11.167</v>
       </c>
-      <c r="T183" s="210"/>
-      <c r="U183" s="211"/>
-      <c r="V183" s="211"/>
-      <c r="W183" s="211"/>
-    </row>
-    <row r="184" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T183" s="187"/>
+    </row>
+    <row r="184" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A184" s="30" t="s">
         <v>693</v>
       </c>
@@ -15734,12 +15500,9 @@
       <c r="K184">
         <v>14</v>
       </c>
-      <c r="T184" s="210"/>
-      <c r="U184" s="211"/>
-      <c r="V184" s="211"/>
-      <c r="W184" s="211"/>
-    </row>
-    <row r="185" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T184" s="187"/>
+    </row>
+    <row r="185" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A185" s="30" t="s">
         <v>694</v>
       </c>
@@ -15771,12 +15534,9 @@
       <c r="K185" s="6">
         <v>5.5</v>
       </c>
-      <c r="T185" s="210"/>
-      <c r="U185" s="211"/>
-      <c r="V185" s="211"/>
-      <c r="W185" s="211"/>
-    </row>
-    <row r="186" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T185" s="187"/>
+    </row>
+    <row r="186" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A186" s="30" t="s">
         <v>695</v>
       </c>
@@ -15808,12 +15568,9 @@
       <c r="K186" s="6">
         <v>10.75</v>
       </c>
-      <c r="T186" s="210"/>
-      <c r="U186" s="211"/>
-      <c r="V186" s="211"/>
-      <c r="W186" s="211"/>
-    </row>
-    <row r="187" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T186" s="187"/>
+    </row>
+    <row r="187" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A187" s="30" t="s">
         <v>696</v>
       </c>
@@ -15845,12 +15602,9 @@
       <c r="K187" s="6">
         <v>31.5</v>
       </c>
-      <c r="T187" s="210"/>
-      <c r="U187" s="211"/>
-      <c r="V187" s="211"/>
-      <c r="W187" s="211"/>
-    </row>
-    <row r="188" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T187" s="187"/>
+    </row>
+    <row r="188" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A188" s="30" t="s">
         <v>697</v>
       </c>
@@ -15882,12 +15636,9 @@
       <c r="K188" s="6">
         <v>11</v>
       </c>
-      <c r="T188" s="210"/>
-      <c r="U188" s="211"/>
-      <c r="V188" s="211"/>
-      <c r="W188" s="211"/>
-    </row>
-    <row r="189" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T188" s="187"/>
+    </row>
+    <row r="189" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A189" s="30" t="s">
         <v>698</v>
       </c>
@@ -15919,12 +15670,10 @@
       <c r="K189">
         <v>18.417000000000002</v>
       </c>
-      <c r="T189" s="210"/>
-      <c r="U189" s="211"/>
-      <c r="V189" s="211"/>
-      <c r="W189" s="212"/>
-    </row>
-    <row r="190" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T189" s="187"/>
+      <c r="W189" s="6"/>
+    </row>
+    <row r="190" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A190" s="30" t="s">
         <v>699</v>
       </c>
@@ -15956,12 +15705,9 @@
       <c r="K190" s="6">
         <v>-1</v>
       </c>
-      <c r="T190" s="210"/>
-      <c r="U190" s="211"/>
-      <c r="V190" s="211"/>
-      <c r="W190" s="211"/>
-    </row>
-    <row r="191" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T190" s="187"/>
+    </row>
+    <row r="191" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A191" s="30" t="s">
         <v>700</v>
       </c>
@@ -15993,12 +15739,9 @@
       <c r="K191" s="6">
         <v>224.875</v>
       </c>
-      <c r="T191" s="210"/>
-      <c r="U191" s="211"/>
-      <c r="V191" s="211"/>
-      <c r="W191" s="211"/>
-    </row>
-    <row r="192" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T191" s="187"/>
+    </row>
+    <row r="192" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A192" s="30" t="s">
         <v>701</v>
       </c>
@@ -16030,12 +15773,9 @@
       <c r="K192" s="6">
         <v>1266</v>
       </c>
-      <c r="T192" s="210"/>
-      <c r="U192" s="211"/>
-      <c r="V192" s="211"/>
-      <c r="W192" s="211"/>
-    </row>
-    <row r="193" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T192" s="187"/>
+    </row>
+    <row r="193" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A193" s="30" t="s">
         <v>702</v>
       </c>
@@ -16067,12 +15807,9 @@
       <c r="K193" s="6">
         <v>25.542000000000002</v>
       </c>
-      <c r="T193" s="210"/>
-      <c r="U193" s="211"/>
-      <c r="V193" s="211"/>
-      <c r="W193" s="211"/>
-    </row>
-    <row r="194" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T193" s="187"/>
+    </row>
+    <row r="194" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A194" s="30" t="s">
         <v>703</v>
       </c>
@@ -16104,12 +15841,9 @@
       <c r="K194" s="6">
         <v>107.167</v>
       </c>
-      <c r="T194" s="210"/>
-      <c r="U194" s="211"/>
-      <c r="V194" s="211"/>
-      <c r="W194" s="211"/>
-    </row>
-    <row r="195" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T194" s="187"/>
+    </row>
+    <row r="195" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A195" s="30" t="s">
         <v>704</v>
       </c>
@@ -16141,12 +15875,9 @@
       <c r="K195" s="6">
         <v>39</v>
       </c>
-      <c r="T195" s="210"/>
-      <c r="U195" s="211"/>
-      <c r="V195" s="211"/>
-      <c r="W195" s="211"/>
-    </row>
-    <row r="196" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T195" s="187"/>
+    </row>
+    <row r="196" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A196" s="30" t="s">
         <v>705</v>
       </c>
@@ -16178,12 +15909,9 @@
       <c r="K196" s="6">
         <v>35</v>
       </c>
-      <c r="T196" s="210"/>
-      <c r="U196" s="211"/>
-      <c r="V196" s="211"/>
-      <c r="W196" s="211"/>
-    </row>
-    <row r="197" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T196" s="187"/>
+    </row>
+    <row r="197" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A197" s="30" t="s">
         <v>706</v>
       </c>
@@ -16215,12 +15943,9 @@
       <c r="K197">
         <v>35.332999999999998</v>
       </c>
-      <c r="T197" s="210"/>
-      <c r="U197" s="211"/>
-      <c r="V197" s="211"/>
-      <c r="W197" s="211"/>
-    </row>
-    <row r="198" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T197" s="187"/>
+    </row>
+    <row r="198" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A198" s="30" t="s">
         <v>707</v>
       </c>
@@ -16252,12 +15977,9 @@
       <c r="K198">
         <v>106.917</v>
       </c>
-      <c r="T198" s="210"/>
-      <c r="U198" s="211"/>
-      <c r="V198" s="211"/>
-      <c r="W198" s="211"/>
-    </row>
-    <row r="199" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T198" s="187"/>
+    </row>
+    <row r="199" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A199" s="30" t="s">
         <v>708</v>
       </c>
@@ -16289,12 +16011,9 @@
       <c r="K199" s="6">
         <v>40.832999999999998</v>
       </c>
-      <c r="T199" s="210"/>
-      <c r="U199" s="211"/>
-      <c r="V199" s="211"/>
-      <c r="W199" s="211"/>
-    </row>
-    <row r="200" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T199" s="187"/>
+    </row>
+    <row r="200" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A200" s="30" t="s">
         <v>709</v>
       </c>
@@ -16326,12 +16045,9 @@
       <c r="K200" s="6">
         <v>28.582999999999998</v>
       </c>
-      <c r="T200" s="210"/>
-      <c r="U200" s="211"/>
-      <c r="V200" s="211"/>
-      <c r="W200" s="211"/>
-    </row>
-    <row r="201" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T200" s="187"/>
+    </row>
+    <row r="201" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A201" s="30" t="s">
         <v>710</v>
       </c>
@@ -16363,12 +16079,9 @@
       <c r="K201" s="6">
         <v>5.875</v>
       </c>
-      <c r="T201" s="210"/>
-      <c r="U201" s="211"/>
-      <c r="V201" s="211"/>
-      <c r="W201" s="211"/>
-    </row>
-    <row r="202" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T201" s="187"/>
+    </row>
+    <row r="202" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A202" s="30" t="s">
         <v>711</v>
       </c>
@@ -16400,12 +16113,9 @@
       <c r="K202">
         <v>6.3330000000000002</v>
       </c>
-      <c r="T202" s="210"/>
-      <c r="U202" s="211"/>
-      <c r="V202" s="211"/>
-      <c r="W202" s="211"/>
-    </row>
-    <row r="203" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T202" s="187"/>
+    </row>
+    <row r="203" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A203" s="30" t="s">
         <v>712</v>
       </c>
@@ -16437,12 +16147,9 @@
       <c r="K203">
         <v>11.5</v>
       </c>
-      <c r="T203" s="210"/>
-      <c r="U203" s="211"/>
-      <c r="V203" s="211"/>
-      <c r="W203" s="211"/>
-    </row>
-    <row r="204" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T203" s="187"/>
+    </row>
+    <row r="204" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A204" s="30" t="s">
         <v>713</v>
       </c>
@@ -16474,12 +16181,9 @@
       <c r="K204" s="6">
         <v>16.417000000000002</v>
       </c>
-      <c r="T204" s="210"/>
-      <c r="U204" s="211"/>
-      <c r="V204" s="211"/>
-      <c r="W204" s="211"/>
-    </row>
-    <row r="205" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T204" s="187"/>
+    </row>
+    <row r="205" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A205" s="30" t="s">
         <v>714</v>
       </c>
@@ -16511,12 +16215,9 @@
       <c r="K205" s="6">
         <v>5.875</v>
       </c>
-      <c r="T205" s="210"/>
-      <c r="U205" s="211"/>
-      <c r="V205" s="211"/>
-      <c r="W205" s="211"/>
-    </row>
-    <row r="206" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T205" s="187"/>
+    </row>
+    <row r="206" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A206" s="30" t="s">
         <v>715</v>
       </c>
@@ -16548,12 +16249,9 @@
       <c r="K206" s="6">
         <v>-8.3000000000000004E-2</v>
       </c>
-      <c r="T206" s="210"/>
-      <c r="U206" s="211"/>
-      <c r="V206" s="211"/>
-      <c r="W206" s="211"/>
-    </row>
-    <row r="207" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T206" s="187"/>
+    </row>
+    <row r="207" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A207" s="30" t="s">
         <v>716</v>
       </c>
@@ -16585,12 +16283,9 @@
       <c r="K207" s="6">
         <v>22</v>
       </c>
-      <c r="T207" s="210"/>
-      <c r="U207" s="211"/>
-      <c r="V207" s="211"/>
-      <c r="W207" s="211"/>
-    </row>
-    <row r="208" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T207" s="187"/>
+    </row>
+    <row r="208" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A208" s="30" t="s">
         <v>717</v>
       </c>
@@ -16622,12 +16317,9 @@
       <c r="K208" s="6">
         <v>29</v>
       </c>
-      <c r="T208" s="210"/>
-      <c r="U208" s="211"/>
-      <c r="V208" s="211"/>
-      <c r="W208" s="211"/>
-    </row>
-    <row r="209" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T208" s="187"/>
+    </row>
+    <row r="209" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A209" s="30" t="s">
         <v>718</v>
       </c>
@@ -16659,12 +16351,9 @@
       <c r="K209" s="6">
         <v>20.582999999999998</v>
       </c>
-      <c r="T209" s="210"/>
-      <c r="U209" s="211"/>
-      <c r="V209" s="211"/>
-      <c r="W209" s="211"/>
-    </row>
-    <row r="210" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T209" s="187"/>
+    </row>
+    <row r="210" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A210" s="30" t="s">
         <v>719</v>
       </c>
@@ -16696,12 +16385,9 @@
       <c r="K210">
         <v>24</v>
       </c>
-      <c r="T210" s="210"/>
-      <c r="U210" s="211"/>
-      <c r="V210" s="211"/>
-      <c r="W210" s="211"/>
-    </row>
-    <row r="211" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T210" s="187"/>
+    </row>
+    <row r="211" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A211" s="30" t="s">
         <v>720</v>
       </c>
@@ -16733,12 +16419,9 @@
       <c r="K211">
         <v>55</v>
       </c>
-      <c r="T211" s="210"/>
-      <c r="U211" s="211"/>
-      <c r="V211" s="211"/>
-      <c r="W211" s="211"/>
-    </row>
-    <row r="212" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T211" s="187"/>
+    </row>
+    <row r="212" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A212" s="30" t="s">
         <v>721</v>
       </c>
@@ -16770,12 +16453,9 @@
       <c r="K212">
         <v>17</v>
       </c>
-      <c r="T212" s="210"/>
-      <c r="U212" s="211"/>
-      <c r="V212" s="211"/>
-      <c r="W212" s="211"/>
-    </row>
-    <row r="213" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T212" s="187"/>
+    </row>
+    <row r="213" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A213" s="30" t="s">
         <v>722</v>
       </c>
@@ -16807,12 +16487,9 @@
       <c r="K213" s="6">
         <v>35.417000000000002</v>
       </c>
-      <c r="T213" s="210"/>
-      <c r="U213" s="211"/>
-      <c r="V213" s="211"/>
-      <c r="W213" s="211"/>
-    </row>
-    <row r="214" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T213" s="187"/>
+    </row>
+    <row r="214" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A214" s="30" t="s">
         <v>723</v>
       </c>
@@ -16844,12 +16521,9 @@
       <c r="K214" s="6">
         <v>6.5</v>
       </c>
-      <c r="T214" s="210"/>
-      <c r="U214" s="211"/>
-      <c r="V214" s="211"/>
-      <c r="W214" s="211"/>
-    </row>
-    <row r="215" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T214" s="187"/>
+    </row>
+    <row r="215" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A215" s="30" t="s">
         <v>724</v>
       </c>
@@ -16881,12 +16555,9 @@
       <c r="K215">
         <v>6.5</v>
       </c>
-      <c r="T215" s="210"/>
-      <c r="U215" s="211"/>
-      <c r="V215" s="211"/>
-      <c r="W215" s="211"/>
-    </row>
-    <row r="216" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T215" s="187"/>
+    </row>
+    <row r="216" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A216" s="30" t="s">
         <v>725</v>
       </c>
@@ -16918,12 +16589,9 @@
       <c r="K216" s="6">
         <v>25.875</v>
       </c>
-      <c r="T216" s="210"/>
-      <c r="U216" s="211"/>
-      <c r="V216" s="211"/>
-      <c r="W216" s="211"/>
-    </row>
-    <row r="217" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T216" s="187"/>
+    </row>
+    <row r="217" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A217" s="30" t="s">
         <v>726</v>
       </c>
@@ -16955,12 +16623,9 @@
       <c r="K217">
         <v>-3.8330000000000002</v>
       </c>
-      <c r="T217" s="210"/>
-      <c r="U217" s="211"/>
-      <c r="V217" s="211"/>
-      <c r="W217" s="211"/>
-    </row>
-    <row r="218" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T217" s="187"/>
+    </row>
+    <row r="218" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A218" s="30" t="s">
         <v>727</v>
       </c>
@@ -16992,12 +16657,9 @@
       <c r="K218">
         <v>296.75</v>
       </c>
-      <c r="T218" s="210"/>
-      <c r="U218" s="211"/>
-      <c r="V218" s="211"/>
-      <c r="W218" s="211"/>
-    </row>
-    <row r="219" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T218" s="187"/>
+    </row>
+    <row r="219" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A219" s="30" t="s">
         <v>728</v>
       </c>
@@ -17029,12 +16691,9 @@
       <c r="K219" s="6">
         <v>7</v>
       </c>
-      <c r="T219" s="210"/>
-      <c r="U219" s="211"/>
-      <c r="V219" s="211"/>
-      <c r="W219" s="211"/>
-    </row>
-    <row r="220" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T219" s="187"/>
+    </row>
+    <row r="220" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A220" s="30" t="s">
         <v>729</v>
       </c>
@@ -17066,12 +16725,10 @@
       <c r="K220" s="6">
         <v>19.167000000000002</v>
       </c>
-      <c r="T220" s="210"/>
-      <c r="U220" s="211"/>
-      <c r="V220" s="211"/>
-      <c r="W220" s="212"/>
-    </row>
-    <row r="221" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T220" s="187"/>
+      <c r="W220" s="6"/>
+    </row>
+    <row r="221" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A221" s="30" t="s">
         <v>730</v>
       </c>
@@ -17103,12 +16760,9 @@
       <c r="K221" s="6">
         <v>50.667000000000002</v>
       </c>
-      <c r="T221" s="210"/>
-      <c r="U221" s="211"/>
-      <c r="V221" s="211"/>
-      <c r="W221" s="211"/>
-    </row>
-    <row r="222" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T221" s="187"/>
+    </row>
+    <row r="222" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A222" s="30" t="s">
         <v>731</v>
       </c>
@@ -17140,12 +16794,9 @@
       <c r="K222" s="6">
         <v>50.917000000000002</v>
       </c>
-      <c r="T222" s="210"/>
-      <c r="U222" s="211"/>
-      <c r="V222" s="211"/>
-      <c r="W222" s="211"/>
-    </row>
-    <row r="223" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T222" s="187"/>
+    </row>
+    <row r="223" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A223" s="30" t="s">
         <v>732</v>
       </c>
@@ -17177,12 +16828,9 @@
       <c r="K223">
         <v>12.25</v>
       </c>
-      <c r="T223" s="210"/>
-      <c r="U223" s="211"/>
-      <c r="V223" s="211"/>
-      <c r="W223" s="211"/>
-    </row>
-    <row r="224" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T223" s="187"/>
+    </row>
+    <row r="224" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A224" s="30" t="s">
         <v>733</v>
       </c>
@@ -17214,12 +16862,9 @@
       <c r="K224">
         <v>63.957999999999998</v>
       </c>
-      <c r="T224" s="210"/>
-      <c r="U224" s="211"/>
-      <c r="V224" s="211"/>
-      <c r="W224" s="211"/>
-    </row>
-    <row r="225" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T224" s="187"/>
+    </row>
+    <row r="225" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A225" s="30" t="s">
         <v>734</v>
       </c>
@@ -17251,12 +16896,9 @@
       <c r="K225" s="6">
         <v>28.917000000000002</v>
       </c>
-      <c r="T225" s="210"/>
-      <c r="U225" s="211"/>
-      <c r="V225" s="211"/>
-      <c r="W225" s="211"/>
-    </row>
-    <row r="226" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T225" s="187"/>
+    </row>
+    <row r="226" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A226" s="30" t="s">
         <v>735</v>
       </c>
@@ -17288,12 +16930,9 @@
       <c r="K226">
         <v>13.625</v>
       </c>
-      <c r="T226" s="210"/>
-      <c r="U226" s="211"/>
-      <c r="V226" s="211"/>
-      <c r="W226" s="211"/>
-    </row>
-    <row r="227" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T226" s="187"/>
+    </row>
+    <row r="227" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A227" s="30" t="s">
         <v>736</v>
       </c>
@@ -17325,12 +16964,9 @@
       <c r="K227">
         <v>29.082999999999998</v>
       </c>
-      <c r="T227" s="210"/>
-      <c r="U227" s="211"/>
-      <c r="V227" s="211"/>
-      <c r="W227" s="211"/>
-    </row>
-    <row r="228" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T227" s="187"/>
+    </row>
+    <row r="228" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A228" s="30" t="s">
         <v>737</v>
       </c>
@@ -17362,12 +16998,9 @@
       <c r="K228">
         <v>0.58299999999999996</v>
       </c>
-      <c r="T228" s="210"/>
-      <c r="U228" s="211"/>
-      <c r="V228" s="211"/>
-      <c r="W228" s="211"/>
-    </row>
-    <row r="229" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T228" s="187"/>
+    </row>
+    <row r="229" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A229" s="30" t="s">
         <v>738</v>
       </c>
@@ -17399,12 +17032,10 @@
       <c r="K229">
         <v>322.83300000000003</v>
       </c>
-      <c r="T229" s="210"/>
-      <c r="U229" s="211"/>
-      <c r="V229" s="211"/>
-      <c r="W229" s="212"/>
-    </row>
-    <row r="230" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T229" s="187"/>
+      <c r="W229" s="6"/>
+    </row>
+    <row r="230" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A230" s="30" t="s">
         <v>739</v>
       </c>
@@ -17436,12 +17067,9 @@
       <c r="K230" s="6">
         <v>6</v>
       </c>
-      <c r="T230" s="210"/>
-      <c r="U230" s="211"/>
-      <c r="V230" s="211"/>
-      <c r="W230" s="211"/>
-    </row>
-    <row r="231" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T230" s="187"/>
+    </row>
+    <row r="231" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A231" s="30" t="s">
         <v>740</v>
       </c>
@@ -17473,12 +17101,9 @@
       <c r="K231">
         <v>13.167</v>
       </c>
-      <c r="T231" s="210"/>
-      <c r="U231" s="211"/>
-      <c r="V231" s="211"/>
-      <c r="W231" s="211"/>
-    </row>
-    <row r="232" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T231" s="187"/>
+    </row>
+    <row r="232" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A232" s="30" t="s">
         <v>741</v>
       </c>
@@ -17510,12 +17135,9 @@
       <c r="K232">
         <v>55</v>
       </c>
-      <c r="T232" s="210"/>
-      <c r="U232" s="211"/>
-      <c r="V232" s="211"/>
-      <c r="W232" s="211"/>
-    </row>
-    <row r="233" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T232" s="187"/>
+    </row>
+    <row r="233" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A233" s="30" t="s">
         <v>742</v>
       </c>
@@ -17547,12 +17169,9 @@
       <c r="K233" s="6">
         <v>58.292000000000002</v>
       </c>
-      <c r="T233" s="210"/>
-      <c r="U233" s="211"/>
-      <c r="V233" s="211"/>
-      <c r="W233" s="211"/>
-    </row>
-    <row r="234" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T233" s="187"/>
+    </row>
+    <row r="234" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A234" s="30" t="s">
         <v>743</v>
       </c>
@@ -17584,12 +17203,9 @@
       <c r="K234">
         <v>9.6669999999999998</v>
       </c>
-      <c r="T234" s="210"/>
-      <c r="U234" s="211"/>
-      <c r="V234" s="211"/>
-      <c r="W234" s="211"/>
-    </row>
-    <row r="235" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T234" s="187"/>
+    </row>
+    <row r="235" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A235" s="30" t="s">
         <v>744</v>
       </c>
@@ -17621,12 +17237,9 @@
       <c r="K235">
         <v>51.167000000000002</v>
       </c>
-      <c r="T235" s="210"/>
-      <c r="U235" s="211"/>
-      <c r="V235" s="211"/>
-      <c r="W235" s="211"/>
-    </row>
-    <row r="236" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T235" s="187"/>
+    </row>
+    <row r="236" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A236" s="30" t="s">
         <v>745</v>
       </c>
@@ -17658,12 +17271,9 @@
       <c r="K236">
         <v>53.082999999999998</v>
       </c>
-      <c r="T236" s="210"/>
-      <c r="U236" s="211"/>
-      <c r="V236" s="211"/>
-      <c r="W236" s="211"/>
-    </row>
-    <row r="237" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T236" s="187"/>
+    </row>
+    <row r="237" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A237" s="30" t="s">
         <v>746</v>
       </c>
@@ -17695,12 +17305,9 @@
       <c r="K237" s="6">
         <v>14.542</v>
       </c>
-      <c r="T237" s="210"/>
-      <c r="U237" s="211"/>
-      <c r="V237" s="211"/>
-      <c r="W237" s="211"/>
-    </row>
-    <row r="238" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T237" s="187"/>
+    </row>
+    <row r="238" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A238" s="30" t="s">
         <v>747</v>
       </c>
@@ -17732,12 +17339,9 @@
       <c r="K238">
         <v>15.875</v>
       </c>
-      <c r="T238" s="210"/>
-      <c r="U238" s="211"/>
-      <c r="V238" s="211"/>
-      <c r="W238" s="211"/>
-    </row>
-    <row r="239" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T238" s="187"/>
+    </row>
+    <row r="239" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A239" s="30" t="s">
         <v>748</v>
       </c>
@@ -17769,12 +17373,9 @@
       <c r="K239" s="6">
         <v>13.75</v>
       </c>
-      <c r="T239" s="210"/>
-      <c r="U239" s="211"/>
-      <c r="V239" s="211"/>
-      <c r="W239" s="211"/>
-    </row>
-    <row r="240" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T239" s="187"/>
+    </row>
+    <row r="240" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A240" s="30" t="s">
         <v>749</v>
       </c>
@@ -17806,12 +17407,9 @@
       <c r="K240">
         <v>515.65300000000002</v>
       </c>
-      <c r="T240" s="210"/>
-      <c r="U240" s="211"/>
-      <c r="V240" s="211"/>
-      <c r="W240" s="211"/>
-    </row>
-    <row r="241" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T240" s="187"/>
+    </row>
+    <row r="241" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A241" s="30" t="s">
         <v>750</v>
       </c>
@@ -17843,12 +17441,9 @@
       <c r="K241">
         <v>9.1669999999999998</v>
       </c>
-      <c r="T241" s="210"/>
-      <c r="U241" s="211"/>
-      <c r="V241" s="211"/>
-      <c r="W241" s="211"/>
-    </row>
-    <row r="242" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T241" s="187"/>
+    </row>
+    <row r="242" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A242" s="30" t="s">
         <v>751</v>
       </c>
@@ -17880,12 +17475,9 @@
       <c r="K242">
         <v>9.9510000000000005</v>
       </c>
-      <c r="T242" s="210"/>
-      <c r="U242" s="211"/>
-      <c r="V242" s="211"/>
-      <c r="W242" s="211"/>
-    </row>
-    <row r="243" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T242" s="187"/>
+    </row>
+    <row r="243" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A243" s="30" t="s">
         <v>752</v>
       </c>
@@ -17917,12 +17509,9 @@
       <c r="K243" s="6">
         <v>89</v>
       </c>
-      <c r="T243" s="210"/>
-      <c r="U243" s="211"/>
-      <c r="V243" s="211"/>
-      <c r="W243" s="211"/>
-    </row>
-    <row r="244" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T243" s="187"/>
+    </row>
+    <row r="244" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A244" s="30" t="s">
         <v>753</v>
       </c>
@@ -17954,12 +17543,9 @@
       <c r="K244">
         <v>74.457999999999998</v>
       </c>
-      <c r="T244" s="210"/>
-      <c r="U244" s="211"/>
-      <c r="V244" s="211"/>
-      <c r="W244" s="211"/>
-    </row>
-    <row r="245" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T244" s="187"/>
+    </row>
+    <row r="245" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A245" s="30" t="s">
         <v>754</v>
       </c>
@@ -17991,12 +17577,9 @@
       <c r="K245">
         <v>15.417</v>
       </c>
-      <c r="T245" s="210"/>
-      <c r="U245" s="211"/>
-      <c r="V245" s="211"/>
-      <c r="W245" s="211"/>
-    </row>
-    <row r="246" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T245" s="187"/>
+    </row>
+    <row r="246" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A246" s="30" t="s">
         <v>755</v>
       </c>
@@ -18028,12 +17611,9 @@
       <c r="K246" s="6">
         <v>63.125</v>
       </c>
-      <c r="T246" s="210"/>
-      <c r="U246" s="211"/>
-      <c r="V246" s="211"/>
-      <c r="W246" s="211"/>
-    </row>
-    <row r="247" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T246" s="187"/>
+    </row>
+    <row r="247" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A247" s="30" t="s">
         <v>756</v>
       </c>
@@ -18065,12 +17645,9 @@
       <c r="K247">
         <v>20.457999999999998</v>
       </c>
-      <c r="T247" s="210"/>
-      <c r="U247" s="211"/>
-      <c r="V247" s="211"/>
-      <c r="W247" s="211"/>
-    </row>
-    <row r="248" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T247" s="187"/>
+    </row>
+    <row r="248" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A248" s="30" t="s">
         <v>757</v>
       </c>
@@ -18102,12 +17679,9 @@
       <c r="K248">
         <v>22</v>
       </c>
-      <c r="T248" s="210"/>
-      <c r="U248" s="211"/>
-      <c r="V248" s="211"/>
-      <c r="W248" s="211"/>
-    </row>
-    <row r="249" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T248" s="187"/>
+    </row>
+    <row r="249" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A249" s="30" t="s">
         <v>758</v>
       </c>
@@ -18139,12 +17713,9 @@
       <c r="K249" s="6">
         <v>109</v>
       </c>
-      <c r="T249" s="210"/>
-      <c r="U249" s="211"/>
-      <c r="V249" s="211"/>
-      <c r="W249" s="211"/>
-    </row>
-    <row r="250" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T249" s="187"/>
+    </row>
+    <row r="250" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A250" s="30" t="s">
         <v>759</v>
       </c>
@@ -18176,12 +17747,9 @@
       <c r="K250" s="6">
         <v>1458</v>
       </c>
-      <c r="T250" s="210"/>
-      <c r="U250" s="211"/>
-      <c r="V250" s="211"/>
-      <c r="W250" s="211"/>
-    </row>
-    <row r="251" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T250" s="187"/>
+    </row>
+    <row r="251" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A251" s="30" t="s">
         <v>760</v>
       </c>
@@ -18213,12 +17781,9 @@
       <c r="K251">
         <v>261</v>
       </c>
-      <c r="T251" s="210"/>
-      <c r="U251" s="211"/>
-      <c r="V251" s="211"/>
-      <c r="W251" s="211"/>
-    </row>
-    <row r="252" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T251" s="187"/>
+    </row>
+    <row r="252" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A252" s="30" t="s">
         <v>761</v>
       </c>
@@ -18250,12 +17815,9 @@
       <c r="K252">
         <v>548.75</v>
       </c>
-      <c r="T252" s="210"/>
-      <c r="U252" s="211"/>
-      <c r="V252" s="211"/>
-      <c r="W252" s="211"/>
-    </row>
-    <row r="253" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T252" s="187"/>
+    </row>
+    <row r="253" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A253" s="30" t="s">
         <v>762</v>
       </c>
@@ -18287,12 +17849,9 @@
       <c r="K253">
         <v>578</v>
       </c>
-      <c r="T253" s="210"/>
-      <c r="U253" s="211"/>
-      <c r="V253" s="211"/>
-      <c r="W253" s="211"/>
-    </row>
-    <row r="254" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T253" s="187"/>
+    </row>
+    <row r="254" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A254" s="30" t="s">
         <v>763</v>
       </c>
@@ -18324,12 +17883,9 @@
       <c r="K254" s="6">
         <v>615</v>
       </c>
-      <c r="T254" s="210"/>
-      <c r="U254" s="211"/>
-      <c r="V254" s="211"/>
-      <c r="W254" s="211"/>
-    </row>
-    <row r="255" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T254" s="187"/>
+    </row>
+    <row r="255" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A255" s="30" t="s">
         <v>764</v>
       </c>
@@ -18361,12 +17917,9 @@
       <c r="K255">
         <v>235.917</v>
       </c>
-      <c r="T255" s="210"/>
-      <c r="U255" s="211"/>
-      <c r="V255" s="211"/>
-      <c r="W255" s="211"/>
-    </row>
-    <row r="256" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T255" s="187"/>
+    </row>
+    <row r="256" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A256" s="30" t="s">
         <v>765</v>
       </c>
@@ -18398,12 +17951,9 @@
       <c r="K256" s="6">
         <v>790.95799999999997</v>
       </c>
-      <c r="T256" s="210"/>
-      <c r="U256" s="211"/>
-      <c r="V256" s="211"/>
-      <c r="W256" s="211"/>
-    </row>
-    <row r="257" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T256" s="187"/>
+    </row>
+    <row r="257" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A257" s="30" t="s">
         <v>766</v>
       </c>
@@ -18435,12 +17985,9 @@
       <c r="K257">
         <v>688</v>
       </c>
-      <c r="T257" s="210"/>
-      <c r="U257" s="211"/>
-      <c r="V257" s="211"/>
-      <c r="W257" s="211"/>
-    </row>
-    <row r="258" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T257" s="187"/>
+    </row>
+    <row r="258" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A258" s="30" t="s">
         <v>767</v>
       </c>
@@ -18472,12 +18019,9 @@
       <c r="K258">
         <v>365</v>
       </c>
-      <c r="T258" s="210"/>
-      <c r="U258" s="211"/>
-      <c r="V258" s="211"/>
-      <c r="W258" s="211"/>
-    </row>
-    <row r="259" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T258" s="187"/>
+    </row>
+    <row r="259" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A259" s="30" t="s">
         <v>768</v>
       </c>
@@ -18509,12 +18053,9 @@
       <c r="K259">
         <v>518</v>
       </c>
-      <c r="T259" s="210"/>
-      <c r="U259" s="211"/>
-      <c r="V259" s="211"/>
-      <c r="W259" s="211"/>
-    </row>
-    <row r="260" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T259" s="187"/>
+    </row>
+    <row r="260" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A260" s="30" t="s">
         <v>769</v>
       </c>
@@ -18546,12 +18087,9 @@
       <c r="K260" s="6">
         <v>5.875</v>
       </c>
-      <c r="T260" s="210"/>
-      <c r="U260" s="211"/>
-      <c r="V260" s="211"/>
-      <c r="W260" s="211"/>
-    </row>
-    <row r="261" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T260" s="187"/>
+    </row>
+    <row r="261" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A261" s="30" t="s">
         <v>770</v>
       </c>
@@ -18583,12 +18121,9 @@
       <c r="K261">
         <v>3</v>
       </c>
-      <c r="T261" s="210"/>
-      <c r="U261" s="211"/>
-      <c r="V261" s="211"/>
-      <c r="W261" s="211"/>
-    </row>
-    <row r="262" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T261" s="187"/>
+    </row>
+    <row r="262" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A262" s="30" t="s">
         <v>771</v>
       </c>
@@ -18620,12 +18155,9 @@
       <c r="K262">
         <v>5.375</v>
       </c>
-      <c r="T262" s="210"/>
-      <c r="U262" s="211"/>
-      <c r="V262" s="211"/>
-      <c r="W262" s="211"/>
-    </row>
-    <row r="263" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T262" s="187"/>
+    </row>
+    <row r="263" spans="1:20" x14ac:dyDescent="0.35">
       <c r="G263" s="29" t="str">
         <f t="shared" si="6"/>
         <v>184335 AGO/2025</v>
@@ -18642,12 +18174,9 @@
       <c r="K263">
         <v>0.5</v>
       </c>
-      <c r="T263" s="210"/>
-      <c r="U263" s="211"/>
-      <c r="V263" s="211"/>
-      <c r="W263" s="211"/>
-    </row>
-    <row r="264" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T263" s="187"/>
+    </row>
+    <row r="264" spans="1:20" x14ac:dyDescent="0.35">
       <c r="G264" s="29" t="str">
         <f t="shared" si="6"/>
         <v>184335 FEV/2026</v>
@@ -18664,12 +18193,9 @@
       <c r="K264">
         <v>3</v>
       </c>
-      <c r="T264" s="210"/>
-      <c r="U264" s="211"/>
-      <c r="V264" s="211"/>
-      <c r="W264" s="211"/>
-    </row>
-    <row r="265" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T264" s="187"/>
+    </row>
+    <row r="265" spans="1:20" x14ac:dyDescent="0.35">
       <c r="G265" s="29" t="str">
         <f t="shared" si="6"/>
         <v>94520 JUL/2025</v>
@@ -18686,12 +18212,9 @@
       <c r="K265">
         <v>397.625</v>
       </c>
-      <c r="T265" s="210"/>
-      <c r="U265" s="211"/>
-      <c r="V265" s="211"/>
-      <c r="W265" s="211"/>
-    </row>
-    <row r="266" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T265" s="187"/>
+    </row>
+    <row r="266" spans="1:20" x14ac:dyDescent="0.35">
       <c r="G266" s="29" t="str">
         <f t="shared" si="6"/>
         <v>94520 AGO/2025</v>
@@ -18708,12 +18231,9 @@
       <c r="K266" s="6">
         <v>49.146000000000001</v>
       </c>
-      <c r="T266" s="210"/>
-      <c r="U266" s="211"/>
-      <c r="V266" s="211"/>
-      <c r="W266" s="211"/>
-    </row>
-    <row r="267" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T266" s="187"/>
+    </row>
+    <row r="267" spans="1:20" x14ac:dyDescent="0.35">
       <c r="G267" s="29" t="str">
         <f t="shared" si="6"/>
         <v>94520 SET/2025</v>
@@ -18730,12 +18250,9 @@
       <c r="K267" s="6">
         <v>1314.6669999999999</v>
       </c>
-      <c r="T267" s="210"/>
-      <c r="U267" s="211"/>
-      <c r="V267" s="211"/>
-      <c r="W267" s="211"/>
-    </row>
-    <row r="268" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="T267" s="187"/>
+    </row>
+    <row r="268" spans="1:20" x14ac:dyDescent="0.35">
       <c r="G268" s="29" t="str">
         <f t="shared" si="6"/>
         <v>94520 OUT/2025</v>
@@ -18754,7 +18271,7 @@
       </c>
       <c r="T268" s="187"/>
     </row>
-    <row r="269" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:20" x14ac:dyDescent="0.35">
       <c r="G269" s="29" t="str">
         <f t="shared" si="6"/>
         <v>94520 NOV/2025</v>
@@ -18773,7 +18290,7 @@
       </c>
       <c r="T269" s="187"/>
     </row>
-    <row r="270" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:20" x14ac:dyDescent="0.35">
       <c r="G270" s="29" t="str">
         <f t="shared" si="6"/>
         <v>94520 DEZ/2025</v>
@@ -18792,7 +18309,7 @@
       </c>
       <c r="T270" s="187"/>
     </row>
-    <row r="271" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:20" x14ac:dyDescent="0.35">
       <c r="G271" s="29" t="str">
         <f t="shared" si="6"/>
         <v>94520 JAN/2026</v>
@@ -18811,7 +18328,7 @@
       </c>
       <c r="T271" s="187"/>
     </row>
-    <row r="272" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:20" x14ac:dyDescent="0.35">
       <c r="G272" s="29" t="str">
         <f t="shared" si="6"/>
         <v>94520 FEV/2026</v>
@@ -18830,7 +18347,7 @@
       </c>
       <c r="T272" s="187"/>
     </row>
-    <row r="273" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="273" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G273" s="29" t="str">
         <f t="shared" si="6"/>
         <v>94520 MAR/2026</v>
@@ -18850,7 +18367,7 @@
       <c r="T273" s="187"/>
       <c r="W273" s="6"/>
     </row>
-    <row r="274" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="274" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G274" s="29" t="str">
         <f t="shared" si="6"/>
         <v>94520 ABR/2026</v>
@@ -18869,7 +18386,7 @@
       </c>
       <c r="T274" s="187"/>
     </row>
-    <row r="275" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="275" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G275" s="29" t="str">
         <f t="shared" si="6"/>
         <v>94520 MAI/2026</v>
@@ -18888,7 +18405,7 @@
       </c>
       <c r="T275" s="187"/>
     </row>
-    <row r="276" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="276" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G276" s="29" t="str">
         <f t="shared" si="6"/>
         <v>53461 AGO/2025</v>
@@ -18907,7 +18424,7 @@
       </c>
       <c r="T276" s="187"/>
     </row>
-    <row r="277" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="277" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G277" s="29" t="str">
         <f t="shared" si="6"/>
         <v>53461 FEV/2026</v>
@@ -18926,7 +18443,7 @@
       </c>
       <c r="T277" s="187"/>
     </row>
-    <row r="278" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="278" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G278" s="29" t="str">
         <f t="shared" si="6"/>
         <v>56110 AGO/2025</v>
@@ -18945,7 +18462,7 @@
       </c>
       <c r="T278" s="187"/>
     </row>
-    <row r="279" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="279" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G279" s="29" t="str">
         <f t="shared" si="6"/>
         <v>56110 FEV/2026</v>
@@ -18964,7 +18481,7 @@
       </c>
       <c r="T279" s="187"/>
     </row>
-    <row r="280" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="280" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G280" s="29" t="str">
         <f t="shared" si="6"/>
         <v>73922 AGO/2025</v>
@@ -18983,7 +18500,7 @@
       </c>
       <c r="T280" s="187"/>
     </row>
-    <row r="281" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="281" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G281" s="29" t="str">
         <f t="shared" si="6"/>
         <v>73922 FEV/2026</v>
@@ -19002,7 +18519,7 @@
       </c>
       <c r="T281" s="187"/>
     </row>
-    <row r="282" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="282" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G282" s="29" t="str">
         <f t="shared" si="6"/>
         <v>102953 AGO/2025</v>
@@ -19021,7 +18538,7 @@
       </c>
       <c r="T282" s="187"/>
     </row>
-    <row r="283" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="283" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G283" s="29" t="str">
         <f t="shared" si="6"/>
         <v>102953 FEV/2026</v>
@@ -19040,7 +18557,7 @@
       </c>
       <c r="T283" s="187"/>
     </row>
-    <row r="284" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="284" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G284" s="29" t="str">
         <f t="shared" si="6"/>
         <v>119456 AGO/2025</v>
@@ -19059,7 +18576,7 @@
       </c>
       <c r="T284" s="187"/>
     </row>
-    <row r="285" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="285" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G285" s="29" t="str">
         <f t="shared" si="6"/>
         <v>119456 FEV/2026</v>
@@ -19078,7 +18595,7 @@
       </c>
       <c r="T285" s="187"/>
     </row>
-    <row r="286" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="286" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G286" s="29" t="str">
         <f t="shared" si="6"/>
         <v>150368 JUL/2025</v>
@@ -19097,7 +18614,7 @@
       </c>
       <c r="T286" s="187"/>
     </row>
-    <row r="287" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="287" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G287" s="29" t="str">
         <f t="shared" si="6"/>
         <v>150368 AGO/2025</v>
@@ -19116,7 +18633,7 @@
       </c>
       <c r="T287" s="187"/>
     </row>
-    <row r="288" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="288" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G288" s="29" t="str">
         <f t="shared" si="6"/>
         <v>150368 SET/2025</v>
@@ -19135,7 +18652,7 @@
       </c>
       <c r="T288" s="187"/>
     </row>
-    <row r="289" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="289" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G289" s="29" t="str">
         <f t="shared" si="6"/>
         <v>150368 FEV/2026</v>
@@ -19154,7 +18671,7 @@
       </c>
       <c r="T289" s="187"/>
     </row>
-    <row r="290" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="290" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G290" s="29" t="str">
         <f t="shared" si="6"/>
         <v>164006 JUL/2025</v>
@@ -19173,7 +18690,7 @@
       </c>
       <c r="T290" s="187"/>
     </row>
-    <row r="291" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="291" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G291" s="29" t="str">
         <f t="shared" si="6"/>
         <v>164006 FEV/2026</v>
@@ -19192,7 +18709,7 @@
       </c>
       <c r="T291" s="187"/>
     </row>
-    <row r="292" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="292" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G292" s="29" t="str">
         <f t="shared" si="6"/>
         <v>167265 JUL/2025</v>
@@ -19212,7 +18729,7 @@
       <c r="T292" s="187"/>
       <c r="W292" s="6"/>
     </row>
-    <row r="293" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="293" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G293" s="29" t="str">
         <f t="shared" si="6"/>
         <v>167265 AGO/2025</v>
@@ -19232,7 +18749,7 @@
       <c r="T293" s="187"/>
       <c r="W293" s="6"/>
     </row>
-    <row r="294" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="294" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G294" s="29" t="str">
         <f t="shared" si="6"/>
         <v>167265 FEV/2026</v>
@@ -19251,7 +18768,7 @@
       </c>
       <c r="T294" s="187"/>
     </row>
-    <row r="295" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="295" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G295" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 JUL/2025</v>
@@ -19270,7 +18787,7 @@
       </c>
       <c r="T295" s="187"/>
     </row>
-    <row r="296" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="296" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G296" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 AGO/2025</v>
@@ -19289,7 +18806,7 @@
       </c>
       <c r="T296" s="187"/>
     </row>
-    <row r="297" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="297" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G297" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 SET/2025</v>
@@ -19308,7 +18825,7 @@
       </c>
       <c r="T297" s="187"/>
     </row>
-    <row r="298" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="298" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G298" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 OUT/2025</v>
@@ -19327,7 +18844,7 @@
       </c>
       <c r="T298" s="187"/>
     </row>
-    <row r="299" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="299" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G299" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 NOV/2025</v>
@@ -19346,7 +18863,7 @@
       </c>
       <c r="T299" s="187"/>
     </row>
-    <row r="300" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="300" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G300" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 DEZ/2025</v>
@@ -19365,7 +18882,7 @@
       </c>
       <c r="T300" s="187"/>
     </row>
-    <row r="301" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="301" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G301" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 JAN/2026</v>
@@ -19384,7 +18901,7 @@
       </c>
       <c r="T301" s="187"/>
     </row>
-    <row r="302" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="302" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G302" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 FEV/2026</v>
@@ -19403,7 +18920,7 @@
       </c>
       <c r="T302" s="187"/>
     </row>
-    <row r="303" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="303" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G303" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 MAR/2026</v>
@@ -19422,7 +18939,7 @@
       </c>
       <c r="T303" s="187"/>
     </row>
-    <row r="304" spans="7:23" x14ac:dyDescent="0.25">
+    <row r="304" spans="7:23" x14ac:dyDescent="0.35">
       <c r="G304" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 ABR/2026</v>
@@ -19441,7 +18958,7 @@
       </c>
       <c r="T304" s="187"/>
     </row>
-    <row r="305" spans="7:20" x14ac:dyDescent="0.25">
+    <row r="305" spans="7:20" x14ac:dyDescent="0.35">
       <c r="G305" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 MAI/2026</v>
@@ -19460,7 +18977,7 @@
       </c>
       <c r="T305" s="187"/>
     </row>
-    <row r="306" spans="7:20" x14ac:dyDescent="0.25">
+    <row r="306" spans="7:20" x14ac:dyDescent="0.35">
       <c r="G306" s="29" t="str">
         <f t="shared" si="6"/>
         <v>48374 JUN/2026</v>
@@ -19479,655 +18996,655 @@
       </c>
       <c r="T306" s="187"/>
     </row>
-    <row r="307" spans="7:20" x14ac:dyDescent="0.25">
+    <row r="307" spans="7:20" x14ac:dyDescent="0.35">
       <c r="T307" s="187"/>
     </row>
-    <row r="308" spans="7:20" x14ac:dyDescent="0.25">
+    <row r="308" spans="7:20" x14ac:dyDescent="0.35">
       <c r="T308" s="187"/>
     </row>
-    <row r="309" spans="7:20" x14ac:dyDescent="0.25">
+    <row r="309" spans="7:20" x14ac:dyDescent="0.35">
       <c r="T309" s="187"/>
     </row>
-    <row r="310" spans="7:20" x14ac:dyDescent="0.25">
+    <row r="310" spans="7:20" x14ac:dyDescent="0.35">
       <c r="T310" s="187"/>
     </row>
-    <row r="311" spans="7:20" x14ac:dyDescent="0.25">
+    <row r="311" spans="7:20" x14ac:dyDescent="0.35">
       <c r="T311" s="187"/>
     </row>
-    <row r="312" spans="7:20" x14ac:dyDescent="0.25">
+    <row r="312" spans="7:20" x14ac:dyDescent="0.35">
       <c r="T312" s="187"/>
     </row>
-    <row r="313" spans="7:20" x14ac:dyDescent="0.25">
+    <row r="313" spans="7:20" x14ac:dyDescent="0.35">
       <c r="T313" s="187"/>
     </row>
-    <row r="314" spans="7:20" x14ac:dyDescent="0.25">
+    <row r="314" spans="7:20" x14ac:dyDescent="0.35">
       <c r="T314" s="187"/>
     </row>
-    <row r="315" spans="7:20" x14ac:dyDescent="0.25">
+    <row r="315" spans="7:20" x14ac:dyDescent="0.35">
       <c r="T315" s="187"/>
     </row>
-    <row r="316" spans="7:20" x14ac:dyDescent="0.25">
+    <row r="316" spans="7:20" x14ac:dyDescent="0.35">
       <c r="T316" s="187"/>
     </row>
-    <row r="317" spans="7:20" x14ac:dyDescent="0.25">
+    <row r="317" spans="7:20" x14ac:dyDescent="0.35">
       <c r="T317" s="187"/>
     </row>
-    <row r="318" spans="7:20" x14ac:dyDescent="0.25">
+    <row r="318" spans="7:20" x14ac:dyDescent="0.35">
       <c r="T318" s="187"/>
     </row>
-    <row r="319" spans="7:20" x14ac:dyDescent="0.25">
+    <row r="319" spans="7:20" x14ac:dyDescent="0.35">
       <c r="T319" s="187"/>
     </row>
-    <row r="320" spans="7:20" x14ac:dyDescent="0.25">
+    <row r="320" spans="7:20" x14ac:dyDescent="0.35">
       <c r="T320" s="187"/>
     </row>
-    <row r="321" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="321" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T321" s="187"/>
     </row>
-    <row r="322" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="322" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T322" s="187"/>
     </row>
-    <row r="323" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="323" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T323" s="187"/>
     </row>
-    <row r="324" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="324" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T324" s="187"/>
     </row>
-    <row r="325" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="325" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T325" s="175"/>
     </row>
-    <row r="326" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="326" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T326" s="175"/>
     </row>
-    <row r="327" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="327" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T327" s="175"/>
     </row>
-    <row r="328" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="328" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T328" s="175"/>
     </row>
-    <row r="329" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="329" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T329" s="175"/>
     </row>
-    <row r="330" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="330" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T330" s="175"/>
     </row>
-    <row r="331" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="331" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T331" s="175"/>
     </row>
-    <row r="332" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="332" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T332" s="175"/>
     </row>
-    <row r="333" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="333" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T333" s="175"/>
     </row>
-    <row r="334" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="334" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T334" s="175"/>
     </row>
-    <row r="335" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="335" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T335" s="175"/>
     </row>
-    <row r="336" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="336" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T336" s="175"/>
     </row>
-    <row r="337" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="337" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T337" s="175"/>
     </row>
-    <row r="338" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="338" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T338" s="175"/>
     </row>
-    <row r="339" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="339" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T339" s="175"/>
     </row>
-    <row r="340" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="340" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T340" s="175"/>
     </row>
-    <row r="341" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="341" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T341" s="175"/>
     </row>
-    <row r="342" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="342" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T342" s="175"/>
     </row>
-    <row r="343" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="343" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T343" s="175"/>
     </row>
-    <row r="344" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="344" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T344" s="175"/>
     </row>
-    <row r="345" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="345" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T345" s="175"/>
     </row>
-    <row r="346" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="346" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T346" s="175"/>
     </row>
-    <row r="347" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="347" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T347" s="175"/>
     </row>
-    <row r="348" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="348" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T348" s="175"/>
     </row>
-    <row r="349" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="349" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T349" s="175"/>
     </row>
-    <row r="350" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="350" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T350" s="175"/>
     </row>
-    <row r="351" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="351" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T351" s="175"/>
     </row>
-    <row r="352" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="352" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T352" s="175"/>
     </row>
-    <row r="353" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="353" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T353" s="175"/>
     </row>
-    <row r="354" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="354" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T354" s="175"/>
     </row>
-    <row r="355" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="355" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T355" s="175"/>
     </row>
-    <row r="356" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="356" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T356" s="175"/>
     </row>
-    <row r="357" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="357" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T357" s="175"/>
     </row>
-    <row r="358" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="358" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T358" s="175"/>
     </row>
-    <row r="359" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="359" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T359" s="175"/>
     </row>
-    <row r="360" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="360" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T360" s="175"/>
     </row>
-    <row r="361" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="361" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T361" s="175"/>
     </row>
-    <row r="362" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="362" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T362" s="175"/>
     </row>
-    <row r="363" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="363" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T363" s="175"/>
     </row>
-    <row r="364" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="364" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T364" s="175"/>
     </row>
-    <row r="365" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="365" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T365" s="175"/>
     </row>
-    <row r="366" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="366" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T366" s="175"/>
     </row>
-    <row r="367" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="367" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T367" s="175"/>
     </row>
-    <row r="368" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="368" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T368" s="175"/>
     </row>
-    <row r="369" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="369" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T369" s="175"/>
     </row>
-    <row r="370" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="370" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T370" s="175"/>
     </row>
-    <row r="371" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="371" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T371" s="175"/>
     </row>
-    <row r="372" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="372" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T372" s="175"/>
     </row>
-    <row r="373" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="373" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T373" s="175"/>
     </row>
-    <row r="374" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="374" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T374" s="175"/>
     </row>
-    <row r="375" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="375" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T375" s="175"/>
     </row>
-    <row r="376" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="376" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T376" s="175"/>
     </row>
-    <row r="377" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="377" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T377" s="175"/>
     </row>
-    <row r="378" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="378" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T378" s="175"/>
     </row>
-    <row r="379" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="379" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T379" s="175"/>
     </row>
-    <row r="380" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="380" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T380" s="175"/>
     </row>
-    <row r="381" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="381" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T381" s="175"/>
     </row>
-    <row r="382" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="382" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T382" s="175"/>
     </row>
-    <row r="383" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="383" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T383" s="175"/>
     </row>
-    <row r="384" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="384" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T384" s="175"/>
     </row>
-    <row r="385" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="385" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T385" s="175"/>
     </row>
-    <row r="386" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="386" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T386" s="175"/>
     </row>
-    <row r="387" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="387" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T387" s="175"/>
     </row>
-    <row r="388" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="388" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T388" s="175"/>
     </row>
-    <row r="389" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="389" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T389" s="175"/>
     </row>
-    <row r="390" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="390" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T390" s="175"/>
     </row>
-    <row r="391" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="391" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T391" s="175"/>
     </row>
-    <row r="392" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="392" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T392" s="175"/>
     </row>
-    <row r="393" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="393" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T393" s="175"/>
     </row>
-    <row r="394" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="394" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T394" s="175"/>
     </row>
-    <row r="395" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="395" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T395" s="175"/>
     </row>
-    <row r="396" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="396" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T396" s="175"/>
     </row>
-    <row r="397" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="397" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T397" s="175"/>
     </row>
-    <row r="398" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="398" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T398" s="175"/>
     </row>
-    <row r="399" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="399" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T399" s="175"/>
     </row>
-    <row r="400" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="400" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T400" s="175"/>
     </row>
-    <row r="401" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="401" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T401" s="175"/>
     </row>
-    <row r="402" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="402" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T402" s="175"/>
     </row>
-    <row r="403" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="403" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T403" s="175"/>
     </row>
-    <row r="404" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="404" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T404" s="175"/>
     </row>
-    <row r="405" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="405" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T405" s="175"/>
     </row>
-    <row r="406" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="406" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T406" s="175"/>
     </row>
-    <row r="407" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="407" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T407" s="175"/>
     </row>
-    <row r="408" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="408" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T408" s="175"/>
     </row>
-    <row r="409" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="409" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T409" s="175"/>
     </row>
-    <row r="410" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="410" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T410" s="175"/>
     </row>
-    <row r="411" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="411" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T411" s="175"/>
     </row>
-    <row r="412" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="412" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T412" s="175"/>
     </row>
-    <row r="413" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="413" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T413" s="175"/>
     </row>
-    <row r="414" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="414" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T414" s="175"/>
     </row>
-    <row r="415" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="415" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T415" s="175"/>
     </row>
-    <row r="416" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="416" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T416" s="175"/>
     </row>
-    <row r="417" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="417" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T417" s="175"/>
     </row>
-    <row r="418" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="418" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T418" s="175"/>
     </row>
-    <row r="419" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="419" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T419" s="175"/>
     </row>
-    <row r="420" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="420" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T420" s="175"/>
     </row>
-    <row r="421" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="421" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T421" s="175"/>
     </row>
-    <row r="422" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="422" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T422" s="175"/>
     </row>
-    <row r="423" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="423" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T423" s="175"/>
     </row>
-    <row r="424" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="424" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T424" s="175"/>
     </row>
-    <row r="425" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="425" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T425" s="175"/>
     </row>
-    <row r="426" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="426" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T426" s="175"/>
     </row>
-    <row r="427" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="427" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T427" s="175"/>
     </row>
-    <row r="428" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="428" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T428" s="175"/>
     </row>
-    <row r="429" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="429" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T429" s="175"/>
     </row>
-    <row r="430" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="430" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T430" s="175"/>
     </row>
-    <row r="431" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="431" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T431" s="175"/>
     </row>
-    <row r="432" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="432" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T432" s="175"/>
     </row>
-    <row r="433" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="433" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T433" s="175"/>
     </row>
-    <row r="434" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="434" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T434" s="175"/>
     </row>
-    <row r="435" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="435" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T435" s="175"/>
     </row>
-    <row r="436" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="436" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T436" s="175"/>
     </row>
-    <row r="437" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="437" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T437" s="175"/>
     </row>
-    <row r="438" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="438" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T438" s="175"/>
     </row>
-    <row r="439" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="439" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T439" s="175"/>
     </row>
-    <row r="440" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="440" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T440" s="175"/>
     </row>
-    <row r="441" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="441" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T441" s="175"/>
     </row>
-    <row r="442" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="442" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T442" s="175"/>
     </row>
-    <row r="443" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="443" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T443" s="175"/>
     </row>
-    <row r="444" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="444" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T444" s="175"/>
     </row>
-    <row r="445" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="445" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T445" s="175"/>
     </row>
-    <row r="446" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="446" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T446" s="175"/>
     </row>
-    <row r="447" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="447" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T447" s="175"/>
     </row>
-    <row r="448" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="448" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T448" s="175"/>
     </row>
-    <row r="449" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="449" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T449" s="175"/>
     </row>
-    <row r="450" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="450" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T450" s="175"/>
     </row>
-    <row r="451" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="451" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T451" s="175"/>
     </row>
-    <row r="452" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="452" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T452" s="175"/>
     </row>
-    <row r="453" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="453" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T453" s="175"/>
     </row>
-    <row r="454" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="454" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T454" s="175"/>
     </row>
-    <row r="455" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="455" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T455" s="175"/>
     </row>
-    <row r="456" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="456" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T456" s="175"/>
     </row>
-    <row r="457" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="457" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T457" s="175"/>
     </row>
-    <row r="458" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="458" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T458" s="175"/>
     </row>
-    <row r="459" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="459" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T459" s="175"/>
     </row>
-    <row r="460" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="460" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T460" s="175"/>
     </row>
-    <row r="461" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="461" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T461" s="175"/>
     </row>
-    <row r="462" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="462" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T462" s="175"/>
     </row>
-    <row r="463" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="463" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T463" s="175"/>
     </row>
-    <row r="464" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="464" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T464" s="175"/>
     </row>
-    <row r="465" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="465" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T465" s="175"/>
     </row>
-    <row r="466" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="466" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T466" s="175"/>
     </row>
-    <row r="467" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="467" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T467" s="175"/>
     </row>
-    <row r="468" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="468" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T468" s="175"/>
     </row>
-    <row r="469" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="469" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T469" s="175"/>
     </row>
-    <row r="470" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="470" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T470" s="175"/>
     </row>
-    <row r="471" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="471" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T471" s="175"/>
     </row>
-    <row r="472" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="472" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T472" s="175"/>
     </row>
-    <row r="473" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="473" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T473" s="175"/>
     </row>
-    <row r="474" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="474" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T474" s="175"/>
     </row>
-    <row r="475" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="475" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T475" s="175"/>
     </row>
-    <row r="476" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="476" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T476" s="175"/>
     </row>
-    <row r="477" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="477" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T477" s="175"/>
     </row>
-    <row r="478" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="478" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T478" s="175"/>
     </row>
-    <row r="479" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="479" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T479" s="175"/>
     </row>
-    <row r="480" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="480" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T480" s="175"/>
     </row>
-    <row r="481" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="481" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T481" s="175"/>
     </row>
-    <row r="482" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="482" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T482" s="175"/>
     </row>
-    <row r="483" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="483" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T483" s="175"/>
     </row>
-    <row r="484" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="484" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T484" s="175"/>
     </row>
-    <row r="485" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="485" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T485" s="175"/>
     </row>
-    <row r="486" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="486" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T486" s="175"/>
     </row>
-    <row r="487" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="487" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T487" s="175"/>
     </row>
-    <row r="488" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="488" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T488" s="175"/>
     </row>
-    <row r="489" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="489" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T489" s="175"/>
     </row>
-    <row r="490" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="490" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T490" s="175"/>
     </row>
-    <row r="491" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="491" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T491" s="175"/>
     </row>
-    <row r="492" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="492" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T492" s="175"/>
     </row>
-    <row r="493" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="493" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T493" s="175"/>
     </row>
-    <row r="494" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="494" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T494" s="175"/>
     </row>
-    <row r="495" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="495" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T495" s="175"/>
     </row>
-    <row r="496" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="496" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T496" s="175"/>
     </row>
-    <row r="497" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="497" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T497" s="175"/>
     </row>
-    <row r="498" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="498" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T498" s="175"/>
     </row>
-    <row r="499" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="499" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T499" s="175"/>
     </row>
-    <row r="500" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="500" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T500" s="175"/>
     </row>
-    <row r="501" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="501" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T501" s="175"/>
     </row>
-    <row r="502" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="502" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T502" s="175"/>
     </row>
-    <row r="503" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="503" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T503" s="175"/>
     </row>
-    <row r="504" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="504" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T504" s="175"/>
     </row>
-    <row r="505" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="505" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T505" s="175"/>
     </row>
-    <row r="506" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="506" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T506" s="175"/>
     </row>
-    <row r="507" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="507" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T507" s="175"/>
     </row>
-    <row r="508" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="508" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T508" s="175"/>
     </row>
-    <row r="509" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="509" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T509" s="175"/>
     </row>
-    <row r="510" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="510" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T510" s="175"/>
     </row>
-    <row r="511" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="511" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T511" s="175"/>
     </row>
-    <row r="512" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="512" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T512" s="175"/>
     </row>
-    <row r="513" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="513" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T513" s="175"/>
     </row>
-    <row r="514" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="514" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T514" s="175"/>
     </row>
-    <row r="515" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="515" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T515" s="175"/>
     </row>
-    <row r="516" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="516" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T516" s="175"/>
     </row>
-    <row r="517" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="517" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T517" s="175"/>
     </row>
-    <row r="518" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="518" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T518" s="175"/>
     </row>
-    <row r="519" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="519" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T519" s="175"/>
     </row>
-    <row r="520" spans="20:20" x14ac:dyDescent="0.25">
+    <row r="520" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T520" s="175"/>
     </row>
-    <row r="753" spans="23:23" x14ac:dyDescent="0.25">
+    <row r="753" spans="23:23" x14ac:dyDescent="0.35">
       <c r="W753" s="6"/>
     </row>
-    <row r="760" spans="23:23" x14ac:dyDescent="0.25">
+    <row r="760" spans="23:23" x14ac:dyDescent="0.35">
       <c r="W760" s="6"/>
     </row>
-    <row r="762" spans="23:23" x14ac:dyDescent="0.25">
+    <row r="762" spans="23:23" x14ac:dyDescent="0.35">
       <c r="W762" s="6"/>
     </row>
   </sheetData>
@@ -20146,18 +19663,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B43:E50"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="0.5703125" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" customWidth="1"/>
-    <col min="5" max="11" width="9.28515625" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="9.28515625" customWidth="1"/>
+    <col min="1" max="1" width="0.54296875" customWidth="1"/>
+    <col min="2" max="2" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.26953125" customWidth="1"/>
+    <col min="5" max="11" width="9.26953125" customWidth="1"/>
+    <col min="12" max="12" width="10.7265625" customWidth="1"/>
+    <col min="13" max="13" width="9.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="43" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="C43" s="153" t="s">
         <v>183</v>
       </c>
@@ -20168,7 +19685,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="44" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B44" s="154" t="s">
         <v>186</v>
       </c>
@@ -20183,7 +19700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B45" s="154" t="s">
         <v>187</v>
       </c>
@@ -20198,7 +19715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B46" s="154" t="s">
         <v>188</v>
       </c>
@@ -20213,7 +19730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B47" s="154" t="s">
         <v>189</v>
       </c>
@@ -20228,7 +19745,7 @@
         <v>2.6785714285714284E-2</v>
       </c>
     </row>
-    <row r="48" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B48" s="157" t="s">
         <v>190</v>
       </c>
@@ -20243,7 +19760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="B49" s="154" t="s">
         <v>191</v>
       </c>
@@ -20258,7 +19775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:5" ht="15.75" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:5" ht="15" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B50" s="158" t="s">
         <v>45</v>
       </c>
@@ -20286,14 +19803,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{306574E5-8675-47EB-B5C3-14B418849B1A}">
   <dimension ref="B3:H11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:8" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8" ht="26" x14ac:dyDescent="0.35">
       <c r="B3" s="182" t="s">
         <v>2</v>
       </c>
@@ -20316,7 +19833,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" s="163">
         <v>4054</v>
       </c>
@@ -20339,7 +19856,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B5" s="163">
         <v>3655</v>
       </c>
@@ -20362,7 +19879,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B6" s="163">
         <v>3919</v>
       </c>
@@ -20383,7 +19900,7 @@
       </c>
       <c r="H6" s="177"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B7" s="163">
         <v>4066</v>
       </c>
@@ -20406,7 +19923,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B8" s="163">
         <v>771</v>
       </c>
@@ -20427,7 +19944,7 @@
       </c>
       <c r="H8" s="163"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B9" s="180">
         <v>179</v>
       </c>
@@ -20448,7 +19965,7 @@
       </c>
       <c r="H9" s="179"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B10" s="180">
         <v>3956</v>
       </c>
@@ -20469,7 +19986,7 @@
       </c>
       <c r="H10" s="179"/>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B11" s="180">
         <v>359</v>
       </c>
@@ -20502,245 +20019,245 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:CU23944"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.26953125" defaultRowHeight="13" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.42578125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="8" max="8" width="8.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="8.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="7.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="7.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="2" max="2" width="16.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.453125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="8" max="8" width="8.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="8.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="7.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="7.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="12" max="12" width="8" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="8.5703125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="14" width="8.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="7.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="16" max="16" width="8.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="17" width="7.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="19" width="7.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="20" width="8.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="7.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="22" max="23" width="7.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="24" max="24" width="8.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="25" max="25" width="7.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="26" max="26" width="7.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="27" max="27" width="1.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="28" max="28" width="8.140625" style="1" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="29" max="29" width="7.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="30" max="30" width="8.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="31" max="31" width="7.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="32" max="32" width="7.140625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="33" max="33" width="7.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="34" max="34" width="8.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="35" max="35" width="7.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="36" max="36" width="8.140625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="37" max="37" width="8.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="38" max="38" width="7.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="39" max="39" width="7.140625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="40" max="40" width="8.140625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="41" max="41" width="8.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="42" max="42" width="7.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="43" max="43" width="7.140625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="44" max="44" width="8.140625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="45" max="45" width="8.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="46" max="46" width="7.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="47" max="47" width="7.140625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="48" max="48" width="4.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="49" max="49" width="8.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="13" max="13" width="8.54296875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="8.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="7.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="8.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="17" width="7.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="19" width="7.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="8.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="7.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="23" width="7.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="24" width="8.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="25" max="25" width="7.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="26" max="26" width="7.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="27" max="27" width="1.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="28" max="28" width="8.1796875" style="1" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="29" max="29" width="7.81640625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="30" max="30" width="8.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="31" max="31" width="7.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="32" max="32" width="7.1796875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="33" max="33" width="7.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="34" max="34" width="8.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="35" max="35" width="7.81640625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="36" max="36" width="8.1796875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="37" max="37" width="8.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="38" max="38" width="7.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="39" max="39" width="7.1796875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="40" max="40" width="8.1796875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="41" max="41" width="8.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="42" max="42" width="7.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="43" max="43" width="7.1796875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="44" max="44" width="8.1796875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="45" max="45" width="8.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="46" max="46" width="7.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="47" max="47" width="7.1796875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="48" max="48" width="4.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="49" max="49" width="8.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
     <col min="50" max="50" width="8" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="51" max="51" width="7.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="52" max="52" width="7.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="53" max="53" width="7.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="54" max="54" width="7.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="55" max="55" width="8.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="51" max="51" width="7.81640625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="52" max="52" width="7.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="53" max="53" width="7.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="54" max="54" width="7.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="55" max="55" width="8.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="56" max="56" width="9" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="57" max="57" width="8.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="58" max="58" width="7.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="59" max="59" width="7.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="60" max="60" width="7.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="61" max="61" width="8.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="62" max="62" width="7.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="63" max="63" width="7.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="64" max="64" width="7.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="65" max="65" width="8.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="66" max="66" width="7.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="67" max="67" width="7.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="68" max="68" width="7.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="69" max="69" width="1.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="57" max="57" width="8.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="58" max="58" width="7.81640625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="59" max="59" width="7.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="60" max="60" width="7.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="61" max="61" width="8.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="62" max="62" width="7.81640625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="63" max="63" width="7.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="64" max="64" width="7.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="65" max="65" width="8.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="66" max="66" width="7.81640625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="67" max="67" width="7.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="68" max="68" width="7.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="69" max="69" width="1.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="70" max="70" width="8" style="1" customWidth="1" collapsed="1"/>
-    <col min="71" max="71" width="7.28515625" style="1" customWidth="1"/>
-    <col min="72" max="72" width="9.42578125" style="1" customWidth="1"/>
-    <col min="73" max="73" width="7.28515625" style="1" customWidth="1"/>
-    <col min="74" max="74" width="7.140625" style="1" customWidth="1"/>
-    <col min="75" max="75" width="7.7109375" style="1" customWidth="1"/>
-    <col min="76" max="76" width="8.28515625" style="1" customWidth="1"/>
-    <col min="77" max="77" width="8.85546875" style="1" customWidth="1"/>
+    <col min="71" max="71" width="7.26953125" style="1" customWidth="1"/>
+    <col min="72" max="72" width="9.453125" style="1" customWidth="1"/>
+    <col min="73" max="73" width="7.26953125" style="1" customWidth="1"/>
+    <col min="74" max="74" width="7.1796875" style="1" customWidth="1"/>
+    <col min="75" max="75" width="7.7265625" style="1" customWidth="1"/>
+    <col min="76" max="76" width="8.26953125" style="1" customWidth="1"/>
+    <col min="77" max="77" width="8.81640625" style="1" customWidth="1"/>
     <col min="78" max="78" width="8" style="1" customWidth="1"/>
-    <col min="79" max="79" width="9.42578125" style="1" customWidth="1"/>
-    <col min="80" max="80" width="7.28515625" style="1" customWidth="1"/>
-    <col min="81" max="81" width="7.140625" style="1" customWidth="1"/>
+    <col min="79" max="79" width="9.453125" style="1" customWidth="1"/>
+    <col min="80" max="80" width="7.26953125" style="1" customWidth="1"/>
+    <col min="81" max="81" width="7.1796875" style="1" customWidth="1"/>
     <col min="82" max="82" width="8" style="1" customWidth="1"/>
-    <col min="83" max="83" width="9.42578125" style="1" customWidth="1"/>
-    <col min="84" max="84" width="7.28515625" style="1" customWidth="1"/>
-    <col min="85" max="85" width="7.140625" style="1" customWidth="1"/>
+    <col min="83" max="83" width="9.453125" style="1" customWidth="1"/>
+    <col min="84" max="84" width="7.26953125" style="1" customWidth="1"/>
+    <col min="85" max="85" width="7.1796875" style="1" customWidth="1"/>
     <col min="86" max="86" width="8" style="1" customWidth="1"/>
-    <col min="87" max="87" width="9.42578125" style="1" customWidth="1"/>
-    <col min="88" max="88" width="7.28515625" style="1" customWidth="1"/>
-    <col min="89" max="89" width="7.140625" style="1" customWidth="1"/>
-    <col min="90" max="90" width="1.7109375" style="1" customWidth="1" collapsed="1"/>
+    <col min="87" max="87" width="9.453125" style="1" customWidth="1"/>
+    <col min="88" max="88" width="7.26953125" style="1" customWidth="1"/>
+    <col min="89" max="89" width="7.1796875" style="1" customWidth="1"/>
+    <col min="90" max="90" width="1.7265625" style="1" customWidth="1" collapsed="1"/>
     <col min="91" max="91" width="9" style="1" customWidth="1" collapsed="1"/>
-    <col min="92" max="92" width="7.7109375" style="1" customWidth="1"/>
+    <col min="92" max="92" width="7.7265625" style="1" customWidth="1"/>
     <col min="93" max="93" width="9" style="1" customWidth="1"/>
-    <col min="94" max="95" width="7.28515625" style="1" customWidth="1"/>
-    <col min="96" max="97" width="8.7109375" style="1" customWidth="1"/>
+    <col min="94" max="95" width="7.26953125" style="1" customWidth="1"/>
+    <col min="96" max="97" width="8.7265625" style="1" customWidth="1"/>
     <col min="98" max="98" width="8" style="1" customWidth="1"/>
-    <col min="99" max="99" width="7.140625" style="1" customWidth="1"/>
-    <col min="100" max="102" width="9.28515625" style="1" customWidth="1"/>
-    <col min="103" max="103" width="9.5703125" style="1" customWidth="1"/>
-    <col min="104" max="16384" width="9.28515625" style="1"/>
+    <col min="99" max="99" width="7.1796875" style="1" customWidth="1"/>
+    <col min="100" max="102" width="9.26953125" style="1" customWidth="1"/>
+    <col min="103" max="103" width="9.54296875" style="1" customWidth="1"/>
+    <col min="104" max="16384" width="9.26953125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:99" ht="4.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:99" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:99" ht="4.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:99" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="152"/>
     </row>
-    <row r="3" spans="2:99" ht="15" x14ac:dyDescent="0.2">
-      <c r="E3" s="190" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="188" t="s">
+    <row r="3" spans="2:99" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="E3" s="203" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="196" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="197" t="s">
+      <c r="G3" s="201" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="193"/>
-      <c r="I3" s="193"/>
-      <c r="J3" s="193"/>
-      <c r="K3" s="193"/>
-      <c r="L3" s="193"/>
-      <c r="M3" s="193"/>
-      <c r="N3" s="194"/>
-      <c r="O3" s="195" t="s">
+      <c r="H3" s="199"/>
+      <c r="I3" s="199"/>
+      <c r="J3" s="199"/>
+      <c r="K3" s="199"/>
+      <c r="L3" s="199"/>
+      <c r="M3" s="199"/>
+      <c r="N3" s="200"/>
+      <c r="O3" s="188" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="196"/>
-      <c r="Q3" s="196"/>
-      <c r="R3" s="196"/>
-      <c r="S3" s="195" t="s">
+      <c r="P3" s="189"/>
+      <c r="Q3" s="189"/>
+      <c r="R3" s="189"/>
+      <c r="S3" s="188" t="s">
         <v>24</v>
       </c>
-      <c r="T3" s="196"/>
-      <c r="U3" s="196"/>
-      <c r="V3" s="196"/>
-      <c r="W3" s="195" t="s">
+      <c r="T3" s="189"/>
+      <c r="U3" s="189"/>
+      <c r="V3" s="189"/>
+      <c r="W3" s="188" t="s">
         <v>25</v>
       </c>
-      <c r="X3" s="196"/>
-      <c r="Y3" s="196"/>
-      <c r="Z3" s="196"/>
-      <c r="AB3" s="192" t="s">
+      <c r="X3" s="189"/>
+      <c r="Y3" s="189"/>
+      <c r="Z3" s="189"/>
+      <c r="AB3" s="198" t="s">
         <v>30</v>
       </c>
-      <c r="AC3" s="193"/>
-      <c r="AD3" s="193"/>
-      <c r="AE3" s="193"/>
-      <c r="AF3" s="193"/>
-      <c r="AG3" s="193"/>
-      <c r="AH3" s="193"/>
-      <c r="AI3" s="198"/>
-      <c r="AJ3" s="195" t="s">
+      <c r="AC3" s="199"/>
+      <c r="AD3" s="199"/>
+      <c r="AE3" s="199"/>
+      <c r="AF3" s="199"/>
+      <c r="AG3" s="199"/>
+      <c r="AH3" s="199"/>
+      <c r="AI3" s="202"/>
+      <c r="AJ3" s="188" t="s">
         <v>27</v>
       </c>
-      <c r="AK3" s="196"/>
-      <c r="AL3" s="196"/>
-      <c r="AM3" s="196"/>
-      <c r="AN3" s="195" t="s">
+      <c r="AK3" s="189"/>
+      <c r="AL3" s="189"/>
+      <c r="AM3" s="189"/>
+      <c r="AN3" s="188" t="s">
         <v>28</v>
       </c>
-      <c r="AO3" s="196"/>
-      <c r="AP3" s="196"/>
-      <c r="AQ3" s="196"/>
-      <c r="AR3" s="195" t="s">
+      <c r="AO3" s="189"/>
+      <c r="AP3" s="189"/>
+      <c r="AQ3" s="189"/>
+      <c r="AR3" s="188" t="s">
         <v>29</v>
       </c>
-      <c r="AS3" s="196"/>
-      <c r="AT3" s="196"/>
-      <c r="AU3" s="196"/>
-      <c r="AW3" s="192" t="s">
+      <c r="AS3" s="189"/>
+      <c r="AT3" s="189"/>
+      <c r="AU3" s="189"/>
+      <c r="AW3" s="198" t="s">
         <v>66</v>
       </c>
-      <c r="AX3" s="193"/>
-      <c r="AY3" s="193"/>
-      <c r="AZ3" s="193"/>
-      <c r="BA3" s="193"/>
-      <c r="BB3" s="193"/>
-      <c r="BC3" s="193"/>
-      <c r="BD3" s="194"/>
-      <c r="BE3" s="195" t="s">
+      <c r="AX3" s="199"/>
+      <c r="AY3" s="199"/>
+      <c r="AZ3" s="199"/>
+      <c r="BA3" s="199"/>
+      <c r="BB3" s="199"/>
+      <c r="BC3" s="199"/>
+      <c r="BD3" s="200"/>
+      <c r="BE3" s="188" t="s">
         <v>67</v>
       </c>
-      <c r="BF3" s="196"/>
-      <c r="BG3" s="196"/>
-      <c r="BH3" s="196"/>
-      <c r="BI3" s="195" t="s">
+      <c r="BF3" s="189"/>
+      <c r="BG3" s="189"/>
+      <c r="BH3" s="189"/>
+      <c r="BI3" s="188" t="s">
         <v>68</v>
       </c>
-      <c r="BJ3" s="196"/>
-      <c r="BK3" s="196"/>
-      <c r="BL3" s="196"/>
-      <c r="BM3" s="195" t="s">
+      <c r="BJ3" s="189"/>
+      <c r="BK3" s="189"/>
+      <c r="BL3" s="189"/>
+      <c r="BM3" s="188" t="s">
         <v>72</v>
       </c>
-      <c r="BN3" s="196"/>
-      <c r="BO3" s="196"/>
-      <c r="BP3" s="196"/>
-      <c r="BR3" s="192" t="s">
+      <c r="BN3" s="189"/>
+      <c r="BO3" s="189"/>
+      <c r="BP3" s="189"/>
+      <c r="BR3" s="198" t="s">
         <v>73</v>
       </c>
-      <c r="BS3" s="193"/>
-      <c r="BT3" s="193"/>
-      <c r="BU3" s="193"/>
-      <c r="BV3" s="193"/>
-      <c r="BW3" s="193"/>
-      <c r="BX3" s="193"/>
-      <c r="BY3" s="194"/>
+      <c r="BS3" s="199"/>
+      <c r="BT3" s="199"/>
+      <c r="BU3" s="199"/>
+      <c r="BV3" s="199"/>
+      <c r="BW3" s="199"/>
+      <c r="BX3" s="199"/>
+      <c r="BY3" s="200"/>
       <c r="BZ3" s="73" t="s">
         <v>69</v>
       </c>
       <c r="CA3" s="74"/>
       <c r="CB3" s="74"/>
       <c r="CC3" s="74"/>
-      <c r="CD3" s="195" t="s">
+      <c r="CD3" s="188" t="s">
         <v>70</v>
       </c>
-      <c r="CE3" s="196"/>
-      <c r="CF3" s="196"/>
-      <c r="CG3" s="196"/>
-      <c r="CH3" s="195" t="s">
+      <c r="CE3" s="189"/>
+      <c r="CF3" s="189"/>
+      <c r="CG3" s="189"/>
+      <c r="CH3" s="188" t="s">
         <v>71</v>
       </c>
-      <c r="CI3" s="196"/>
-      <c r="CJ3" s="196"/>
-      <c r="CK3" s="196"/>
-      <c r="CM3" s="192" t="s">
+      <c r="CI3" s="189"/>
+      <c r="CJ3" s="189"/>
+      <c r="CK3" s="189"/>
+      <c r="CM3" s="198" t="s">
         <v>783</v>
       </c>
-      <c r="CN3" s="193"/>
-      <c r="CO3" s="193"/>
-      <c r="CP3" s="193"/>
-      <c r="CQ3" s="193"/>
-      <c r="CR3" s="193"/>
-      <c r="CS3" s="193"/>
-      <c r="CT3" s="194"/>
-    </row>
-    <row r="4" spans="2:99" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="E4" s="191"/>
-      <c r="F4" s="189"/>
+      <c r="CN3" s="199"/>
+      <c r="CO3" s="199"/>
+      <c r="CP3" s="199"/>
+      <c r="CQ3" s="199"/>
+      <c r="CR3" s="199"/>
+      <c r="CS3" s="199"/>
+      <c r="CT3" s="200"/>
+    </row>
+    <row r="4" spans="2:99" ht="26" x14ac:dyDescent="0.3">
+      <c r="E4" s="204"/>
+      <c r="F4" s="197"/>
       <c r="G4" s="148" t="s">
         <v>169</v>
       </c>
@@ -21008,7 +20525,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="2:99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:99" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C5" s="9"/>
       <c r="E5" s="163" t="s">
         <v>402</v>
@@ -21373,7 +20890,7 @@
       </c>
       <c r="CU5" s="21"/>
     </row>
-    <row r="6" spans="2:99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:99" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C6" s="9"/>
       <c r="E6" s="163" t="s">
         <v>97</v>
@@ -21738,7 +21255,7 @@
       </c>
       <c r="CU6" s="21"/>
     </row>
-    <row r="7" spans="2:99" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:99" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="E7" s="50" t="s">
@@ -22104,14 +21621,14 @@
       </c>
       <c r="CU7" s="21"/>
     </row>
-    <row r="8" spans="2:99" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:99" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3"/>
       <c r="C8" s="2"/>
       <c r="E8" s="135" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="9" spans="2:99" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:99" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B9" s="3"/>
       <c r="C9" s="2"/>
       <c r="Q9" s="11"/>
@@ -22139,140 +21656,140 @@
       <c r="CJ9" s="11"/>
       <c r="CK9" s="11"/>
     </row>
-    <row r="10" spans="2:99" ht="15" x14ac:dyDescent="0.2">
-      <c r="B10" s="202" t="s">
+    <row r="10" spans="2:99" ht="14.5" x14ac:dyDescent="0.3">
+      <c r="B10" s="193" t="s">
         <v>784</v>
       </c>
-      <c r="C10" s="203"/>
-      <c r="D10" s="203"/>
-      <c r="E10" s="204"/>
-      <c r="F10" s="188" t="s">
+      <c r="C10" s="194"/>
+      <c r="D10" s="194"/>
+      <c r="E10" s="195"/>
+      <c r="F10" s="196" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="192" t="s">
+      <c r="G10" s="198" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="193"/>
-      <c r="I10" s="193"/>
-      <c r="J10" s="193"/>
-      <c r="K10" s="193"/>
-      <c r="L10" s="193"/>
-      <c r="M10" s="193"/>
-      <c r="N10" s="194"/>
-      <c r="O10" s="195" t="s">
+      <c r="H10" s="199"/>
+      <c r="I10" s="199"/>
+      <c r="J10" s="199"/>
+      <c r="K10" s="199"/>
+      <c r="L10" s="199"/>
+      <c r="M10" s="199"/>
+      <c r="N10" s="200"/>
+      <c r="O10" s="188" t="s">
         <v>23</v>
       </c>
-      <c r="P10" s="196"/>
-      <c r="Q10" s="196"/>
-      <c r="R10" s="196"/>
-      <c r="S10" s="195" t="s">
+      <c r="P10" s="189"/>
+      <c r="Q10" s="189"/>
+      <c r="R10" s="189"/>
+      <c r="S10" s="188" t="s">
         <v>24</v>
       </c>
-      <c r="T10" s="196"/>
-      <c r="U10" s="196"/>
-      <c r="V10" s="196"/>
-      <c r="W10" s="195" t="s">
+      <c r="T10" s="189"/>
+      <c r="U10" s="189"/>
+      <c r="V10" s="189"/>
+      <c r="W10" s="188" t="s">
         <v>25</v>
       </c>
-      <c r="X10" s="196"/>
-      <c r="Y10" s="196"/>
-      <c r="Z10" s="196"/>
-      <c r="AB10" s="192" t="s">
+      <c r="X10" s="189"/>
+      <c r="Y10" s="189"/>
+      <c r="Z10" s="189"/>
+      <c r="AB10" s="198" t="s">
         <v>30</v>
       </c>
-      <c r="AC10" s="193"/>
-      <c r="AD10" s="193"/>
-      <c r="AE10" s="193"/>
-      <c r="AF10" s="193"/>
-      <c r="AG10" s="193"/>
-      <c r="AH10" s="193"/>
-      <c r="AI10" s="198"/>
-      <c r="AJ10" s="195" t="s">
+      <c r="AC10" s="199"/>
+      <c r="AD10" s="199"/>
+      <c r="AE10" s="199"/>
+      <c r="AF10" s="199"/>
+      <c r="AG10" s="199"/>
+      <c r="AH10" s="199"/>
+      <c r="AI10" s="202"/>
+      <c r="AJ10" s="188" t="s">
         <v>27</v>
       </c>
-      <c r="AK10" s="196"/>
-      <c r="AL10" s="196"/>
-      <c r="AM10" s="196"/>
-      <c r="AN10" s="195" t="s">
+      <c r="AK10" s="189"/>
+      <c r="AL10" s="189"/>
+      <c r="AM10" s="189"/>
+      <c r="AN10" s="188" t="s">
         <v>28</v>
       </c>
-      <c r="AO10" s="196"/>
-      <c r="AP10" s="196"/>
-      <c r="AQ10" s="196"/>
-      <c r="AR10" s="195" t="s">
+      <c r="AO10" s="189"/>
+      <c r="AP10" s="189"/>
+      <c r="AQ10" s="189"/>
+      <c r="AR10" s="188" t="s">
         <v>29</v>
       </c>
-      <c r="AS10" s="196"/>
-      <c r="AT10" s="196"/>
-      <c r="AU10" s="196"/>
-      <c r="AW10" s="192" t="s">
+      <c r="AS10" s="189"/>
+      <c r="AT10" s="189"/>
+      <c r="AU10" s="189"/>
+      <c r="AW10" s="198" t="s">
         <v>66</v>
       </c>
-      <c r="AX10" s="193"/>
-      <c r="AY10" s="193"/>
-      <c r="AZ10" s="193"/>
-      <c r="BA10" s="193"/>
-      <c r="BB10" s="193"/>
-      <c r="BC10" s="193"/>
-      <c r="BD10" s="194"/>
-      <c r="BE10" s="195" t="s">
+      <c r="AX10" s="199"/>
+      <c r="AY10" s="199"/>
+      <c r="AZ10" s="199"/>
+      <c r="BA10" s="199"/>
+      <c r="BB10" s="199"/>
+      <c r="BC10" s="199"/>
+      <c r="BD10" s="200"/>
+      <c r="BE10" s="188" t="s">
         <v>67</v>
       </c>
-      <c r="BF10" s="196"/>
-      <c r="BG10" s="196"/>
-      <c r="BH10" s="196"/>
-      <c r="BI10" s="195" t="s">
+      <c r="BF10" s="189"/>
+      <c r="BG10" s="189"/>
+      <c r="BH10" s="189"/>
+      <c r="BI10" s="188" t="s">
         <v>68</v>
       </c>
-      <c r="BJ10" s="196"/>
-      <c r="BK10" s="196"/>
-      <c r="BL10" s="196"/>
-      <c r="BM10" s="195" t="s">
+      <c r="BJ10" s="189"/>
+      <c r="BK10" s="189"/>
+      <c r="BL10" s="189"/>
+      <c r="BM10" s="188" t="s">
         <v>72</v>
       </c>
-      <c r="BN10" s="196"/>
-      <c r="BO10" s="196"/>
-      <c r="BP10" s="196"/>
-      <c r="BR10" s="192" t="s">
+      <c r="BN10" s="189"/>
+      <c r="BO10" s="189"/>
+      <c r="BP10" s="189"/>
+      <c r="BR10" s="198" t="s">
         <v>73</v>
       </c>
-      <c r="BS10" s="193"/>
-      <c r="BT10" s="193"/>
-      <c r="BU10" s="193"/>
-      <c r="BV10" s="193"/>
-      <c r="BW10" s="193"/>
-      <c r="BX10" s="193"/>
-      <c r="BY10" s="194"/>
+      <c r="BS10" s="199"/>
+      <c r="BT10" s="199"/>
+      <c r="BU10" s="199"/>
+      <c r="BV10" s="199"/>
+      <c r="BW10" s="199"/>
+      <c r="BX10" s="199"/>
+      <c r="BY10" s="200"/>
       <c r="BZ10" s="73" t="s">
         <v>69</v>
       </c>
       <c r="CA10" s="74"/>
       <c r="CB10" s="74"/>
       <c r="CC10" s="74"/>
-      <c r="CD10" s="195" t="s">
+      <c r="CD10" s="188" t="s">
         <v>70</v>
       </c>
-      <c r="CE10" s="196"/>
-      <c r="CF10" s="196"/>
-      <c r="CG10" s="196"/>
-      <c r="CH10" s="195" t="s">
+      <c r="CE10" s="189"/>
+      <c r="CF10" s="189"/>
+      <c r="CG10" s="189"/>
+      <c r="CH10" s="188" t="s">
         <v>71</v>
       </c>
-      <c r="CI10" s="196"/>
-      <c r="CJ10" s="196"/>
-      <c r="CK10" s="196"/>
-      <c r="CM10" s="192" t="s">
+      <c r="CI10" s="189"/>
+      <c r="CJ10" s="189"/>
+      <c r="CK10" s="189"/>
+      <c r="CM10" s="198" t="s">
         <v>783</v>
       </c>
-      <c r="CN10" s="193"/>
-      <c r="CO10" s="193"/>
-      <c r="CP10" s="193"/>
-      <c r="CQ10" s="193"/>
-      <c r="CR10" s="193"/>
-      <c r="CS10" s="193"/>
-      <c r="CT10" s="194"/>
-    </row>
-    <row r="11" spans="2:99" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="CN10" s="199"/>
+      <c r="CO10" s="199"/>
+      <c r="CP10" s="199"/>
+      <c r="CQ10" s="199"/>
+      <c r="CR10" s="199"/>
+      <c r="CS10" s="199"/>
+      <c r="CT10" s="200"/>
+    </row>
+    <row r="11" spans="2:99" ht="26" x14ac:dyDescent="0.3">
       <c r="B11" s="52" t="s">
         <v>0</v>
       </c>
@@ -22285,7 +21802,7 @@
       <c r="E11" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="189"/>
+      <c r="F11" s="197"/>
       <c r="G11" s="38" t="s">
         <v>169</v>
       </c>
@@ -22553,7 +22070,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="2:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:99" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="163" t="s">
         <v>402</v>
       </c>
@@ -22926,7 +22443,7 @@
       </c>
       <c r="CU12" s="21"/>
     </row>
-    <row r="13" spans="2:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:99" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="163" t="s">
         <v>402</v>
       </c>
@@ -23299,7 +22816,7 @@
       </c>
       <c r="CU13" s="21"/>
     </row>
-    <row r="14" spans="2:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:99" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="163" t="s">
         <v>402</v>
       </c>
@@ -23672,7 +23189,7 @@
       </c>
       <c r="CU14" s="21"/>
     </row>
-    <row r="15" spans="2:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:99" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="163" t="s">
         <v>402</v>
       </c>
@@ -24045,7 +23562,7 @@
       </c>
       <c r="CU15" s="21"/>
     </row>
-    <row r="16" spans="2:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:99" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="163" t="s">
         <v>97</v>
       </c>
@@ -24418,7 +23935,7 @@
       </c>
       <c r="CU16" s="21"/>
     </row>
-    <row r="17" spans="2:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:99" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="163" t="s">
         <v>97</v>
       </c>
@@ -24791,7 +24308,7 @@
       </c>
       <c r="CU17" s="21"/>
     </row>
-    <row r="18" spans="2:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:99" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="163" t="s">
         <v>97</v>
       </c>
@@ -25164,7 +24681,7 @@
       </c>
       <c r="CU18" s="21"/>
     </row>
-    <row r="19" spans="2:99" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:99" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="163" t="s">
         <v>97</v>
       </c>
@@ -25537,13 +25054,13 @@
       </c>
       <c r="CU19" s="21"/>
     </row>
-    <row r="20" spans="2:99" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="199" t="s">
+    <row r="20" spans="2:99" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="190" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="200"/>
-      <c r="D20" s="200"/>
-      <c r="E20" s="201"/>
+      <c r="C20" s="191"/>
+      <c r="D20" s="191"/>
+      <c r="E20" s="192"/>
       <c r="F20" s="115">
         <f>SUM(F12:F19)</f>
         <v>14</v>
@@ -25902,189 +25419,200 @@
       </c>
       <c r="CU20" s="21"/>
     </row>
-    <row r="21" spans="2:99" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:99" x14ac:dyDescent="0.3">
       <c r="D21" s="12"/>
       <c r="E21" s="13"/>
     </row>
-    <row r="9526" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="9526" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D9526" s="4"/>
       <c r="E9526" s="4"/>
     </row>
-    <row r="10161" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="10161" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D10161" s="4"/>
       <c r="E10161" s="4"/>
     </row>
-    <row r="10163" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="10163" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D10163" s="4"/>
       <c r="E10163" s="4"/>
     </row>
-    <row r="12413" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="12413" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D12413" s="4"/>
       <c r="E12413" s="4"/>
     </row>
-    <row r="12417" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="12417" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D12417" s="4"/>
       <c r="E12417" s="4"/>
     </row>
-    <row r="13531" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="13531" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D13531" s="4"/>
       <c r="E13531" s="4"/>
     </row>
-    <row r="13535" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="13535" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D13535" s="4"/>
       <c r="E13535" s="4"/>
     </row>
-    <row r="13905" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="13905" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D13905" s="4"/>
       <c r="E13905" s="4"/>
     </row>
-    <row r="16902" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="16902" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D16902" s="4"/>
       <c r="E16902" s="4"/>
     </row>
-    <row r="16911" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="16911" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D16911" s="4"/>
       <c r="E16911" s="4"/>
     </row>
-    <row r="17232" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="17232" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D17232" s="4"/>
       <c r="E17232" s="4"/>
     </row>
-    <row r="17256" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="17256" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D17256" s="4"/>
       <c r="E17256" s="4"/>
     </row>
-    <row r="17261" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="17261" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D17261" s="4"/>
       <c r="E17261" s="4"/>
     </row>
-    <row r="17674" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="17674" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D17674" s="4"/>
       <c r="E17674" s="4"/>
     </row>
-    <row r="17690" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="17690" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D17690" s="4"/>
       <c r="E17690" s="4"/>
     </row>
-    <row r="19342" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="19342" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D19342" s="4"/>
       <c r="E19342" s="4"/>
     </row>
-    <row r="21113" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="21113" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D21113" s="4"/>
       <c r="E21113" s="4"/>
     </row>
-    <row r="21114" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="21114" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D21114" s="4"/>
       <c r="E21114" s="4"/>
     </row>
-    <row r="21115" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="21115" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D21115" s="4"/>
       <c r="E21115" s="4"/>
     </row>
-    <row r="21116" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="21116" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D21116" s="4"/>
       <c r="E21116" s="4"/>
     </row>
-    <row r="21118" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="21118" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D21118" s="4"/>
       <c r="E21118" s="4"/>
     </row>
-    <row r="21209" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="21209" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D21209" s="4"/>
       <c r="E21209" s="4"/>
     </row>
-    <row r="21211" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="21211" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D21211" s="4"/>
       <c r="E21211" s="4"/>
     </row>
-    <row r="21212" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="21212" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D21212" s="4"/>
       <c r="E21212" s="4"/>
     </row>
-    <row r="21213" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="21213" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D21213" s="4"/>
       <c r="E21213" s="4"/>
     </row>
-    <row r="21214" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="21214" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D21214" s="4"/>
       <c r="E21214" s="4"/>
     </row>
-    <row r="21655" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="21655" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D21655" s="4"/>
       <c r="E21655" s="4"/>
     </row>
-    <row r="21693" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="21693" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D21693" s="4"/>
       <c r="E21693" s="4"/>
     </row>
-    <row r="21700" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="21700" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D21700" s="4"/>
       <c r="E21700" s="4"/>
     </row>
-    <row r="22388" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="22388" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D22388" s="4"/>
       <c r="E22388" s="4"/>
     </row>
-    <row r="22396" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="22396" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D22396" s="4"/>
       <c r="E22396" s="4"/>
     </row>
-    <row r="22397" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="22397" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D22397" s="4"/>
       <c r="E22397" s="4"/>
     </row>
-    <row r="22398" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="22398" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D22398" s="4"/>
       <c r="E22398" s="4"/>
     </row>
-    <row r="22507" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="22507" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D22507" s="4"/>
       <c r="E22507" s="4"/>
     </row>
-    <row r="22691" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="22691" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D22691" s="4"/>
       <c r="E22691" s="4"/>
     </row>
-    <row r="23050" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="23050" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D23050" s="4"/>
       <c r="E23050" s="4"/>
     </row>
-    <row r="23060" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="23060" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D23060" s="4"/>
       <c r="E23060" s="4"/>
     </row>
-    <row r="23554" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="23554" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D23554" s="4"/>
       <c r="E23554" s="4"/>
     </row>
-    <row r="23556" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="23556" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D23556" s="4"/>
       <c r="E23556" s="4"/>
     </row>
-    <row r="23557" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="23557" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D23557" s="4"/>
       <c r="E23557" s="4"/>
     </row>
-    <row r="23558" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="23558" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D23558" s="4"/>
       <c r="E23558" s="4"/>
     </row>
-    <row r="23942" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="23942" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D23942" s="4"/>
       <c r="E23942" s="4"/>
     </row>
-    <row r="23944" spans="4:5" x14ac:dyDescent="0.2">
+    <row r="23944" spans="4:5" x14ac:dyDescent="0.3">
       <c r="D23944" s="4"/>
       <c r="E23944" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="AN10:AQ10"/>
-    <mergeCell ref="AR10:AU10"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="CM3:CT3"/>
+    <mergeCell ref="CM10:CT10"/>
+    <mergeCell ref="CD10:CG10"/>
+    <mergeCell ref="CH10:CK10"/>
+    <mergeCell ref="BR3:BY3"/>
+    <mergeCell ref="BR10:BY10"/>
+    <mergeCell ref="CD3:CG3"/>
+    <mergeCell ref="CH3:CK3"/>
+    <mergeCell ref="BI3:BL3"/>
+    <mergeCell ref="BM3:BP3"/>
+    <mergeCell ref="BE3:BH3"/>
+    <mergeCell ref="BE10:BH10"/>
+    <mergeCell ref="AW10:BD10"/>
+    <mergeCell ref="BI10:BL10"/>
     <mergeCell ref="BM10:BP10"/>
     <mergeCell ref="AW3:BD3"/>
     <mergeCell ref="G3:N3"/>
@@ -26101,22 +25629,11 @@
     <mergeCell ref="O3:R3"/>
     <mergeCell ref="S3:V3"/>
     <mergeCell ref="W3:Z3"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="CM3:CT3"/>
-    <mergeCell ref="CM10:CT10"/>
-    <mergeCell ref="CD10:CG10"/>
-    <mergeCell ref="CH10:CK10"/>
-    <mergeCell ref="BR3:BY3"/>
-    <mergeCell ref="BR10:BY10"/>
-    <mergeCell ref="CD3:CG3"/>
-    <mergeCell ref="CH3:CK3"/>
-    <mergeCell ref="BI3:BL3"/>
-    <mergeCell ref="BM3:BP3"/>
-    <mergeCell ref="BE3:BH3"/>
-    <mergeCell ref="BE10:BH10"/>
-    <mergeCell ref="AW10:BD10"/>
-    <mergeCell ref="BI10:BL10"/>
+    <mergeCell ref="AN10:AQ10"/>
+    <mergeCell ref="AR10:AU10"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="F10:F11"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="L5:L7 AG5:AG7 BB5:BB7 BW5:BW7 CR5:CR7 L12:L20 AG12:AG20 BB12:BB20 BW12:BW20 CR12:CR20">
@@ -26397,114 +25914,114 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:CX39"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.28515625" customWidth="1"/>
-    <col min="2" max="2" width="0.28515625" customWidth="1"/>
-    <col min="3" max="3" width="16.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" style="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.26953125" customWidth="1"/>
+    <col min="2" max="2" width="0.26953125" customWidth="1"/>
+    <col min="3" max="3" width="16.54296875" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.54296875" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.453125" style="21" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23" style="25" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="11.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="9.140625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="8.5703125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="7.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="8.140625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="8.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="14" width="9.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="8.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="16" max="16" width="9.140625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="17" width="7.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="7.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="8.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="20" max="20" width="9.140625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="8.5703125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="22" max="22" width="7.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="23" max="23" width="8.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="24" max="24" width="9.140625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="25" max="25" width="8.5703125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="26" max="26" width="7.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="27" max="27" width="2.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="28" max="28" width="8.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="29" max="29" width="7.5703125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="30" max="30" width="8.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="31" max="31" width="7.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="32" max="32" width="6.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="33" max="33" width="7.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="34" max="34" width="8.5703125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="35" max="35" width="9.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="36" max="36" width="7.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="37" max="37" width="8.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="38" max="38" width="7.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="39" max="39" width="6.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="40" max="40" width="7.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="41" max="41" width="8.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="42" max="42" width="7.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="43" max="43" width="6.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="44" max="44" width="7.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="45" max="45" width="8.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="46" max="46" width="7.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="47" max="47" width="6.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="48" max="48" width="2.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="49" max="49" width="7.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="50" max="50" width="7.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="51" max="51" width="8.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="52" max="52" width="7.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="53" max="53" width="6.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="8.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="11.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="9.1796875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="8.54296875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="7.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="8.1796875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="8.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="9.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="8.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="9.1796875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="17" width="7.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="7.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="8.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="20" max="20" width="9.1796875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="8.54296875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="22" width="7.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="23" width="8.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="24" width="9.1796875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="25" max="25" width="8.54296875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="26" max="26" width="7.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="27" max="27" width="2.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="28" max="28" width="8.81640625" style="1" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="29" max="29" width="7.54296875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="30" max="30" width="8.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="31" max="31" width="7.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="32" max="32" width="6.81640625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="33" max="33" width="7.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="34" max="34" width="8.54296875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="35" max="35" width="9.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="36" max="36" width="7.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="37" max="37" width="8.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="38" max="38" width="7.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="39" max="39" width="6.81640625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="40" max="40" width="7.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="41" max="41" width="8.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="42" max="42" width="7.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="43" max="43" width="6.81640625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="44" max="44" width="7.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="45" max="45" width="8.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="46" max="46" width="7.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="47" max="47" width="6.81640625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="48" max="48" width="2.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="49" max="49" width="7.81640625" style="1" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="50" max="50" width="7.81640625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="51" max="51" width="8.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="52" max="52" width="7.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="53" max="53" width="6.81640625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="54" max="54" width="8" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="55" max="55" width="8.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="56" max="56" width="9.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="57" max="57" width="7.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="58" max="58" width="8.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="59" max="59" width="7.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="60" max="60" width="6.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="61" max="61" width="7.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="62" max="62" width="8.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="63" max="63" width="7.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="64" max="64" width="6.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="65" max="65" width="7.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="66" max="66" width="8.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="67" max="67" width="7.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="68" max="68" width="6.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="69" max="69" width="2.42578125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="70" max="70" width="9.42578125" style="1" customWidth="1" collapsed="1"/>
-    <col min="71" max="71" width="8.28515625" style="1" customWidth="1"/>
-    <col min="72" max="72" width="8.7109375" style="1" customWidth="1"/>
-    <col min="73" max="73" width="8.5703125" style="1" customWidth="1"/>
+    <col min="55" max="55" width="8.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="56" max="56" width="9.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="57" max="57" width="7.81640625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="58" max="58" width="8.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="59" max="59" width="7.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="60" max="60" width="6.81640625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="61" max="61" width="7.81640625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="62" max="62" width="8.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="63" max="63" width="7.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="64" max="64" width="6.81640625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="65" max="65" width="7.81640625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="66" max="66" width="8.453125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="67" max="67" width="7.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="68" max="68" width="6.81640625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="69" max="69" width="2.453125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="70" max="70" width="9.453125" style="1" customWidth="1" collapsed="1"/>
+    <col min="71" max="71" width="8.26953125" style="1" customWidth="1"/>
+    <col min="72" max="72" width="8.7265625" style="1" customWidth="1"/>
+    <col min="73" max="73" width="8.54296875" style="1" customWidth="1"/>
     <col min="74" max="74" width="8" style="1" customWidth="1"/>
-    <col min="75" max="75" width="8.28515625" style="1" customWidth="1"/>
-    <col min="76" max="76" width="8.140625" style="1" customWidth="1"/>
-    <col min="77" max="77" width="9.7109375" style="1" customWidth="1"/>
-    <col min="78" max="78" width="9.42578125" style="1" customWidth="1"/>
-    <col min="79" max="79" width="8.7109375" style="1" customWidth="1"/>
-    <col min="80" max="80" width="8.5703125" style="1" customWidth="1"/>
+    <col min="75" max="75" width="8.26953125" style="1" customWidth="1"/>
+    <col min="76" max="76" width="8.1796875" style="1" customWidth="1"/>
+    <col min="77" max="77" width="9.7265625" style="1" customWidth="1"/>
+    <col min="78" max="78" width="9.453125" style="1" customWidth="1"/>
+    <col min="79" max="79" width="8.7265625" style="1" customWidth="1"/>
+    <col min="80" max="80" width="8.54296875" style="1" customWidth="1"/>
     <col min="81" max="81" width="8" style="1" customWidth="1"/>
-    <col min="82" max="82" width="9.42578125" style="1" customWidth="1"/>
-    <col min="83" max="83" width="8.7109375" style="1" customWidth="1"/>
-    <col min="84" max="84" width="8.5703125" style="1" customWidth="1"/>
+    <col min="82" max="82" width="9.453125" style="1" customWidth="1"/>
+    <col min="83" max="83" width="8.7265625" style="1" customWidth="1"/>
+    <col min="84" max="84" width="8.54296875" style="1" customWidth="1"/>
     <col min="85" max="85" width="8" style="1" customWidth="1"/>
-    <col min="86" max="86" width="9.42578125" style="1" customWidth="1"/>
-    <col min="87" max="87" width="8.7109375" style="1" customWidth="1"/>
-    <col min="88" max="88" width="8.5703125" style="1" customWidth="1"/>
+    <col min="86" max="86" width="9.453125" style="1" customWidth="1"/>
+    <col min="87" max="87" width="8.7265625" style="1" customWidth="1"/>
+    <col min="88" max="88" width="8.54296875" style="1" customWidth="1"/>
     <col min="89" max="89" width="8" style="1" customWidth="1"/>
-    <col min="90" max="90" width="2.7109375" customWidth="1"/>
-    <col min="91" max="91" width="10.28515625" style="1" customWidth="1"/>
-    <col min="92" max="92" width="8.42578125" style="1" customWidth="1"/>
-    <col min="93" max="93" width="10.5703125" style="1" customWidth="1"/>
+    <col min="90" max="90" width="2.7265625" customWidth="1"/>
+    <col min="91" max="91" width="10.26953125" style="1" customWidth="1"/>
+    <col min="92" max="92" width="8.453125" style="1" customWidth="1"/>
+    <col min="93" max="93" width="10.54296875" style="1" customWidth="1"/>
     <col min="94" max="94" width="10" style="1" customWidth="1"/>
-    <col min="95" max="95" width="8.7109375" style="1" customWidth="1"/>
-    <col min="96" max="96" width="7.7109375" style="1" customWidth="1"/>
-    <col min="97" max="97" width="8.5703125" style="1" customWidth="1"/>
-    <col min="98" max="98" width="15.7109375" style="1" customWidth="1"/>
-    <col min="99" max="99" width="6.5703125" customWidth="1"/>
-    <col min="100" max="100" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="101" max="101" width="9.28515625" customWidth="1"/>
-    <col min="102" max="102" width="7.85546875" customWidth="1"/>
-    <col min="103" max="103" width="9.28515625" customWidth="1"/>
+    <col min="95" max="95" width="8.7265625" style="1" customWidth="1"/>
+    <col min="96" max="96" width="7.7265625" style="1" customWidth="1"/>
+    <col min="97" max="97" width="8.54296875" style="1" customWidth="1"/>
+    <col min="98" max="98" width="15.7265625" style="1" customWidth="1"/>
+    <col min="99" max="99" width="6.54296875" customWidth="1"/>
+    <col min="100" max="100" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="101" max="101" width="9.26953125" customWidth="1"/>
+    <col min="102" max="102" width="7.81640625" customWidth="1"/>
+    <col min="103" max="103" width="9.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:102" x14ac:dyDescent="0.35">
       <c r="C1" s="22"/>
       <c r="D1" s="19"/>
       <c r="E1" s="19"/>
@@ -26600,7 +26117,7 @@
       <c r="CS1" s="5"/>
       <c r="CT1" s="5"/>
     </row>
-    <row r="2" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:102" x14ac:dyDescent="0.35">
       <c r="C2" s="22"/>
       <c r="D2" s="19"/>
       <c r="E2" s="19"/>
@@ -26696,7 +26213,7 @@
       <c r="CS2" s="5"/>
       <c r="CT2" s="5"/>
     </row>
-    <row r="3" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:102" x14ac:dyDescent="0.35">
       <c r="C3" s="22"/>
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
@@ -26792,7 +26309,7 @@
       <c r="CS3" s="5"/>
       <c r="CT3" s="5"/>
     </row>
-    <row r="4" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:102" x14ac:dyDescent="0.35">
       <c r="C4" s="22"/>
       <c r="D4" s="19"/>
       <c r="E4" s="19"/>
@@ -26888,7 +26405,7 @@
       <c r="CS4" s="5"/>
       <c r="CT4" s="5"/>
     </row>
-    <row r="5" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B5" s="10"/>
       <c r="C5" s="22"/>
       <c r="D5" s="19"/>
@@ -26985,7 +26502,7 @@
       <c r="CS5" s="5"/>
       <c r="CT5" s="5"/>
     </row>
-    <row r="6" spans="2:102" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:102" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C6" s="22"/>
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
@@ -27081,7 +26598,7 @@
       <c r="CS6" s="5"/>
       <c r="CT6" s="5"/>
     </row>
-    <row r="7" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B7" s="10"/>
       <c r="C7" s="24"/>
       <c r="D7" s="19"/>
@@ -27442,7 +26959,7 @@
         <v>3561.6474337312729</v>
       </c>
     </row>
-    <row r="8" spans="2:102" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:102" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F8" s="26"/>
       <c r="G8" s="84" t="s">
         <v>22</v>
@@ -27569,7 +27086,7 @@
       <c r="CS8" s="85"/>
       <c r="CT8" s="86"/>
     </row>
-    <row r="9" spans="2:102" s="132" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:102" s="132" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C9" s="87" t="s">
         <v>0</v>
       </c>
@@ -27849,7 +27366,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B10" s="10"/>
       <c r="C10" s="53" t="s">
         <v>402</v>
@@ -28222,7 +27739,7 @@
       <c r="CW10" s="141"/>
       <c r="CX10" s="144"/>
     </row>
-    <row r="11" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B11" s="10"/>
       <c r="C11" s="53" t="s">
         <v>402</v>
@@ -28595,7 +28112,7 @@
       <c r="CW11" s="141"/>
       <c r="CX11" s="144"/>
     </row>
-    <row r="12" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B12" s="10"/>
       <c r="C12" s="53" t="s">
         <v>402</v>
@@ -28968,7 +28485,7 @@
       <c r="CW12" s="141"/>
       <c r="CX12" s="144"/>
     </row>
-    <row r="13" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B13" s="10"/>
       <c r="C13" s="53" t="s">
         <v>402</v>
@@ -29341,7 +28858,7 @@
       <c r="CW13" s="141"/>
       <c r="CX13" s="144"/>
     </row>
-    <row r="14" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B14" s="10"/>
       <c r="C14" s="53" t="s">
         <v>402</v>
@@ -29714,7 +29231,7 @@
       <c r="CW14" s="141"/>
       <c r="CX14" s="144"/>
     </row>
-    <row r="15" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B15" s="10"/>
       <c r="C15" s="53" t="s">
         <v>402</v>
@@ -30087,7 +29604,7 @@
       <c r="CW15" s="141"/>
       <c r="CX15" s="144"/>
     </row>
-    <row r="16" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B16" s="10"/>
       <c r="C16" s="53" t="s">
         <v>402</v>
@@ -30460,7 +29977,7 @@
       <c r="CW16" s="141"/>
       <c r="CX16" s="144"/>
     </row>
-    <row r="17" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B17" s="10"/>
       <c r="C17" s="53" t="s">
         <v>402</v>
@@ -30833,7 +30350,7 @@
       <c r="CW17" s="141"/>
       <c r="CX17" s="144"/>
     </row>
-    <row r="18" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B18" s="10"/>
       <c r="C18" s="53" t="s">
         <v>97</v>
@@ -31206,7 +30723,7 @@
       <c r="CW18" s="141"/>
       <c r="CX18" s="144"/>
     </row>
-    <row r="19" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B19" s="10"/>
       <c r="C19" s="53" t="s">
         <v>97</v>
@@ -31579,7 +31096,7 @@
       <c r="CW19" s="141"/>
       <c r="CX19" s="144"/>
     </row>
-    <row r="20" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B20" s="10"/>
       <c r="C20" s="53" t="s">
         <v>97</v>
@@ -31952,7 +31469,7 @@
       <c r="CW20" s="141"/>
       <c r="CX20" s="144"/>
     </row>
-    <row r="21" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B21" s="10"/>
       <c r="C21" s="53" t="s">
         <v>97</v>
@@ -32325,7 +31842,7 @@
       <c r="CW21" s="141"/>
       <c r="CX21" s="144"/>
     </row>
-    <row r="22" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B22" s="10"/>
       <c r="C22" s="53" t="s">
         <v>97</v>
@@ -32698,7 +32215,7 @@
       <c r="CW22" s="141"/>
       <c r="CX22" s="144"/>
     </row>
-    <row r="23" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B23" s="10"/>
       <c r="C23" s="53" t="s">
         <v>97</v>
@@ -33071,49 +32588,49 @@
       <c r="CW23" s="141"/>
       <c r="CX23" s="144"/>
     </row>
-    <row r="25" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B25" s="10"/>
     </row>
-    <row r="26" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B26" s="10"/>
     </row>
-    <row r="27" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B27" s="10"/>
     </row>
-    <row r="28" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B28" s="10"/>
     </row>
-    <row r="29" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B29" s="10"/>
     </row>
-    <row r="30" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B30" s="10"/>
     </row>
-    <row r="31" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B31" s="10"/>
     </row>
-    <row r="32" spans="2:102" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:102" x14ac:dyDescent="0.35">
       <c r="B32" s="10"/>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B33" s="10"/>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B34" s="10"/>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B35" s="10"/>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B36" s="10"/>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B37" s="10"/>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B38" s="10"/>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B39" s="10"/>
     </row>
   </sheetData>
@@ -33371,19 +32888,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26696A5A-3C96-4417-A445-09149A5CF12A}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.26953125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="162" t="s">
         <v>0</v>
       </c>
@@ -33409,7 +32926,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="163" t="s">
         <v>402</v>
       </c>
@@ -33435,7 +32952,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="163" t="s">
         <v>402</v>
       </c>
@@ -33461,7 +32978,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="163" t="s">
         <v>402</v>
       </c>
@@ -33487,7 +33004,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="163" t="s">
         <v>402</v>
       </c>
@@ -33513,7 +33030,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="163" t="s">
         <v>97</v>
       </c>
@@ -33539,7 +33056,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="163" t="s">
         <v>97</v>
       </c>
@@ -33565,7 +33082,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="163" t="s">
         <v>97</v>
       </c>
@@ -33591,7 +33108,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="163" t="s">
         <v>98</v>
       </c>
@@ -33617,7 +33134,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="E10" s="163" t="s">
         <v>99</v>
       </c>
@@ -33634,7 +33151,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="E11" s="163" t="s">
         <v>106</v>
       </c>
@@ -33651,7 +33168,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="E12" s="163" t="s">
         <v>110</v>
       </c>
@@ -33668,7 +33185,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="E13" s="163" t="s">
         <v>103</v>
       </c>
@@ -33685,7 +33202,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="E14" s="163" t="s">
         <v>108</v>
       </c>
@@ -33702,7 +33219,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="E15" s="163" t="s">
         <v>134</v>
       </c>
@@ -33727,66 +33244,66 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A385D0EF-BEB3-48FE-B5EB-2A3D5B006E56}">
   <dimension ref="B1:BX107"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.7265625" customWidth="1"/>
+    <col min="2" max="2" width="18.7265625" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.26953125" style="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11" style="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="21" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" style="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="39.7109375" style="25" customWidth="1"/>
-    <col min="8" max="8" width="16.85546875" style="25" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="12.5703125" style="25" customWidth="1"/>
+    <col min="5" max="5" width="10.7265625" style="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.7265625" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39.7265625" style="25" customWidth="1"/>
+    <col min="8" max="8" width="16.81640625" style="25" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="12.54296875" style="25" customWidth="1"/>
     <col min="10" max="11" width="8" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="9.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="8.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="9.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="8.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="14" max="14" width="8" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="17" width="7.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="17" width="7.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="18" max="18" width="8" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="22" width="7.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="23" max="24" width="7.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="25" max="25" width="7.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="26" max="26" width="0.7109375" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="19" max="22" width="7.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="24" width="7.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="25" max="25" width="7.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="26" max="26" width="0.7265625" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
     <col min="27" max="27" width="8" style="1" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
     <col min="28" max="28" width="8" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="29" max="29" width="8.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="30" max="30" width="9.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="29" max="29" width="8.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="30" max="30" width="9.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="31" max="31" width="8" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="32" max="34" width="7.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="32" max="34" width="7.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="35" max="35" width="8" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="36" max="39" width="7.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="40" max="41" width="7.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="42" max="42" width="7.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="43" max="43" width="0.7109375" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="36" max="39" width="7.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="40" max="41" width="7.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="42" max="42" width="7.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="43" max="43" width="0.7265625" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
     <col min="44" max="44" width="8" style="1" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
     <col min="45" max="45" width="8" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="46" max="46" width="9" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="47" max="47" width="9.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="47" max="47" width="9.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="48" max="48" width="8" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="49" max="51" width="7.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="49" max="51" width="7.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="52" max="52" width="8" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="53" max="54" width="7.5703125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="55" max="55" width="7.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="56" max="56" width="8.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="57" max="57" width="8.28515625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="53" max="54" width="7.54296875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="55" max="55" width="7.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="56" max="56" width="8.453125" style="1" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="57" max="57" width="8.26953125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="58" max="58" width="9" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="59" max="59" width="7.7109375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="60" max="60" width="1.28515625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="59" max="59" width="7.7265625" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="60" max="60" width="1.26953125" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="61" max="61" width="8" style="1" customWidth="1" collapsed="1"/>
     <col min="62" max="62" width="8" style="1" customWidth="1"/>
-    <col min="63" max="63" width="8.7109375" style="1" customWidth="1"/>
+    <col min="63" max="63" width="8.7265625" style="1" customWidth="1"/>
     <col min="64" max="65" width="8" style="1" customWidth="1"/>
-    <col min="66" max="66" width="7.7109375" style="1" customWidth="1"/>
+    <col min="66" max="66" width="7.7265625" style="1" customWidth="1"/>
     <col min="67" max="67" width="9" style="1" customWidth="1"/>
-    <col min="68" max="68" width="7.7109375" style="1" customWidth="1"/>
+    <col min="68" max="68" width="7.7265625" style="1" customWidth="1"/>
     <col min="69" max="69" width="8" style="1" customWidth="1"/>
-    <col min="70" max="73" width="7.7109375" style="1" customWidth="1"/>
-    <col min="74" max="75" width="7.28515625" style="1" customWidth="1"/>
-    <col min="76" max="76" width="7.7109375" style="1" customWidth="1"/>
+    <col min="70" max="73" width="7.7265625" style="1" customWidth="1"/>
+    <col min="74" max="75" width="7.26953125" style="1" customWidth="1"/>
+    <col min="76" max="76" width="7.7265625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B1" s="22"/>
       <c r="C1" s="19"/>
       <c r="D1" s="19"/>
@@ -33860,7 +33377,7 @@
       <c r="BW1" s="5"/>
       <c r="BX1" s="5"/>
     </row>
-    <row r="2" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B2" s="22"/>
       <c r="C2" s="19"/>
       <c r="D2" s="19"/>
@@ -33934,7 +33451,7 @@
       <c r="BW2" s="5"/>
       <c r="BX2" s="5"/>
     </row>
-    <row r="3" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B3" s="22"/>
       <c r="C3" s="19"/>
       <c r="D3" s="19"/>
@@ -34008,7 +33525,7 @@
       <c r="BW3" s="5"/>
       <c r="BX3" s="5"/>
     </row>
-    <row r="4" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B4" s="22"/>
       <c r="C4" s="19"/>
       <c r="D4" s="19"/>
@@ -34082,7 +33599,7 @@
       <c r="BW4" s="5"/>
       <c r="BX4" s="5"/>
     </row>
-    <row r="5" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B5" s="22"/>
       <c r="C5" s="19"/>
       <c r="D5" s="19"/>
@@ -34156,7 +33673,7 @@
       <c r="BW5" s="5"/>
       <c r="BX5" s="5"/>
     </row>
-    <row r="6" spans="2:76" s="18" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:76" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B6" s="23"/>
       <c r="C6" s="20"/>
       <c r="D6" s="20"/>
@@ -34278,7 +33795,7 @@
       <c r="BW6" s="17"/>
       <c r="BX6" s="17"/>
     </row>
-    <row r="7" spans="2:76" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:76" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B7" s="24"/>
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
@@ -34557,7 +34074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:76" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:76" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="H8" s="26"/>
       <c r="J8" s="205" t="s">
         <v>22</v>
@@ -34656,7 +34173,7 @@
       <c r="BW8" s="104"/>
       <c r="BX8" s="109"/>
     </row>
-    <row r="9" spans="2:76" s="124" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:76" s="124" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="87" t="s">
         <v>0</v>
       </c>
@@ -34874,7 +34391,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B10" s="53" t="s">
         <v>402</v>
       </c>
@@ -35131,7 +34648,7 @@
       </c>
       <c r="BX10" s="111"/>
     </row>
-    <row r="11" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B11" s="53" t="s">
         <v>402</v>
       </c>
@@ -35388,7 +34905,7 @@
       </c>
       <c r="BX11" s="111"/>
     </row>
-    <row r="12" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B12" s="53" t="s">
         <v>402</v>
       </c>
@@ -35645,7 +35162,7 @@
       </c>
       <c r="BX12" s="111"/>
     </row>
-    <row r="13" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B13" s="53" t="s">
         <v>402</v>
       </c>
@@ -35902,7 +35419,7 @@
       </c>
       <c r="BX13" s="111"/>
     </row>
-    <row r="14" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B14" s="53" t="s">
         <v>402</v>
       </c>
@@ -36159,7 +35676,7 @@
       </c>
       <c r="BX14" s="111"/>
     </row>
-    <row r="15" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B15" s="53" t="s">
         <v>402</v>
       </c>
@@ -36416,7 +35933,7 @@
       </c>
       <c r="BX15" s="111"/>
     </row>
-    <row r="16" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B16" s="53" t="s">
         <v>402</v>
       </c>
@@ -36673,7 +36190,7 @@
       </c>
       <c r="BX16" s="111"/>
     </row>
-    <row r="17" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B17" s="53" t="s">
         <v>402</v>
       </c>
@@ -36930,7 +36447,7 @@
       </c>
       <c r="BX17" s="111"/>
     </row>
-    <row r="18" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B18" s="53" t="s">
         <v>402</v>
       </c>
@@ -37187,7 +36704,7 @@
       </c>
       <c r="BX18" s="111"/>
     </row>
-    <row r="19" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B19" s="53" t="s">
         <v>402</v>
       </c>
@@ -37444,7 +36961,7 @@
       </c>
       <c r="BX19" s="111"/>
     </row>
-    <row r="20" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B20" s="53" t="s">
         <v>402</v>
       </c>
@@ -37701,7 +37218,7 @@
       </c>
       <c r="BX20" s="111"/>
     </row>
-    <row r="21" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B21" s="53" t="s">
         <v>402</v>
       </c>
@@ -37958,7 +37475,7 @@
       </c>
       <c r="BX21" s="111"/>
     </row>
-    <row r="22" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B22" s="53" t="s">
         <v>402</v>
       </c>
@@ -38215,7 +37732,7 @@
       </c>
       <c r="BX22" s="111"/>
     </row>
-    <row r="23" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B23" s="53" t="s">
         <v>402</v>
       </c>
@@ -38472,7 +37989,7 @@
       </c>
       <c r="BX23" s="111"/>
     </row>
-    <row r="24" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B24" s="53" t="s">
         <v>402</v>
       </c>
@@ -38729,7 +38246,7 @@
       </c>
       <c r="BX24" s="111"/>
     </row>
-    <row r="25" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B25" s="53" t="s">
         <v>402</v>
       </c>
@@ -38986,7 +38503,7 @@
       </c>
       <c r="BX25" s="111"/>
     </row>
-    <row r="26" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B26" s="53" t="s">
         <v>402</v>
       </c>
@@ -39243,7 +38760,7 @@
       </c>
       <c r="BX26" s="111"/>
     </row>
-    <row r="27" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B27" s="53" t="s">
         <v>402</v>
       </c>
@@ -39500,7 +39017,7 @@
       </c>
       <c r="BX27" s="111"/>
     </row>
-    <row r="28" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B28" s="53" t="s">
         <v>402</v>
       </c>
@@ -39757,7 +39274,7 @@
       </c>
       <c r="BX28" s="111"/>
     </row>
-    <row r="29" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B29" s="53" t="s">
         <v>402</v>
       </c>
@@ -40014,7 +39531,7 @@
       </c>
       <c r="BX29" s="111"/>
     </row>
-    <row r="30" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B30" s="53" t="s">
         <v>402</v>
       </c>
@@ -40271,7 +39788,7 @@
       </c>
       <c r="BX30" s="111"/>
     </row>
-    <row r="31" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B31" s="53" t="s">
         <v>402</v>
       </c>
@@ -40528,7 +40045,7 @@
       </c>
       <c r="BX31" s="111"/>
     </row>
-    <row r="32" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B32" s="53" t="s">
         <v>402</v>
       </c>
@@ -40785,7 +40302,7 @@
       </c>
       <c r="BX32" s="111"/>
     </row>
-    <row r="33" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B33" s="53" t="s">
         <v>402</v>
       </c>
@@ -41042,7 +40559,7 @@
       </c>
       <c r="BX33" s="111"/>
     </row>
-    <row r="34" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B34" s="53" t="s">
         <v>402</v>
       </c>
@@ -41299,7 +40816,7 @@
       </c>
       <c r="BX34" s="111"/>
     </row>
-    <row r="35" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B35" s="53" t="s">
         <v>402</v>
       </c>
@@ -41556,7 +41073,7 @@
       </c>
       <c r="BX35" s="111"/>
     </row>
-    <row r="36" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B36" s="53" t="s">
         <v>402</v>
       </c>
@@ -41813,7 +41330,7 @@
       </c>
       <c r="BX36" s="111"/>
     </row>
-    <row r="37" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B37" s="53" t="s">
         <v>402</v>
       </c>
@@ -42070,7 +41587,7 @@
       </c>
       <c r="BX37" s="111"/>
     </row>
-    <row r="38" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B38" s="53" t="s">
         <v>402</v>
       </c>
@@ -42327,7 +41844,7 @@
       </c>
       <c r="BX38" s="111"/>
     </row>
-    <row r="39" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B39" s="53" t="s">
         <v>402</v>
       </c>
@@ -42584,7 +42101,7 @@
       </c>
       <c r="BX39" s="111"/>
     </row>
-    <row r="40" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B40" s="53" t="s">
         <v>402</v>
       </c>
@@ -42841,7 +42358,7 @@
       </c>
       <c r="BX40" s="111"/>
     </row>
-    <row r="41" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B41" s="53" t="s">
         <v>402</v>
       </c>
@@ -43098,7 +42615,7 @@
       </c>
       <c r="BX41" s="111"/>
     </row>
-    <row r="42" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B42" s="53" t="s">
         <v>402</v>
       </c>
@@ -43355,7 +42872,7 @@
       </c>
       <c r="BX42" s="111"/>
     </row>
-    <row r="43" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B43" s="53" t="s">
         <v>402</v>
       </c>
@@ -43612,7 +43129,7 @@
       </c>
       <c r="BX43" s="111"/>
     </row>
-    <row r="44" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B44" s="53" t="s">
         <v>402</v>
       </c>
@@ -43869,7 +43386,7 @@
       </c>
       <c r="BX44" s="111"/>
     </row>
-    <row r="45" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B45" s="53" t="s">
         <v>402</v>
       </c>
@@ -44126,7 +43643,7 @@
       </c>
       <c r="BX45" s="111"/>
     </row>
-    <row r="46" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B46" s="53" t="s">
         <v>402</v>
       </c>
@@ -44383,7 +43900,7 @@
       </c>
       <c r="BX46" s="111"/>
     </row>
-    <row r="47" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B47" s="53" t="s">
         <v>402</v>
       </c>
@@ -44640,7 +44157,7 @@
       </c>
       <c r="BX47" s="111"/>
     </row>
-    <row r="48" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B48" s="53" t="s">
         <v>402</v>
       </c>
@@ -44897,7 +44414,7 @@
       </c>
       <c r="BX48" s="111"/>
     </row>
-    <row r="49" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B49" s="53" t="s">
         <v>402</v>
       </c>
@@ -45154,7 +44671,7 @@
       </c>
       <c r="BX49" s="111"/>
     </row>
-    <row r="50" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B50" s="53" t="s">
         <v>402</v>
       </c>
@@ -45411,7 +44928,7 @@
       </c>
       <c r="BX50" s="111"/>
     </row>
-    <row r="51" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B51" s="53" t="s">
         <v>402</v>
       </c>
@@ -45668,7 +45185,7 @@
       </c>
       <c r="BX51" s="111"/>
     </row>
-    <row r="52" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B52" s="53" t="s">
         <v>402</v>
       </c>
@@ -45925,7 +45442,7 @@
       </c>
       <c r="BX52" s="111"/>
     </row>
-    <row r="53" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B53" s="53" t="s">
         <v>402</v>
       </c>
@@ -46182,7 +45699,7 @@
       </c>
       <c r="BX53" s="111"/>
     </row>
-    <row r="54" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B54" s="53" t="s">
         <v>402</v>
       </c>
@@ -46439,7 +45956,7 @@
       </c>
       <c r="BX54" s="111"/>
     </row>
-    <row r="55" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B55" s="53" t="s">
         <v>402</v>
       </c>
@@ -46696,7 +46213,7 @@
       </c>
       <c r="BX55" s="111"/>
     </row>
-    <row r="56" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B56" s="53" t="s">
         <v>402</v>
       </c>
@@ -46953,7 +46470,7 @@
       </c>
       <c r="BX56" s="111"/>
     </row>
-    <row r="57" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B57" s="53" t="s">
         <v>402</v>
       </c>
@@ -47210,7 +46727,7 @@
       </c>
       <c r="BX57" s="111"/>
     </row>
-    <row r="58" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B58" s="53" t="s">
         <v>402</v>
       </c>
@@ -47467,7 +46984,7 @@
       </c>
       <c r="BX58" s="111"/>
     </row>
-    <row r="59" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B59" s="53" t="s">
         <v>402</v>
       </c>
@@ -47724,7 +47241,7 @@
       </c>
       <c r="BX59" s="111"/>
     </row>
-    <row r="60" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B60" s="53" t="s">
         <v>402</v>
       </c>
@@ -47981,7 +47498,7 @@
       </c>
       <c r="BX60" s="111"/>
     </row>
-    <row r="61" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B61" s="53" t="s">
         <v>402</v>
       </c>
@@ -48238,7 +47755,7 @@
       </c>
       <c r="BX61" s="111"/>
     </row>
-    <row r="62" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B62" s="53" t="s">
         <v>97</v>
       </c>
@@ -48495,7 +48012,7 @@
       </c>
       <c r="BX62" s="111"/>
     </row>
-    <row r="63" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B63" s="53" t="s">
         <v>97</v>
       </c>
@@ -48752,7 +48269,7 @@
       </c>
       <c r="BX63" s="111"/>
     </row>
-    <row r="64" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B64" s="53" t="s">
         <v>97</v>
       </c>
@@ -49009,7 +48526,7 @@
       </c>
       <c r="BX64" s="111"/>
     </row>
-    <row r="65" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B65" s="53" t="s">
         <v>97</v>
       </c>
@@ -49266,7 +48783,7 @@
       </c>
       <c r="BX65" s="111"/>
     </row>
-    <row r="66" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B66" s="53" t="s">
         <v>97</v>
       </c>
@@ -49523,7 +49040,7 @@
       </c>
       <c r="BX66" s="111"/>
     </row>
-    <row r="67" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B67" s="53" t="s">
         <v>97</v>
       </c>
@@ -49780,7 +49297,7 @@
       </c>
       <c r="BX67" s="111"/>
     </row>
-    <row r="68" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B68" s="53" t="s">
         <v>97</v>
       </c>
@@ -50037,7 +49554,7 @@
       </c>
       <c r="BX68" s="111"/>
     </row>
-    <row r="69" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B69" s="53" t="s">
         <v>97</v>
       </c>
@@ -50294,7 +49811,7 @@
       </c>
       <c r="BX69" s="111"/>
     </row>
-    <row r="70" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B70" s="53" t="s">
         <v>97</v>
       </c>
@@ -50551,7 +50068,7 @@
       </c>
       <c r="BX70" s="111"/>
     </row>
-    <row r="71" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B71" s="53" t="s">
         <v>97</v>
       </c>
@@ -50808,7 +50325,7 @@
       </c>
       <c r="BX71" s="111"/>
     </row>
-    <row r="72" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B72" s="53" t="s">
         <v>97</v>
       </c>
@@ -51065,7 +50582,7 @@
       </c>
       <c r="BX72" s="111"/>
     </row>
-    <row r="73" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B73" s="53" t="s">
         <v>97</v>
       </c>
@@ -51322,7 +50839,7 @@
       </c>
       <c r="BX73" s="111"/>
     </row>
-    <row r="74" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B74" s="53" t="s">
         <v>97</v>
       </c>
@@ -51579,7 +51096,7 @@
       </c>
       <c r="BX74" s="111"/>
     </row>
-    <row r="75" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B75" s="53" t="s">
         <v>97</v>
       </c>
@@ -51836,7 +51353,7 @@
       </c>
       <c r="BX75" s="111"/>
     </row>
-    <row r="76" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B76" s="53" t="s">
         <v>97</v>
       </c>
@@ -52093,7 +51610,7 @@
       </c>
       <c r="BX76" s="111"/>
     </row>
-    <row r="77" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B77" s="53" t="s">
         <v>97</v>
       </c>
@@ -52350,7 +51867,7 @@
       </c>
       <c r="BX77" s="111"/>
     </row>
-    <row r="78" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B78" s="53" t="s">
         <v>97</v>
       </c>
@@ -52607,7 +52124,7 @@
       </c>
       <c r="BX78" s="111"/>
     </row>
-    <row r="79" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B79" s="53" t="s">
         <v>97</v>
       </c>
@@ -52864,7 +52381,7 @@
       </c>
       <c r="BX79" s="111"/>
     </row>
-    <row r="80" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B80" s="53" t="s">
         <v>97</v>
       </c>
@@ -53121,7 +52638,7 @@
       </c>
       <c r="BX80" s="111"/>
     </row>
-    <row r="81" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B81" s="53" t="s">
         <v>97</v>
       </c>
@@ -53378,7 +52895,7 @@
       </c>
       <c r="BX81" s="111"/>
     </row>
-    <row r="82" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B82" s="53" t="s">
         <v>97</v>
       </c>
@@ -53635,7 +53152,7 @@
       </c>
       <c r="BX82" s="111"/>
     </row>
-    <row r="83" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B83" s="53" t="s">
         <v>97</v>
       </c>
@@ -53892,7 +53409,7 @@
       </c>
       <c r="BX83" s="111"/>
     </row>
-    <row r="84" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B84" s="53" t="s">
         <v>97</v>
       </c>
@@ -54149,7 +53666,7 @@
       </c>
       <c r="BX84" s="111"/>
     </row>
-    <row r="85" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B85" s="53" t="s">
         <v>97</v>
       </c>
@@ -54406,7 +53923,7 @@
       </c>
       <c r="BX85" s="111"/>
     </row>
-    <row r="86" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B86" s="53" t="s">
         <v>97</v>
       </c>
@@ -54663,7 +54180,7 @@
       </c>
       <c r="BX86" s="111"/>
     </row>
-    <row r="87" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B87" s="53" t="s">
         <v>97</v>
       </c>
@@ -54920,7 +54437,7 @@
       </c>
       <c r="BX87" s="111"/>
     </row>
-    <row r="88" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B88" s="53" t="s">
         <v>97</v>
       </c>
@@ -55177,7 +54694,7 @@
       </c>
       <c r="BX88" s="111"/>
     </row>
-    <row r="89" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B89" s="53" t="s">
         <v>97</v>
       </c>
@@ -55434,7 +54951,7 @@
       </c>
       <c r="BX89" s="111"/>
     </row>
-    <row r="90" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B90" s="53" t="s">
         <v>97</v>
       </c>
@@ -55691,7 +55208,7 @@
       </c>
       <c r="BX90" s="111"/>
     </row>
-    <row r="91" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B91" s="53" t="s">
         <v>97</v>
       </c>
@@ -55948,7 +55465,7 @@
       </c>
       <c r="BX91" s="111"/>
     </row>
-    <row r="92" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B92" s="53" t="s">
         <v>97</v>
       </c>
@@ -56205,7 +55722,7 @@
       </c>
       <c r="BX92" s="111"/>
     </row>
-    <row r="93" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B93" s="53" t="s">
         <v>97</v>
       </c>
@@ -56462,7 +55979,7 @@
       </c>
       <c r="BX93" s="111"/>
     </row>
-    <row r="94" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B94" s="53" t="s">
         <v>97</v>
       </c>
@@ -56719,7 +56236,7 @@
       </c>
       <c r="BX94" s="111"/>
     </row>
-    <row r="95" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B95" s="53" t="s">
         <v>97</v>
       </c>
@@ -56976,7 +56493,7 @@
       </c>
       <c r="BX95" s="111"/>
     </row>
-    <row r="96" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B96" s="53" t="s">
         <v>97</v>
       </c>
@@ -57233,7 +56750,7 @@
       </c>
       <c r="BX96" s="111"/>
     </row>
-    <row r="97" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B97" s="53" t="s">
         <v>97</v>
       </c>
@@ -57490,7 +57007,7 @@
       </c>
       <c r="BX97" s="111"/>
     </row>
-    <row r="98" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B98" s="53" t="s">
         <v>97</v>
       </c>
@@ -57747,7 +57264,7 @@
       </c>
       <c r="BX98" s="111"/>
     </row>
-    <row r="99" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B99" s="53" t="s">
         <v>97</v>
       </c>
@@ -58004,7 +57521,7 @@
       </c>
       <c r="BX99" s="111"/>
     </row>
-    <row r="100" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B100" s="53" t="s">
         <v>97</v>
       </c>
@@ -58261,7 +57778,7 @@
       </c>
       <c r="BX100" s="111"/>
     </row>
-    <row r="101" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B101" s="53" t="s">
         <v>97</v>
       </c>
@@ -58518,7 +58035,7 @@
       </c>
       <c r="BX101" s="111"/>
     </row>
-    <row r="102" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B102" s="53" t="s">
         <v>97</v>
       </c>
@@ -58775,7 +58292,7 @@
       </c>
       <c r="BX102" s="111"/>
     </row>
-    <row r="103" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B103" s="53" t="s">
         <v>97</v>
       </c>
@@ -59032,7 +58549,7 @@
       </c>
       <c r="BX103" s="111"/>
     </row>
-    <row r="104" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B104" s="53" t="s">
         <v>97</v>
       </c>
@@ -59289,7 +58806,7 @@
       </c>
       <c r="BX104" s="111"/>
     </row>
-    <row r="105" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B105" s="53" t="s">
         <v>97</v>
       </c>
@@ -59546,7 +59063,7 @@
       </c>
       <c r="BX105" s="111"/>
     </row>
-    <row r="106" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B106" s="53" t="s">
         <v>97</v>
       </c>
@@ -59803,7 +59320,7 @@
       </c>
       <c r="BX106" s="111"/>
     </row>
-    <row r="107" spans="2:76" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:76" x14ac:dyDescent="0.35">
       <c r="B107" s="53" t="s">
         <v>97</v>
       </c>
@@ -60087,18 +59604,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:V17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.7265625" customWidth="1"/>
+    <col min="2" max="2" width="18.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="13" width="0" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="10.140625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="10.1796875" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="0" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="2.5703125" customWidth="1"/>
-    <col min="22" max="22" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="2.54296875" customWidth="1"/>
+    <col min="22" max="22" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:22" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:22" ht="18" x14ac:dyDescent="0.5">
       <c r="H1" s="172">
         <v>2025</v>
       </c>
@@ -60106,7 +59623,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B2" s="151" t="s">
         <v>32</v>
       </c>
@@ -60168,7 +59685,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="3" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B3" s="163" t="s">
         <v>136</v>
       </c>
@@ -60244,7 +59761,7 @@
         <v>Estrela</v>
       </c>
     </row>
-    <row r="4" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B4" s="163" t="s">
         <v>153</v>
       </c>
@@ -60320,7 +59837,7 @@
         <v>Estrela</v>
       </c>
     </row>
-    <row r="5" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B5" s="163" t="s">
         <v>105</v>
       </c>
@@ -60396,7 +59913,7 @@
         <v>Estrela</v>
       </c>
     </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B6" s="163" t="s">
         <v>107</v>
       </c>
@@ -60472,7 +59989,7 @@
         <v>Estrela</v>
       </c>
     </row>
-    <row r="7" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B7" s="163" t="s">
         <v>102</v>
       </c>
@@ -60548,7 +60065,7 @@
         <v>Estrela</v>
       </c>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B8" s="163" t="s">
         <v>101</v>
       </c>
@@ -60624,7 +60141,7 @@
         <v>Estrela</v>
       </c>
     </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B9" s="163" t="s">
         <v>154</v>
       </c>
@@ -60700,7 +60217,7 @@
         <v>Estrela</v>
       </c>
     </row>
-    <row r="10" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B10" s="163" t="s">
         <v>135</v>
       </c>
@@ -60776,7 +60293,7 @@
         <v>Estrela</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B11" s="163" t="s">
         <v>99</v>
       </c>
@@ -60852,7 +60369,7 @@
         <v>Diamante</v>
       </c>
     </row>
-    <row r="12" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B12" s="163" t="s">
         <v>106</v>
       </c>
@@ -60928,7 +60445,7 @@
         <v>Estrela</v>
       </c>
     </row>
-    <row r="13" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B13" s="163" t="s">
         <v>110</v>
       </c>
@@ -61004,7 +60521,7 @@
         <v>Estrela</v>
       </c>
     </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B14" s="163" t="s">
         <v>103</v>
       </c>
@@ -61080,7 +60597,7 @@
         <v>Estrela</v>
       </c>
     </row>
-    <row r="15" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B15" s="163" t="s">
         <v>108</v>
       </c>
@@ -61156,7 +60673,7 @@
         <v>Estrela</v>
       </c>
     </row>
-    <row r="16" spans="2:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:22" x14ac:dyDescent="0.35">
       <c r="B16" s="163" t="s">
         <v>134</v>
       </c>
@@ -61232,7 +60749,7 @@
         <v>Diamante</v>
       </c>
     </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:21" x14ac:dyDescent="0.35">
       <c r="C17" s="165">
         <f t="shared" ref="C17:O17" si="2">SUM(C3:C16)</f>
         <v>1856.1390000000001</v>
@@ -61314,28 +60831,28 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF51D1E0-CD75-48F2-9AAA-AABC475E49E8}">
   <dimension ref="B1:X99"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.5703125" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="1.54296875" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="9.1796875" customWidth="1"/>
     <col min="10" max="10" width="36" customWidth="1"/>
-    <col min="11" max="11" width="28.5703125" customWidth="1"/>
-    <col min="12" max="12" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.7109375" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="14" width="7.85546875" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="7.140625" customWidth="1" outlineLevel="1"/>
-    <col min="16" max="16" width="7.7109375" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="28.54296875" customWidth="1"/>
+    <col min="12" max="12" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.7265625" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="7.81640625" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="7.1796875" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="7.7265625" customWidth="1" outlineLevel="1"/>
     <col min="17" max="17" width="8" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="7.5703125" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="20" width="7.28515625" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="8.140625" customWidth="1" outlineLevel="1"/>
-    <col min="22" max="22" width="7.5703125" customWidth="1" outlineLevel="1"/>
-    <col min="23" max="23" width="7.85546875" customWidth="1" outlineLevel="1"/>
-    <col min="24" max="24" width="7.42578125" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="7.54296875" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="20" width="7.26953125" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="8.1796875" customWidth="1" outlineLevel="1"/>
+    <col min="22" max="22" width="7.54296875" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="23" width="7.81640625" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="24" width="7.453125" customWidth="1" outlineLevel="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:24" x14ac:dyDescent="0.35">
       <c r="E1" t="s">
         <v>507</v>
       </c>
@@ -61379,7 +60896,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="2" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>402</v>
       </c>
@@ -61450,7 +60967,7 @@
         <v>15.238</v>
       </c>
     </row>
-    <row r="3" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>402</v>
       </c>
@@ -61521,7 +61038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>402</v>
       </c>
@@ -61592,7 +61109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>402</v>
       </c>
@@ -61663,7 +61180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>402</v>
       </c>
@@ -61734,7 +61251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>402</v>
       </c>
@@ -61805,7 +61322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>402</v>
       </c>
@@ -61876,7 +61393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>402</v>
       </c>
@@ -61947,7 +61464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>402</v>
       </c>
@@ -62018,7 +61535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>402</v>
       </c>
@@ -62089,7 +61606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>402</v>
       </c>
@@ -62160,7 +61677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>402</v>
       </c>
@@ -62231,7 +61748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>402</v>
       </c>
@@ -62302,7 +61819,7 @@
         <v>52.417000000000002</v>
       </c>
     </row>
-    <row r="15" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>402</v>
       </c>
@@ -62373,7 +61890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>402</v>
       </c>
@@ -62444,7 +61961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>402</v>
       </c>
@@ -62515,7 +62032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>402</v>
       </c>
@@ -62586,7 +62103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>402</v>
       </c>
@@ -62657,7 +62174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>402</v>
       </c>
@@ -62728,7 +62245,7 @@
         <v>-15.007</v>
       </c>
     </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>402</v>
       </c>
@@ -62799,7 +62316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>402</v>
       </c>
@@ -62870,7 +62387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>402</v>
       </c>
@@ -62941,7 +62458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>402</v>
       </c>
@@ -63012,7 +62529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>402</v>
       </c>
@@ -63083,7 +62600,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>402</v>
       </c>
@@ -63154,7 +62671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>402</v>
       </c>
@@ -63225,7 +62742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>402</v>
       </c>
@@ -63296,7 +62813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>402</v>
       </c>
@@ -63367,7 +62884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>402</v>
       </c>
@@ -63438,7 +62955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>402</v>
       </c>
@@ -63509,7 +63026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>402</v>
       </c>
@@ -63580,7 +63097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>402</v>
       </c>
@@ -63651,7 +63168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>402</v>
       </c>
@@ -63722,7 +63239,7 @@
         <v>67.832999999999998</v>
       </c>
     </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
         <v>402</v>
       </c>
@@ -63793,7 +63310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>402</v>
       </c>
@@ -63864,7 +63381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>402</v>
       </c>
@@ -63935,7 +63452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>402</v>
       </c>
@@ -64006,7 +63523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>402</v>
       </c>
@@ -64077,7 +63594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>402</v>
       </c>
@@ -64148,7 +63665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>402</v>
       </c>
@@ -64219,7 +63736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>402</v>
       </c>
@@ -64290,7 +63807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>402</v>
       </c>
@@ -64361,7 +63878,7 @@
         <v>26.25</v>
       </c>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>402</v>
       </c>
@@ -64432,7 +63949,7 @@
         <v>10.375</v>
       </c>
     </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>402</v>
       </c>
@@ -64503,7 +64020,7 @@
         <v>21.082999999999998</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>402</v>
       </c>
@@ -64574,7 +64091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>402</v>
       </c>
@@ -64645,7 +64162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
         <v>402</v>
       </c>
@@ -64716,7 +64233,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
         <v>402</v>
       </c>
@@ -64787,7 +64304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
         <v>402</v>
       </c>
@@ -64858,7 +64375,7 @@
         <v>183.5</v>
       </c>
     </row>
-    <row r="51" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
         <v>402</v>
       </c>
@@ -64929,7 +64446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
         <v>402</v>
       </c>
@@ -65000,7 +64517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
         <v>402</v>
       </c>
@@ -65071,7 +64588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
         <v>97</v>
       </c>
@@ -65142,7 +64659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
         <v>97</v>
       </c>
@@ -65213,7 +64730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B56" t="s">
         <v>97</v>
       </c>
@@ -65284,7 +64801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B57" t="s">
         <v>97</v>
       </c>
@@ -65355,7 +64872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
         <v>97</v>
       </c>
@@ -65426,7 +64943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
         <v>97</v>
       </c>
@@ -65497,7 +65014,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="60" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
         <v>97</v>
       </c>
@@ -65568,7 +65085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
         <v>97</v>
       </c>
@@ -65639,7 +65156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B62" t="s">
         <v>97</v>
       </c>
@@ -65710,7 +65227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
         <v>97</v>
       </c>
@@ -65781,7 +65298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
         <v>97</v>
       </c>
@@ -65852,7 +65369,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B65" t="s">
         <v>97</v>
       </c>
@@ -65923,7 +65440,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
         <v>97</v>
       </c>
@@ -65994,7 +65511,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
         <v>97</v>
       </c>
@@ -66065,7 +65582,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
         <v>97</v>
       </c>
@@ -66136,7 +65653,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B69" t="s">
         <v>97</v>
       </c>
@@ -66207,7 +65724,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
         <v>97</v>
       </c>
@@ -66278,7 +65795,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B71" t="s">
         <v>97</v>
       </c>
@@ -66349,7 +65866,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B72" t="s">
         <v>98</v>
       </c>
@@ -66420,7 +65937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B73" t="s">
         <v>98</v>
       </c>
@@ -66491,7 +66008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
         <v>98</v>
       </c>
@@ -66562,7 +66079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
         <v>98</v>
       </c>
@@ -66633,7 +66150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
         <v>98</v>
       </c>
@@ -66704,7 +66221,7 @@
         <v>284.91699999999997</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
         <v>98</v>
       </c>
@@ -66775,7 +66292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
         <v>98</v>
       </c>
@@ -66846,7 +66363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
         <v>98</v>
       </c>
@@ -66917,7 +66434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
         <v>98</v>
       </c>
@@ -66988,7 +66505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
         <v>98</v>
       </c>
@@ -67059,7 +66576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
         <v>98</v>
       </c>
@@ -67130,7 +66647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
         <v>98</v>
       </c>
@@ -67201,7 +66718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
         <v>98</v>
       </c>
@@ -67272,7 +66789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
         <v>98</v>
       </c>
@@ -67343,7 +66860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
         <v>98</v>
       </c>
@@ -67414,7 +66931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
         <v>98</v>
       </c>
@@ -67485,7 +67002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
         <v>98</v>
       </c>
@@ -67556,7 +67073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
         <v>98</v>
       </c>
@@ -67627,7 +67144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B90" t="s">
         <v>98</v>
       </c>
@@ -67698,7 +67215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B91" t="s">
         <v>98</v>
       </c>
@@ -67769,7 +67286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B92" t="s">
         <v>98</v>
       </c>
@@ -67840,7 +67357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B93" t="s">
         <v>98</v>
       </c>
@@ -67911,7 +67428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
         <v>98</v>
       </c>
@@ -67982,7 +67499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
         <v>98</v>
       </c>
@@ -68053,7 +67570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
         <v>98</v>
       </c>
@@ -68124,7 +67641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
         <v>98</v>
       </c>
@@ -68195,7 +67712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
         <v>98</v>
       </c>
@@ -68266,7 +67783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:24" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
         <v>98</v>
       </c>

--- a/MECÂNICAS/PAUTA M/JHONSON/Campanha Johnson - Top Contas Q4 FY26.xlsx
+++ b/MECÂNICAS/PAUTA M/JHONSON/Campanha Johnson - Top Contas Q4 FY26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\Nicolas\Acompanhamentos\JOHNSON\2025.26\Q4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20EFE581-66D0-4101-9E8E-8C9C765DF180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C6F879B-6FDD-42F4-B5C4-559046CCD7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="705" firstSheet="1" activeTab="3" xr2:uid="{1E3193F5-9832-4B59-8D54-14EFCF6055F0}"/>
   </bookViews>
@@ -3942,10 +3942,37 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3965,33 +3992,6 @@
     </xf>
     <xf numFmtId="3" fontId="4" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5777,9 +5777,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>960452</xdr:colOff>
+      <xdr:colOff>963627</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>9582</xdr:rowOff>
+      <xdr:rowOff>6407</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5857,9 +5857,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>597342</xdr:colOff>
+      <xdr:colOff>600517</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>122720</xdr:rowOff>
+      <xdr:rowOff>125895</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -20019,7 +20019,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:CU23944"/>
-  <sheetFormatPr defaultColWidth="9.26953125" defaultRowHeight="13" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.26953125" defaultRowHeight="13" zeroHeight="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.26953125" style="1" bestFit="1" customWidth="1"/>
@@ -20126,138 +20126,138 @@
       <c r="B2" s="152"/>
     </row>
     <row r="3" spans="2:99" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="E3" s="203" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="196" t="s">
+      <c r="E3" s="190" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="188" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="201" t="s">
+      <c r="G3" s="197" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="199"/>
-      <c r="I3" s="199"/>
-      <c r="J3" s="199"/>
-      <c r="K3" s="199"/>
-      <c r="L3" s="199"/>
-      <c r="M3" s="199"/>
-      <c r="N3" s="200"/>
-      <c r="O3" s="188" t="s">
+      <c r="H3" s="193"/>
+      <c r="I3" s="193"/>
+      <c r="J3" s="193"/>
+      <c r="K3" s="193"/>
+      <c r="L3" s="193"/>
+      <c r="M3" s="193"/>
+      <c r="N3" s="194"/>
+      <c r="O3" s="195" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="189"/>
-      <c r="Q3" s="189"/>
-      <c r="R3" s="189"/>
-      <c r="S3" s="188" t="s">
+      <c r="P3" s="196"/>
+      <c r="Q3" s="196"/>
+      <c r="R3" s="196"/>
+      <c r="S3" s="195" t="s">
         <v>24</v>
       </c>
-      <c r="T3" s="189"/>
-      <c r="U3" s="189"/>
-      <c r="V3" s="189"/>
-      <c r="W3" s="188" t="s">
+      <c r="T3" s="196"/>
+      <c r="U3" s="196"/>
+      <c r="V3" s="196"/>
+      <c r="W3" s="195" t="s">
         <v>25</v>
       </c>
-      <c r="X3" s="189"/>
-      <c r="Y3" s="189"/>
-      <c r="Z3" s="189"/>
-      <c r="AB3" s="198" t="s">
+      <c r="X3" s="196"/>
+      <c r="Y3" s="196"/>
+      <c r="Z3" s="196"/>
+      <c r="AB3" s="192" t="s">
         <v>30</v>
       </c>
-      <c r="AC3" s="199"/>
-      <c r="AD3" s="199"/>
-      <c r="AE3" s="199"/>
-      <c r="AF3" s="199"/>
-      <c r="AG3" s="199"/>
-      <c r="AH3" s="199"/>
-      <c r="AI3" s="202"/>
-      <c r="AJ3" s="188" t="s">
+      <c r="AC3" s="193"/>
+      <c r="AD3" s="193"/>
+      <c r="AE3" s="193"/>
+      <c r="AF3" s="193"/>
+      <c r="AG3" s="193"/>
+      <c r="AH3" s="193"/>
+      <c r="AI3" s="198"/>
+      <c r="AJ3" s="195" t="s">
         <v>27</v>
       </c>
-      <c r="AK3" s="189"/>
-      <c r="AL3" s="189"/>
-      <c r="AM3" s="189"/>
-      <c r="AN3" s="188" t="s">
+      <c r="AK3" s="196"/>
+      <c r="AL3" s="196"/>
+      <c r="AM3" s="196"/>
+      <c r="AN3" s="195" t="s">
         <v>28</v>
       </c>
-      <c r="AO3" s="189"/>
-      <c r="AP3" s="189"/>
-      <c r="AQ3" s="189"/>
-      <c r="AR3" s="188" t="s">
+      <c r="AO3" s="196"/>
+      <c r="AP3" s="196"/>
+      <c r="AQ3" s="196"/>
+      <c r="AR3" s="195" t="s">
         <v>29</v>
       </c>
-      <c r="AS3" s="189"/>
-      <c r="AT3" s="189"/>
-      <c r="AU3" s="189"/>
-      <c r="AW3" s="198" t="s">
+      <c r="AS3" s="196"/>
+      <c r="AT3" s="196"/>
+      <c r="AU3" s="196"/>
+      <c r="AW3" s="192" t="s">
         <v>66</v>
       </c>
-      <c r="AX3" s="199"/>
-      <c r="AY3" s="199"/>
-      <c r="AZ3" s="199"/>
-      <c r="BA3" s="199"/>
-      <c r="BB3" s="199"/>
-      <c r="BC3" s="199"/>
-      <c r="BD3" s="200"/>
-      <c r="BE3" s="188" t="s">
+      <c r="AX3" s="193"/>
+      <c r="AY3" s="193"/>
+      <c r="AZ3" s="193"/>
+      <c r="BA3" s="193"/>
+      <c r="BB3" s="193"/>
+      <c r="BC3" s="193"/>
+      <c r="BD3" s="194"/>
+      <c r="BE3" s="195" t="s">
         <v>67</v>
       </c>
-      <c r="BF3" s="189"/>
-      <c r="BG3" s="189"/>
-      <c r="BH3" s="189"/>
-      <c r="BI3" s="188" t="s">
+      <c r="BF3" s="196"/>
+      <c r="BG3" s="196"/>
+      <c r="BH3" s="196"/>
+      <c r="BI3" s="195" t="s">
         <v>68</v>
       </c>
-      <c r="BJ3" s="189"/>
-      <c r="BK3" s="189"/>
-      <c r="BL3" s="189"/>
-      <c r="BM3" s="188" t="s">
+      <c r="BJ3" s="196"/>
+      <c r="BK3" s="196"/>
+      <c r="BL3" s="196"/>
+      <c r="BM3" s="195" t="s">
         <v>72</v>
       </c>
-      <c r="BN3" s="189"/>
-      <c r="BO3" s="189"/>
-      <c r="BP3" s="189"/>
-      <c r="BR3" s="198" t="s">
+      <c r="BN3" s="196"/>
+      <c r="BO3" s="196"/>
+      <c r="BP3" s="196"/>
+      <c r="BR3" s="192" t="s">
         <v>73</v>
       </c>
-      <c r="BS3" s="199"/>
-      <c r="BT3" s="199"/>
-      <c r="BU3" s="199"/>
-      <c r="BV3" s="199"/>
-      <c r="BW3" s="199"/>
-      <c r="BX3" s="199"/>
-      <c r="BY3" s="200"/>
+      <c r="BS3" s="193"/>
+      <c r="BT3" s="193"/>
+      <c r="BU3" s="193"/>
+      <c r="BV3" s="193"/>
+      <c r="BW3" s="193"/>
+      <c r="BX3" s="193"/>
+      <c r="BY3" s="194"/>
       <c r="BZ3" s="73" t="s">
         <v>69</v>
       </c>
       <c r="CA3" s="74"/>
       <c r="CB3" s="74"/>
       <c r="CC3" s="74"/>
-      <c r="CD3" s="188" t="s">
+      <c r="CD3" s="195" t="s">
         <v>70</v>
       </c>
-      <c r="CE3" s="189"/>
-      <c r="CF3" s="189"/>
-      <c r="CG3" s="189"/>
-      <c r="CH3" s="188" t="s">
+      <c r="CE3" s="196"/>
+      <c r="CF3" s="196"/>
+      <c r="CG3" s="196"/>
+      <c r="CH3" s="195" t="s">
         <v>71</v>
       </c>
-      <c r="CI3" s="189"/>
-      <c r="CJ3" s="189"/>
-      <c r="CK3" s="189"/>
-      <c r="CM3" s="198" t="s">
+      <c r="CI3" s="196"/>
+      <c r="CJ3" s="196"/>
+      <c r="CK3" s="196"/>
+      <c r="CM3" s="192" t="s">
         <v>783</v>
       </c>
-      <c r="CN3" s="199"/>
-      <c r="CO3" s="199"/>
-      <c r="CP3" s="199"/>
-      <c r="CQ3" s="199"/>
-      <c r="CR3" s="199"/>
-      <c r="CS3" s="199"/>
-      <c r="CT3" s="200"/>
+      <c r="CN3" s="193"/>
+      <c r="CO3" s="193"/>
+      <c r="CP3" s="193"/>
+      <c r="CQ3" s="193"/>
+      <c r="CR3" s="193"/>
+      <c r="CS3" s="193"/>
+      <c r="CT3" s="194"/>
     </row>
     <row r="4" spans="2:99" ht="26" x14ac:dyDescent="0.3">
-      <c r="E4" s="204"/>
-      <c r="F4" s="197"/>
+      <c r="E4" s="191"/>
+      <c r="F4" s="189"/>
       <c r="G4" s="148" t="s">
         <v>169</v>
       </c>
@@ -21657,137 +21657,137 @@
       <c r="CK9" s="11"/>
     </row>
     <row r="10" spans="2:99" ht="14.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="193" t="s">
+      <c r="B10" s="202" t="s">
         <v>784</v>
       </c>
-      <c r="C10" s="194"/>
-      <c r="D10" s="194"/>
-      <c r="E10" s="195"/>
-      <c r="F10" s="196" t="s">
+      <c r="C10" s="203"/>
+      <c r="D10" s="203"/>
+      <c r="E10" s="204"/>
+      <c r="F10" s="188" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="198" t="s">
+      <c r="G10" s="192" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="199"/>
-      <c r="I10" s="199"/>
-      <c r="J10" s="199"/>
-      <c r="K10" s="199"/>
-      <c r="L10" s="199"/>
-      <c r="M10" s="199"/>
-      <c r="N10" s="200"/>
-      <c r="O10" s="188" t="s">
+      <c r="H10" s="193"/>
+      <c r="I10" s="193"/>
+      <c r="J10" s="193"/>
+      <c r="K10" s="193"/>
+      <c r="L10" s="193"/>
+      <c r="M10" s="193"/>
+      <c r="N10" s="194"/>
+      <c r="O10" s="195" t="s">
         <v>23</v>
       </c>
-      <c r="P10" s="189"/>
-      <c r="Q10" s="189"/>
-      <c r="R10" s="189"/>
-      <c r="S10" s="188" t="s">
+      <c r="P10" s="196"/>
+      <c r="Q10" s="196"/>
+      <c r="R10" s="196"/>
+      <c r="S10" s="195" t="s">
         <v>24</v>
       </c>
-      <c r="T10" s="189"/>
-      <c r="U10" s="189"/>
-      <c r="V10" s="189"/>
-      <c r="W10" s="188" t="s">
+      <c r="T10" s="196"/>
+      <c r="U10" s="196"/>
+      <c r="V10" s="196"/>
+      <c r="W10" s="195" t="s">
         <v>25</v>
       </c>
-      <c r="X10" s="189"/>
-      <c r="Y10" s="189"/>
-      <c r="Z10" s="189"/>
-      <c r="AB10" s="198" t="s">
+      <c r="X10" s="196"/>
+      <c r="Y10" s="196"/>
+      <c r="Z10" s="196"/>
+      <c r="AB10" s="192" t="s">
         <v>30</v>
       </c>
-      <c r="AC10" s="199"/>
-      <c r="AD10" s="199"/>
-      <c r="AE10" s="199"/>
-      <c r="AF10" s="199"/>
-      <c r="AG10" s="199"/>
-      <c r="AH10" s="199"/>
-      <c r="AI10" s="202"/>
-      <c r="AJ10" s="188" t="s">
+      <c r="AC10" s="193"/>
+      <c r="AD10" s="193"/>
+      <c r="AE10" s="193"/>
+      <c r="AF10" s="193"/>
+      <c r="AG10" s="193"/>
+      <c r="AH10" s="193"/>
+      <c r="AI10" s="198"/>
+      <c r="AJ10" s="195" t="s">
         <v>27</v>
       </c>
-      <c r="AK10" s="189"/>
-      <c r="AL10" s="189"/>
-      <c r="AM10" s="189"/>
-      <c r="AN10" s="188" t="s">
+      <c r="AK10" s="196"/>
+      <c r="AL10" s="196"/>
+      <c r="AM10" s="196"/>
+      <c r="AN10" s="195" t="s">
         <v>28</v>
       </c>
-      <c r="AO10" s="189"/>
-      <c r="AP10" s="189"/>
-      <c r="AQ10" s="189"/>
-      <c r="AR10" s="188" t="s">
+      <c r="AO10" s="196"/>
+      <c r="AP10" s="196"/>
+      <c r="AQ10" s="196"/>
+      <c r="AR10" s="195" t="s">
         <v>29</v>
       </c>
-      <c r="AS10" s="189"/>
-      <c r="AT10" s="189"/>
-      <c r="AU10" s="189"/>
-      <c r="AW10" s="198" t="s">
+      <c r="AS10" s="196"/>
+      <c r="AT10" s="196"/>
+      <c r="AU10" s="196"/>
+      <c r="AW10" s="192" t="s">
         <v>66</v>
       </c>
-      <c r="AX10" s="199"/>
-      <c r="AY10" s="199"/>
-      <c r="AZ10" s="199"/>
-      <c r="BA10" s="199"/>
-      <c r="BB10" s="199"/>
-      <c r="BC10" s="199"/>
-      <c r="BD10" s="200"/>
-      <c r="BE10" s="188" t="s">
+      <c r="AX10" s="193"/>
+      <c r="AY10" s="193"/>
+      <c r="AZ10" s="193"/>
+      <c r="BA10" s="193"/>
+      <c r="BB10" s="193"/>
+      <c r="BC10" s="193"/>
+      <c r="BD10" s="194"/>
+      <c r="BE10" s="195" t="s">
         <v>67</v>
       </c>
-      <c r="BF10" s="189"/>
-      <c r="BG10" s="189"/>
-      <c r="BH10" s="189"/>
-      <c r="BI10" s="188" t="s">
+      <c r="BF10" s="196"/>
+      <c r="BG10" s="196"/>
+      <c r="BH10" s="196"/>
+      <c r="BI10" s="195" t="s">
         <v>68</v>
       </c>
-      <c r="BJ10" s="189"/>
-      <c r="BK10" s="189"/>
-      <c r="BL10" s="189"/>
-      <c r="BM10" s="188" t="s">
+      <c r="BJ10" s="196"/>
+      <c r="BK10" s="196"/>
+      <c r="BL10" s="196"/>
+      <c r="BM10" s="195" t="s">
         <v>72</v>
       </c>
-      <c r="BN10" s="189"/>
-      <c r="BO10" s="189"/>
-      <c r="BP10" s="189"/>
-      <c r="BR10" s="198" t="s">
+      <c r="BN10" s="196"/>
+      <c r="BO10" s="196"/>
+      <c r="BP10" s="196"/>
+      <c r="BR10" s="192" t="s">
         <v>73</v>
       </c>
-      <c r="BS10" s="199"/>
-      <c r="BT10" s="199"/>
-      <c r="BU10" s="199"/>
-      <c r="BV10" s="199"/>
-      <c r="BW10" s="199"/>
-      <c r="BX10" s="199"/>
-      <c r="BY10" s="200"/>
+      <c r="BS10" s="193"/>
+      <c r="BT10" s="193"/>
+      <c r="BU10" s="193"/>
+      <c r="BV10" s="193"/>
+      <c r="BW10" s="193"/>
+      <c r="BX10" s="193"/>
+      <c r="BY10" s="194"/>
       <c r="BZ10" s="73" t="s">
         <v>69</v>
       </c>
       <c r="CA10" s="74"/>
       <c r="CB10" s="74"/>
       <c r="CC10" s="74"/>
-      <c r="CD10" s="188" t="s">
+      <c r="CD10" s="195" t="s">
         <v>70</v>
       </c>
-      <c r="CE10" s="189"/>
-      <c r="CF10" s="189"/>
-      <c r="CG10" s="189"/>
-      <c r="CH10" s="188" t="s">
+      <c r="CE10" s="196"/>
+      <c r="CF10" s="196"/>
+      <c r="CG10" s="196"/>
+      <c r="CH10" s="195" t="s">
         <v>71</v>
       </c>
-      <c r="CI10" s="189"/>
-      <c r="CJ10" s="189"/>
-      <c r="CK10" s="189"/>
-      <c r="CM10" s="198" t="s">
+      <c r="CI10" s="196"/>
+      <c r="CJ10" s="196"/>
+      <c r="CK10" s="196"/>
+      <c r="CM10" s="192" t="s">
         <v>783</v>
       </c>
-      <c r="CN10" s="199"/>
-      <c r="CO10" s="199"/>
-      <c r="CP10" s="199"/>
-      <c r="CQ10" s="199"/>
-      <c r="CR10" s="199"/>
-      <c r="CS10" s="199"/>
-      <c r="CT10" s="200"/>
+      <c r="CN10" s="193"/>
+      <c r="CO10" s="193"/>
+      <c r="CP10" s="193"/>
+      <c r="CQ10" s="193"/>
+      <c r="CR10" s="193"/>
+      <c r="CS10" s="193"/>
+      <c r="CT10" s="194"/>
     </row>
     <row r="11" spans="2:99" ht="26" x14ac:dyDescent="0.3">
       <c r="B11" s="52" t="s">
@@ -21802,7 +21802,7 @@
       <c r="E11" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="197"/>
+      <c r="F11" s="189"/>
       <c r="G11" s="38" t="s">
         <v>169</v>
       </c>
@@ -25055,12 +25055,12 @@
       <c r="CU19" s="21"/>
     </row>
     <row r="20" spans="2:99" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="190" t="s">
+      <c r="B20" s="199" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="191"/>
-      <c r="D20" s="191"/>
-      <c r="E20" s="192"/>
+      <c r="C20" s="200"/>
+      <c r="D20" s="200"/>
+      <c r="E20" s="201"/>
       <c r="F20" s="115">
         <f>SUM(F12:F19)</f>
         <v>14</v>
@@ -25423,180 +25423,241 @@
       <c r="D21" s="12"/>
       <c r="E21" s="13"/>
     </row>
-    <row r="9526" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:99" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="2:99" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="2:99" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="2:99" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="2:99" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:99" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="2:99" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="2:99" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="2:99" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="2:99" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="2:99" x14ac:dyDescent="0.3"/>
+    <row r="33" x14ac:dyDescent="0.3"/>
+    <row r="34" x14ac:dyDescent="0.3"/>
+    <row r="35" x14ac:dyDescent="0.3"/>
+    <row r="36" x14ac:dyDescent="0.3"/>
+    <row r="37" x14ac:dyDescent="0.3"/>
+    <row r="38" x14ac:dyDescent="0.3"/>
+    <row r="39" x14ac:dyDescent="0.3"/>
+    <row r="40" x14ac:dyDescent="0.3"/>
+    <row r="41" x14ac:dyDescent="0.3"/>
+    <row r="42" x14ac:dyDescent="0.3"/>
+    <row r="43" x14ac:dyDescent="0.3"/>
+    <row r="44" x14ac:dyDescent="0.3"/>
+    <row r="45" x14ac:dyDescent="0.3"/>
+    <row r="46" x14ac:dyDescent="0.3"/>
+    <row r="47" x14ac:dyDescent="0.3"/>
+    <row r="48" x14ac:dyDescent="0.3"/>
+    <row r="49" x14ac:dyDescent="0.3"/>
+    <row r="50" x14ac:dyDescent="0.3"/>
+    <row r="51" x14ac:dyDescent="0.3"/>
+    <row r="52" x14ac:dyDescent="0.3"/>
+    <row r="53" x14ac:dyDescent="0.3"/>
+    <row r="54" x14ac:dyDescent="0.3"/>
+    <row r="55" x14ac:dyDescent="0.3"/>
+    <row r="56" x14ac:dyDescent="0.3"/>
+    <row r="57" x14ac:dyDescent="0.3"/>
+    <row r="58" x14ac:dyDescent="0.3"/>
+    <row r="59" x14ac:dyDescent="0.3"/>
+    <row r="60" x14ac:dyDescent="0.3"/>
+    <row r="61" x14ac:dyDescent="0.3"/>
+    <row r="9526" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D9526" s="4"/>
       <c r="E9526" s="4"/>
     </row>
-    <row r="10161" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="10161" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D10161" s="4"/>
       <c r="E10161" s="4"/>
     </row>
-    <row r="10163" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="10163" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D10163" s="4"/>
       <c r="E10163" s="4"/>
     </row>
-    <row r="12413" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="12413" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D12413" s="4"/>
       <c r="E12413" s="4"/>
     </row>
-    <row r="12417" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="12417" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D12417" s="4"/>
       <c r="E12417" s="4"/>
     </row>
-    <row r="13531" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="13531" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D13531" s="4"/>
       <c r="E13531" s="4"/>
     </row>
-    <row r="13535" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="13535" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D13535" s="4"/>
       <c r="E13535" s="4"/>
     </row>
-    <row r="13905" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="13905" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D13905" s="4"/>
       <c r="E13905" s="4"/>
     </row>
-    <row r="16902" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="16902" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D16902" s="4"/>
       <c r="E16902" s="4"/>
     </row>
-    <row r="16911" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="16911" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D16911" s="4"/>
       <c r="E16911" s="4"/>
     </row>
-    <row r="17232" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="17232" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D17232" s="4"/>
       <c r="E17232" s="4"/>
     </row>
-    <row r="17256" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="17256" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D17256" s="4"/>
       <c r="E17256" s="4"/>
     </row>
-    <row r="17261" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="17261" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D17261" s="4"/>
       <c r="E17261" s="4"/>
     </row>
-    <row r="17674" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="17674" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D17674" s="4"/>
       <c r="E17674" s="4"/>
     </row>
-    <row r="17690" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="17690" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D17690" s="4"/>
       <c r="E17690" s="4"/>
     </row>
-    <row r="19342" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="19342" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D19342" s="4"/>
       <c r="E19342" s="4"/>
     </row>
-    <row r="21113" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="21113" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D21113" s="4"/>
       <c r="E21113" s="4"/>
     </row>
-    <row r="21114" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="21114" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D21114" s="4"/>
       <c r="E21114" s="4"/>
     </row>
-    <row r="21115" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="21115" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D21115" s="4"/>
       <c r="E21115" s="4"/>
     </row>
-    <row r="21116" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="21116" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D21116" s="4"/>
       <c r="E21116" s="4"/>
     </row>
-    <row r="21118" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="21118" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D21118" s="4"/>
       <c r="E21118" s="4"/>
     </row>
-    <row r="21209" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="21209" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D21209" s="4"/>
       <c r="E21209" s="4"/>
     </row>
-    <row r="21211" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="21211" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D21211" s="4"/>
       <c r="E21211" s="4"/>
     </row>
-    <row r="21212" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="21212" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D21212" s="4"/>
       <c r="E21212" s="4"/>
     </row>
-    <row r="21213" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="21213" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D21213" s="4"/>
       <c r="E21213" s="4"/>
     </row>
-    <row r="21214" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="21214" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D21214" s="4"/>
       <c r="E21214" s="4"/>
     </row>
-    <row r="21655" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="21655" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D21655" s="4"/>
       <c r="E21655" s="4"/>
     </row>
-    <row r="21693" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="21693" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D21693" s="4"/>
       <c r="E21693" s="4"/>
     </row>
-    <row r="21700" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="21700" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D21700" s="4"/>
       <c r="E21700" s="4"/>
     </row>
-    <row r="22388" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="22388" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D22388" s="4"/>
       <c r="E22388" s="4"/>
     </row>
-    <row r="22396" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="22396" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D22396" s="4"/>
       <c r="E22396" s="4"/>
     </row>
-    <row r="22397" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="22397" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D22397" s="4"/>
       <c r="E22397" s="4"/>
     </row>
-    <row r="22398" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="22398" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D22398" s="4"/>
       <c r="E22398" s="4"/>
     </row>
-    <row r="22507" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="22507" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D22507" s="4"/>
       <c r="E22507" s="4"/>
     </row>
-    <row r="22691" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="22691" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D22691" s="4"/>
       <c r="E22691" s="4"/>
     </row>
-    <row r="23050" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="23050" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D23050" s="4"/>
       <c r="E23050" s="4"/>
     </row>
-    <row r="23060" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="23060" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D23060" s="4"/>
       <c r="E23060" s="4"/>
     </row>
-    <row r="23554" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="23554" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D23554" s="4"/>
       <c r="E23554" s="4"/>
     </row>
-    <row r="23556" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="23556" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D23556" s="4"/>
       <c r="E23556" s="4"/>
     </row>
-    <row r="23557" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="23557" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D23557" s="4"/>
       <c r="E23557" s="4"/>
     </row>
-    <row r="23558" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="23558" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D23558" s="4"/>
       <c r="E23558" s="4"/>
     </row>
-    <row r="23942" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="23942" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D23942" s="4"/>
       <c r="E23942" s="4"/>
     </row>
-    <row r="23944" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="23944" spans="4:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="D23944" s="4"/>
       <c r="E23944" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="AN10:AQ10"/>
+    <mergeCell ref="AR10:AU10"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="BM10:BP10"/>
+    <mergeCell ref="AW3:BD3"/>
+    <mergeCell ref="G3:N3"/>
+    <mergeCell ref="G10:N10"/>
+    <mergeCell ref="AB3:AI3"/>
+    <mergeCell ref="AB10:AI10"/>
+    <mergeCell ref="AJ3:AM3"/>
+    <mergeCell ref="O10:R10"/>
+    <mergeCell ref="S10:V10"/>
+    <mergeCell ref="W10:Z10"/>
+    <mergeCell ref="AJ10:AM10"/>
+    <mergeCell ref="AN3:AQ3"/>
+    <mergeCell ref="AR3:AU3"/>
+    <mergeCell ref="O3:R3"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="W3:Z3"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="CM3:CT3"/>
@@ -25613,27 +25674,6 @@
     <mergeCell ref="BE10:BH10"/>
     <mergeCell ref="AW10:BD10"/>
     <mergeCell ref="BI10:BL10"/>
-    <mergeCell ref="BM10:BP10"/>
-    <mergeCell ref="AW3:BD3"/>
-    <mergeCell ref="G3:N3"/>
-    <mergeCell ref="G10:N10"/>
-    <mergeCell ref="AB3:AI3"/>
-    <mergeCell ref="AB10:AI10"/>
-    <mergeCell ref="AJ3:AM3"/>
-    <mergeCell ref="O10:R10"/>
-    <mergeCell ref="S10:V10"/>
-    <mergeCell ref="W10:Z10"/>
-    <mergeCell ref="AJ10:AM10"/>
-    <mergeCell ref="AN3:AQ3"/>
-    <mergeCell ref="AR3:AU3"/>
-    <mergeCell ref="O3:R3"/>
-    <mergeCell ref="S3:V3"/>
-    <mergeCell ref="W3:Z3"/>
-    <mergeCell ref="AN10:AQ10"/>
-    <mergeCell ref="AR10:AU10"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="F10:F11"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="L5:L7 AG5:AG7 BB5:BB7 BW5:BW7 CR5:CR7 L12:L20 AG12:AG20 BB12:BB20 BW12:BW20 CR12:CR20">
@@ -25653,7 +25693,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="60" orientation="landscape" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="46" orientation="landscape" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
